--- a/templates/Weekflow_Task导入模板.xlsx
+++ b/templates/Weekflow_Task导入模板.xlsx
@@ -4382,7 +4382,7 @@
     <row r="5" ht="24" customHeight="1">
       <c r="A5" s="16" t="inlineStr">
         <is>
-          <t>4. 校验无误后点击“确认导入”；导入只会新增 Task，不会覆盖已有 Task。</t>
+          <t>4. 校验无误后选择“补充导入”或“完整覆盖”；完整覆盖会连续确认两次。</t>
         </is>
       </c>
     </row>

--- a/templates/Weekflow_Task导入模板.xlsx
+++ b/templates/Weekflow_Task导入模板.xlsx
@@ -11,11 +11,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="填写说明" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Task导入'!$A$4:$P$204</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Task导入'!$A$4:$T$204</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Task导入'!$1:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'Task导入'!$A$1:$P$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'填写说明'!$A$6:$D$22</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'填写说明'!$A$1:$D$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Task导入'!$A$1:$T$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'填写说明'!$A$6:$D$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'填写说明'!$A$1:$D$26</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:P204"/>
+  <dimension ref="A1:T204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -579,15 +579,19 @@
     <col width="11" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
     <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
     <col width="14" customWidth="1" min="10" max="10"/>
-    <col width="18" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="26" customWidth="1" min="13" max="13"/>
-    <col width="34" customWidth="1" min="14" max="14"/>
-    <col width="38" customWidth="1" min="15" max="15"/>
-    <col width="38" customWidth="1" min="16" max="16"/>
+    <col width="32" customWidth="1" min="11" max="11"/>
+    <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+    <col width="18" customWidth="1" min="15" max="15"/>
+    <col width="20" customWidth="1" min="16" max="16"/>
+    <col width="26" customWidth="1" min="17" max="17"/>
+    <col width="34" customWidth="1" min="18" max="18"/>
+    <col width="38" customWidth="1" min="19" max="19"/>
+    <col width="38" customWidth="1" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
@@ -647,47 +651,67 @@
           <t>DDL*</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>周期</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>周期开始</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>周期结束</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>周期完成记录</t>
+        </is>
+      </c>
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>紧急程度*</t>
         </is>
       </c>
-      <c r="I4" s="5" t="inlineStr">
+      <c r="M4" s="5" t="inlineStr">
         <is>
           <t>完成状态</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="N4" s="5" t="inlineStr">
         <is>
           <t>完成日期</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="O4" s="4" t="inlineStr">
         <is>
           <t>汇报对象*</t>
         </is>
       </c>
-      <c r="L4" s="5" t="inlineStr">
+      <c r="P4" s="5" t="inlineStr">
         <is>
           <t>管理对象</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="Q4" s="4" t="inlineStr">
         <is>
           <t>交付物*</t>
         </is>
       </c>
-      <c r="N4" s="5" t="inlineStr">
+      <c r="R4" s="5" t="inlineStr">
         <is>
           <t>进度记录</t>
         </is>
       </c>
-      <c r="O4" s="5" t="inlineStr">
+      <c r="S4" s="5" t="inlineStr">
         <is>
           <t>说明文档链接</t>
         </is>
       </c>
-      <c r="P4" s="5" t="inlineStr">
+      <c r="T4" s="5" t="inlineStr">
         <is>
           <t>交付物链接</t>
         </is>
@@ -702,14 +726,18 @@
       <c r="F5" s="6" t="n"/>
       <c r="G5" s="8" t="n"/>
       <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
+      <c r="I5" s="8" t="n"/>
       <c r="J5" s="8" t="n"/>
-      <c r="K5" s="6" t="n"/>
+      <c r="K5" s="9" t="n"/>
       <c r="L5" s="6" t="n"/>
-      <c r="M5" s="9" t="n"/>
-      <c r="N5" s="9" t="n"/>
-      <c r="O5" s="9" t="n"/>
-      <c r="P5" s="9" t="n"/>
+      <c r="M5" s="6" t="n"/>
+      <c r="N5" s="8" t="n"/>
+      <c r="O5" s="6" t="n"/>
+      <c r="P5" s="6" t="n"/>
+      <c r="Q5" s="9" t="n"/>
+      <c r="R5" s="9" t="n"/>
+      <c r="S5" s="9" t="n"/>
+      <c r="T5" s="9" t="n"/>
     </row>
     <row r="6" ht="23" customHeight="1">
       <c r="A6" s="10" t="n"/>
@@ -720,14 +748,18 @@
       <c r="F6" s="10" t="n"/>
       <c r="G6" s="12" t="n"/>
       <c r="H6" s="10" t="n"/>
-      <c r="I6" s="10" t="n"/>
+      <c r="I6" s="12" t="n"/>
       <c r="J6" s="12" t="n"/>
-      <c r="K6" s="10" t="n"/>
+      <c r="K6" s="13" t="n"/>
       <c r="L6" s="10" t="n"/>
-      <c r="M6" s="13" t="n"/>
-      <c r="N6" s="13" t="n"/>
-      <c r="O6" s="13" t="n"/>
-      <c r="P6" s="13" t="n"/>
+      <c r="M6" s="10" t="n"/>
+      <c r="N6" s="12" t="n"/>
+      <c r="O6" s="10" t="n"/>
+      <c r="P6" s="10" t="n"/>
+      <c r="Q6" s="13" t="n"/>
+      <c r="R6" s="13" t="n"/>
+      <c r="S6" s="13" t="n"/>
+      <c r="T6" s="13" t="n"/>
     </row>
     <row r="7" ht="23" customHeight="1">
       <c r="A7" s="6" t="n"/>
@@ -738,14 +770,18 @@
       <c r="F7" s="6" t="n"/>
       <c r="G7" s="8" t="n"/>
       <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
+      <c r="I7" s="8" t="n"/>
       <c r="J7" s="8" t="n"/>
-      <c r="K7" s="6" t="n"/>
+      <c r="K7" s="9" t="n"/>
       <c r="L7" s="6" t="n"/>
-      <c r="M7" s="9" t="n"/>
-      <c r="N7" s="9" t="n"/>
-      <c r="O7" s="9" t="n"/>
-      <c r="P7" s="9" t="n"/>
+      <c r="M7" s="6" t="n"/>
+      <c r="N7" s="8" t="n"/>
+      <c r="O7" s="6" t="n"/>
+      <c r="P7" s="6" t="n"/>
+      <c r="Q7" s="9" t="n"/>
+      <c r="R7" s="9" t="n"/>
+      <c r="S7" s="9" t="n"/>
+      <c r="T7" s="9" t="n"/>
     </row>
     <row r="8" ht="23" customHeight="1">
       <c r="A8" s="10" t="n"/>
@@ -756,14 +792,18 @@
       <c r="F8" s="10" t="n"/>
       <c r="G8" s="12" t="n"/>
       <c r="H8" s="10" t="n"/>
-      <c r="I8" s="10" t="n"/>
+      <c r="I8" s="12" t="n"/>
       <c r="J8" s="12" t="n"/>
-      <c r="K8" s="10" t="n"/>
+      <c r="K8" s="13" t="n"/>
       <c r="L8" s="10" t="n"/>
-      <c r="M8" s="13" t="n"/>
-      <c r="N8" s="13" t="n"/>
-      <c r="O8" s="13" t="n"/>
-      <c r="P8" s="13" t="n"/>
+      <c r="M8" s="10" t="n"/>
+      <c r="N8" s="12" t="n"/>
+      <c r="O8" s="10" t="n"/>
+      <c r="P8" s="10" t="n"/>
+      <c r="Q8" s="13" t="n"/>
+      <c r="R8" s="13" t="n"/>
+      <c r="S8" s="13" t="n"/>
+      <c r="T8" s="13" t="n"/>
     </row>
     <row r="9" ht="23" customHeight="1">
       <c r="A9" s="6" t="n"/>
@@ -774,14 +814,18 @@
       <c r="F9" s="6" t="n"/>
       <c r="G9" s="8" t="n"/>
       <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
+      <c r="I9" s="8" t="n"/>
       <c r="J9" s="8" t="n"/>
-      <c r="K9" s="6" t="n"/>
+      <c r="K9" s="9" t="n"/>
       <c r="L9" s="6" t="n"/>
-      <c r="M9" s="9" t="n"/>
-      <c r="N9" s="9" t="n"/>
-      <c r="O9" s="9" t="n"/>
-      <c r="P9" s="9" t="n"/>
+      <c r="M9" s="6" t="n"/>
+      <c r="N9" s="8" t="n"/>
+      <c r="O9" s="6" t="n"/>
+      <c r="P9" s="6" t="n"/>
+      <c r="Q9" s="9" t="n"/>
+      <c r="R9" s="9" t="n"/>
+      <c r="S9" s="9" t="n"/>
+      <c r="T9" s="9" t="n"/>
     </row>
     <row r="10" ht="23" customHeight="1">
       <c r="A10" s="10" t="n"/>
@@ -792,14 +836,18 @@
       <c r="F10" s="10" t="n"/>
       <c r="G10" s="12" t="n"/>
       <c r="H10" s="10" t="n"/>
-      <c r="I10" s="10" t="n"/>
+      <c r="I10" s="12" t="n"/>
       <c r="J10" s="12" t="n"/>
-      <c r="K10" s="10" t="n"/>
+      <c r="K10" s="13" t="n"/>
       <c r="L10" s="10" t="n"/>
-      <c r="M10" s="13" t="n"/>
-      <c r="N10" s="13" t="n"/>
-      <c r="O10" s="13" t="n"/>
-      <c r="P10" s="13" t="n"/>
+      <c r="M10" s="10" t="n"/>
+      <c r="N10" s="12" t="n"/>
+      <c r="O10" s="10" t="n"/>
+      <c r="P10" s="10" t="n"/>
+      <c r="Q10" s="13" t="n"/>
+      <c r="R10" s="13" t="n"/>
+      <c r="S10" s="13" t="n"/>
+      <c r="T10" s="13" t="n"/>
     </row>
     <row r="11" ht="23" customHeight="1">
       <c r="A11" s="6" t="n"/>
@@ -810,14 +858,18 @@
       <c r="F11" s="6" t="n"/>
       <c r="G11" s="8" t="n"/>
       <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
+      <c r="I11" s="8" t="n"/>
       <c r="J11" s="8" t="n"/>
-      <c r="K11" s="6" t="n"/>
+      <c r="K11" s="9" t="n"/>
       <c r="L11" s="6" t="n"/>
-      <c r="M11" s="9" t="n"/>
-      <c r="N11" s="9" t="n"/>
-      <c r="O11" s="9" t="n"/>
-      <c r="P11" s="9" t="n"/>
+      <c r="M11" s="6" t="n"/>
+      <c r="N11" s="8" t="n"/>
+      <c r="O11" s="6" t="n"/>
+      <c r="P11" s="6" t="n"/>
+      <c r="Q11" s="9" t="n"/>
+      <c r="R11" s="9" t="n"/>
+      <c r="S11" s="9" t="n"/>
+      <c r="T11" s="9" t="n"/>
     </row>
     <row r="12" ht="23" customHeight="1">
       <c r="A12" s="10" t="n"/>
@@ -828,14 +880,18 @@
       <c r="F12" s="10" t="n"/>
       <c r="G12" s="12" t="n"/>
       <c r="H12" s="10" t="n"/>
-      <c r="I12" s="10" t="n"/>
+      <c r="I12" s="12" t="n"/>
       <c r="J12" s="12" t="n"/>
-      <c r="K12" s="10" t="n"/>
+      <c r="K12" s="13" t="n"/>
       <c r="L12" s="10" t="n"/>
-      <c r="M12" s="13" t="n"/>
-      <c r="N12" s="13" t="n"/>
-      <c r="O12" s="13" t="n"/>
-      <c r="P12" s="13" t="n"/>
+      <c r="M12" s="10" t="n"/>
+      <c r="N12" s="12" t="n"/>
+      <c r="O12" s="10" t="n"/>
+      <c r="P12" s="10" t="n"/>
+      <c r="Q12" s="13" t="n"/>
+      <c r="R12" s="13" t="n"/>
+      <c r="S12" s="13" t="n"/>
+      <c r="T12" s="13" t="n"/>
     </row>
     <row r="13" ht="23" customHeight="1">
       <c r="A13" s="6" t="n"/>
@@ -846,14 +902,18 @@
       <c r="F13" s="6" t="n"/>
       <c r="G13" s="8" t="n"/>
       <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
+      <c r="I13" s="8" t="n"/>
       <c r="J13" s="8" t="n"/>
-      <c r="K13" s="6" t="n"/>
+      <c r="K13" s="9" t="n"/>
       <c r="L13" s="6" t="n"/>
-      <c r="M13" s="9" t="n"/>
-      <c r="N13" s="9" t="n"/>
-      <c r="O13" s="9" t="n"/>
-      <c r="P13" s="9" t="n"/>
+      <c r="M13" s="6" t="n"/>
+      <c r="N13" s="8" t="n"/>
+      <c r="O13" s="6" t="n"/>
+      <c r="P13" s="6" t="n"/>
+      <c r="Q13" s="9" t="n"/>
+      <c r="R13" s="9" t="n"/>
+      <c r="S13" s="9" t="n"/>
+      <c r="T13" s="9" t="n"/>
     </row>
     <row r="14" ht="23" customHeight="1">
       <c r="A14" s="10" t="n"/>
@@ -864,14 +924,18 @@
       <c r="F14" s="10" t="n"/>
       <c r="G14" s="12" t="n"/>
       <c r="H14" s="10" t="n"/>
-      <c r="I14" s="10" t="n"/>
+      <c r="I14" s="12" t="n"/>
       <c r="J14" s="12" t="n"/>
-      <c r="K14" s="10" t="n"/>
+      <c r="K14" s="13" t="n"/>
       <c r="L14" s="10" t="n"/>
-      <c r="M14" s="13" t="n"/>
-      <c r="N14" s="13" t="n"/>
-      <c r="O14" s="13" t="n"/>
-      <c r="P14" s="13" t="n"/>
+      <c r="M14" s="10" t="n"/>
+      <c r="N14" s="12" t="n"/>
+      <c r="O14" s="10" t="n"/>
+      <c r="P14" s="10" t="n"/>
+      <c r="Q14" s="13" t="n"/>
+      <c r="R14" s="13" t="n"/>
+      <c r="S14" s="13" t="n"/>
+      <c r="T14" s="13" t="n"/>
     </row>
     <row r="15" ht="23" customHeight="1">
       <c r="A15" s="6" t="n"/>
@@ -882,14 +946,18 @@
       <c r="F15" s="6" t="n"/>
       <c r="G15" s="8" t="n"/>
       <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
+      <c r="I15" s="8" t="n"/>
       <c r="J15" s="8" t="n"/>
-      <c r="K15" s="6" t="n"/>
+      <c r="K15" s="9" t="n"/>
       <c r="L15" s="6" t="n"/>
-      <c r="M15" s="9" t="n"/>
-      <c r="N15" s="9" t="n"/>
-      <c r="O15" s="9" t="n"/>
-      <c r="P15" s="9" t="n"/>
+      <c r="M15" s="6" t="n"/>
+      <c r="N15" s="8" t="n"/>
+      <c r="O15" s="6" t="n"/>
+      <c r="P15" s="6" t="n"/>
+      <c r="Q15" s="9" t="n"/>
+      <c r="R15" s="9" t="n"/>
+      <c r="S15" s="9" t="n"/>
+      <c r="T15" s="9" t="n"/>
     </row>
     <row r="16" ht="23" customHeight="1">
       <c r="A16" s="10" t="n"/>
@@ -900,14 +968,18 @@
       <c r="F16" s="10" t="n"/>
       <c r="G16" s="12" t="n"/>
       <c r="H16" s="10" t="n"/>
-      <c r="I16" s="10" t="n"/>
+      <c r="I16" s="12" t="n"/>
       <c r="J16" s="12" t="n"/>
-      <c r="K16" s="10" t="n"/>
+      <c r="K16" s="13" t="n"/>
       <c r="L16" s="10" t="n"/>
-      <c r="M16" s="13" t="n"/>
-      <c r="N16" s="13" t="n"/>
-      <c r="O16" s="13" t="n"/>
-      <c r="P16" s="13" t="n"/>
+      <c r="M16" s="10" t="n"/>
+      <c r="N16" s="12" t="n"/>
+      <c r="O16" s="10" t="n"/>
+      <c r="P16" s="10" t="n"/>
+      <c r="Q16" s="13" t="n"/>
+      <c r="R16" s="13" t="n"/>
+      <c r="S16" s="13" t="n"/>
+      <c r="T16" s="13" t="n"/>
     </row>
     <row r="17" ht="23" customHeight="1">
       <c r="A17" s="6" t="n"/>
@@ -918,14 +990,18 @@
       <c r="F17" s="6" t="n"/>
       <c r="G17" s="8" t="n"/>
       <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
+      <c r="I17" s="8" t="n"/>
       <c r="J17" s="8" t="n"/>
-      <c r="K17" s="6" t="n"/>
+      <c r="K17" s="9" t="n"/>
       <c r="L17" s="6" t="n"/>
-      <c r="M17" s="9" t="n"/>
-      <c r="N17" s="9" t="n"/>
-      <c r="O17" s="9" t="n"/>
-      <c r="P17" s="9" t="n"/>
+      <c r="M17" s="6" t="n"/>
+      <c r="N17" s="8" t="n"/>
+      <c r="O17" s="6" t="n"/>
+      <c r="P17" s="6" t="n"/>
+      <c r="Q17" s="9" t="n"/>
+      <c r="R17" s="9" t="n"/>
+      <c r="S17" s="9" t="n"/>
+      <c r="T17" s="9" t="n"/>
     </row>
     <row r="18" ht="23" customHeight="1">
       <c r="A18" s="10" t="n"/>
@@ -936,14 +1012,18 @@
       <c r="F18" s="10" t="n"/>
       <c r="G18" s="12" t="n"/>
       <c r="H18" s="10" t="n"/>
-      <c r="I18" s="10" t="n"/>
+      <c r="I18" s="12" t="n"/>
       <c r="J18" s="12" t="n"/>
-      <c r="K18" s="10" t="n"/>
+      <c r="K18" s="13" t="n"/>
       <c r="L18" s="10" t="n"/>
-      <c r="M18" s="13" t="n"/>
-      <c r="N18" s="13" t="n"/>
-      <c r="O18" s="13" t="n"/>
-      <c r="P18" s="13" t="n"/>
+      <c r="M18" s="10" t="n"/>
+      <c r="N18" s="12" t="n"/>
+      <c r="O18" s="10" t="n"/>
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="13" t="n"/>
+      <c r="R18" s="13" t="n"/>
+      <c r="S18" s="13" t="n"/>
+      <c r="T18" s="13" t="n"/>
     </row>
     <row r="19" ht="23" customHeight="1">
       <c r="A19" s="6" t="n"/>
@@ -954,14 +1034,18 @@
       <c r="F19" s="6" t="n"/>
       <c r="G19" s="8" t="n"/>
       <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
+      <c r="I19" s="8" t="n"/>
       <c r="J19" s="8" t="n"/>
-      <c r="K19" s="6" t="n"/>
+      <c r="K19" s="9" t="n"/>
       <c r="L19" s="6" t="n"/>
-      <c r="M19" s="9" t="n"/>
-      <c r="N19" s="9" t="n"/>
-      <c r="O19" s="9" t="n"/>
-      <c r="P19" s="9" t="n"/>
+      <c r="M19" s="6" t="n"/>
+      <c r="N19" s="8" t="n"/>
+      <c r="O19" s="6" t="n"/>
+      <c r="P19" s="6" t="n"/>
+      <c r="Q19" s="9" t="n"/>
+      <c r="R19" s="9" t="n"/>
+      <c r="S19" s="9" t="n"/>
+      <c r="T19" s="9" t="n"/>
     </row>
     <row r="20" ht="23" customHeight="1">
       <c r="A20" s="10" t="n"/>
@@ -972,14 +1056,18 @@
       <c r="F20" s="10" t="n"/>
       <c r="G20" s="12" t="n"/>
       <c r="H20" s="10" t="n"/>
-      <c r="I20" s="10" t="n"/>
+      <c r="I20" s="12" t="n"/>
       <c r="J20" s="12" t="n"/>
-      <c r="K20" s="10" t="n"/>
+      <c r="K20" s="13" t="n"/>
       <c r="L20" s="10" t="n"/>
-      <c r="M20" s="13" t="n"/>
-      <c r="N20" s="13" t="n"/>
-      <c r="O20" s="13" t="n"/>
-      <c r="P20" s="13" t="n"/>
+      <c r="M20" s="10" t="n"/>
+      <c r="N20" s="12" t="n"/>
+      <c r="O20" s="10" t="n"/>
+      <c r="P20" s="10" t="n"/>
+      <c r="Q20" s="13" t="n"/>
+      <c r="R20" s="13" t="n"/>
+      <c r="S20" s="13" t="n"/>
+      <c r="T20" s="13" t="n"/>
     </row>
     <row r="21" ht="23" customHeight="1">
       <c r="A21" s="6" t="n"/>
@@ -990,14 +1078,18 @@
       <c r="F21" s="6" t="n"/>
       <c r="G21" s="8" t="n"/>
       <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
+      <c r="I21" s="8" t="n"/>
       <c r="J21" s="8" t="n"/>
-      <c r="K21" s="6" t="n"/>
+      <c r="K21" s="9" t="n"/>
       <c r="L21" s="6" t="n"/>
-      <c r="M21" s="9" t="n"/>
-      <c r="N21" s="9" t="n"/>
-      <c r="O21" s="9" t="n"/>
-      <c r="P21" s="9" t="n"/>
+      <c r="M21" s="6" t="n"/>
+      <c r="N21" s="8" t="n"/>
+      <c r="O21" s="6" t="n"/>
+      <c r="P21" s="6" t="n"/>
+      <c r="Q21" s="9" t="n"/>
+      <c r="R21" s="9" t="n"/>
+      <c r="S21" s="9" t="n"/>
+      <c r="T21" s="9" t="n"/>
     </row>
     <row r="22" ht="23" customHeight="1">
       <c r="A22" s="10" t="n"/>
@@ -1008,14 +1100,18 @@
       <c r="F22" s="10" t="n"/>
       <c r="G22" s="12" t="n"/>
       <c r="H22" s="10" t="n"/>
-      <c r="I22" s="10" t="n"/>
+      <c r="I22" s="12" t="n"/>
       <c r="J22" s="12" t="n"/>
-      <c r="K22" s="10" t="n"/>
+      <c r="K22" s="13" t="n"/>
       <c r="L22" s="10" t="n"/>
-      <c r="M22" s="13" t="n"/>
-      <c r="N22" s="13" t="n"/>
-      <c r="O22" s="13" t="n"/>
-      <c r="P22" s="13" t="n"/>
+      <c r="M22" s="10" t="n"/>
+      <c r="N22" s="12" t="n"/>
+      <c r="O22" s="10" t="n"/>
+      <c r="P22" s="10" t="n"/>
+      <c r="Q22" s="13" t="n"/>
+      <c r="R22" s="13" t="n"/>
+      <c r="S22" s="13" t="n"/>
+      <c r="T22" s="13" t="n"/>
     </row>
     <row r="23" ht="23" customHeight="1">
       <c r="A23" s="6" t="n"/>
@@ -1026,14 +1122,18 @@
       <c r="F23" s="6" t="n"/>
       <c r="G23" s="8" t="n"/>
       <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
+      <c r="I23" s="8" t="n"/>
       <c r="J23" s="8" t="n"/>
-      <c r="K23" s="6" t="n"/>
+      <c r="K23" s="9" t="n"/>
       <c r="L23" s="6" t="n"/>
-      <c r="M23" s="9" t="n"/>
-      <c r="N23" s="9" t="n"/>
-      <c r="O23" s="9" t="n"/>
-      <c r="P23" s="9" t="n"/>
+      <c r="M23" s="6" t="n"/>
+      <c r="N23" s="8" t="n"/>
+      <c r="O23" s="6" t="n"/>
+      <c r="P23" s="6" t="n"/>
+      <c r="Q23" s="9" t="n"/>
+      <c r="R23" s="9" t="n"/>
+      <c r="S23" s="9" t="n"/>
+      <c r="T23" s="9" t="n"/>
     </row>
     <row r="24" ht="23" customHeight="1">
       <c r="A24" s="10" t="n"/>
@@ -1044,14 +1144,18 @@
       <c r="F24" s="10" t="n"/>
       <c r="G24" s="12" t="n"/>
       <c r="H24" s="10" t="n"/>
-      <c r="I24" s="10" t="n"/>
+      <c r="I24" s="12" t="n"/>
       <c r="J24" s="12" t="n"/>
-      <c r="K24" s="10" t="n"/>
+      <c r="K24" s="13" t="n"/>
       <c r="L24" s="10" t="n"/>
-      <c r="M24" s="13" t="n"/>
-      <c r="N24" s="13" t="n"/>
-      <c r="O24" s="13" t="n"/>
-      <c r="P24" s="13" t="n"/>
+      <c r="M24" s="10" t="n"/>
+      <c r="N24" s="12" t="n"/>
+      <c r="O24" s="10" t="n"/>
+      <c r="P24" s="10" t="n"/>
+      <c r="Q24" s="13" t="n"/>
+      <c r="R24" s="13" t="n"/>
+      <c r="S24" s="13" t="n"/>
+      <c r="T24" s="13" t="n"/>
     </row>
     <row r="25" ht="23" customHeight="1">
       <c r="A25" s="6" t="n"/>
@@ -1062,14 +1166,18 @@
       <c r="F25" s="6" t="n"/>
       <c r="G25" s="8" t="n"/>
       <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
+      <c r="I25" s="8" t="n"/>
       <c r="J25" s="8" t="n"/>
-      <c r="K25" s="6" t="n"/>
+      <c r="K25" s="9" t="n"/>
       <c r="L25" s="6" t="n"/>
-      <c r="M25" s="9" t="n"/>
-      <c r="N25" s="9" t="n"/>
-      <c r="O25" s="9" t="n"/>
-      <c r="P25" s="9" t="n"/>
+      <c r="M25" s="6" t="n"/>
+      <c r="N25" s="8" t="n"/>
+      <c r="O25" s="6" t="n"/>
+      <c r="P25" s="6" t="n"/>
+      <c r="Q25" s="9" t="n"/>
+      <c r="R25" s="9" t="n"/>
+      <c r="S25" s="9" t="n"/>
+      <c r="T25" s="9" t="n"/>
     </row>
     <row r="26" ht="23" customHeight="1">
       <c r="A26" s="10" t="n"/>
@@ -1080,14 +1188,18 @@
       <c r="F26" s="10" t="n"/>
       <c r="G26" s="12" t="n"/>
       <c r="H26" s="10" t="n"/>
-      <c r="I26" s="10" t="n"/>
+      <c r="I26" s="12" t="n"/>
       <c r="J26" s="12" t="n"/>
-      <c r="K26" s="10" t="n"/>
+      <c r="K26" s="13" t="n"/>
       <c r="L26" s="10" t="n"/>
-      <c r="M26" s="13" t="n"/>
-      <c r="N26" s="13" t="n"/>
-      <c r="O26" s="13" t="n"/>
-      <c r="P26" s="13" t="n"/>
+      <c r="M26" s="10" t="n"/>
+      <c r="N26" s="12" t="n"/>
+      <c r="O26" s="10" t="n"/>
+      <c r="P26" s="10" t="n"/>
+      <c r="Q26" s="13" t="n"/>
+      <c r="R26" s="13" t="n"/>
+      <c r="S26" s="13" t="n"/>
+      <c r="T26" s="13" t="n"/>
     </row>
     <row r="27" ht="23" customHeight="1">
       <c r="A27" s="6" t="n"/>
@@ -1098,14 +1210,18 @@
       <c r="F27" s="6" t="n"/>
       <c r="G27" s="8" t="n"/>
       <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
+      <c r="I27" s="8" t="n"/>
       <c r="J27" s="8" t="n"/>
-      <c r="K27" s="6" t="n"/>
+      <c r="K27" s="9" t="n"/>
       <c r="L27" s="6" t="n"/>
-      <c r="M27" s="9" t="n"/>
-      <c r="N27" s="9" t="n"/>
-      <c r="O27" s="9" t="n"/>
-      <c r="P27" s="9" t="n"/>
+      <c r="M27" s="6" t="n"/>
+      <c r="N27" s="8" t="n"/>
+      <c r="O27" s="6" t="n"/>
+      <c r="P27" s="6" t="n"/>
+      <c r="Q27" s="9" t="n"/>
+      <c r="R27" s="9" t="n"/>
+      <c r="S27" s="9" t="n"/>
+      <c r="T27" s="9" t="n"/>
     </row>
     <row r="28" ht="23" customHeight="1">
       <c r="A28" s="10" t="n"/>
@@ -1116,14 +1232,18 @@
       <c r="F28" s="10" t="n"/>
       <c r="G28" s="12" t="n"/>
       <c r="H28" s="10" t="n"/>
-      <c r="I28" s="10" t="n"/>
+      <c r="I28" s="12" t="n"/>
       <c r="J28" s="12" t="n"/>
-      <c r="K28" s="10" t="n"/>
+      <c r="K28" s="13" t="n"/>
       <c r="L28" s="10" t="n"/>
-      <c r="M28" s="13" t="n"/>
-      <c r="N28" s="13" t="n"/>
-      <c r="O28" s="13" t="n"/>
-      <c r="P28" s="13" t="n"/>
+      <c r="M28" s="10" t="n"/>
+      <c r="N28" s="12" t="n"/>
+      <c r="O28" s="10" t="n"/>
+      <c r="P28" s="10" t="n"/>
+      <c r="Q28" s="13" t="n"/>
+      <c r="R28" s="13" t="n"/>
+      <c r="S28" s="13" t="n"/>
+      <c r="T28" s="13" t="n"/>
     </row>
     <row r="29" ht="23" customHeight="1">
       <c r="A29" s="6" t="n"/>
@@ -1134,14 +1254,18 @@
       <c r="F29" s="6" t="n"/>
       <c r="G29" s="8" t="n"/>
       <c r="H29" s="6" t="n"/>
-      <c r="I29" s="6" t="n"/>
+      <c r="I29" s="8" t="n"/>
       <c r="J29" s="8" t="n"/>
-      <c r="K29" s="6" t="n"/>
+      <c r="K29" s="9" t="n"/>
       <c r="L29" s="6" t="n"/>
-      <c r="M29" s="9" t="n"/>
-      <c r="N29" s="9" t="n"/>
-      <c r="O29" s="9" t="n"/>
-      <c r="P29" s="9" t="n"/>
+      <c r="M29" s="6" t="n"/>
+      <c r="N29" s="8" t="n"/>
+      <c r="O29" s="6" t="n"/>
+      <c r="P29" s="6" t="n"/>
+      <c r="Q29" s="9" t="n"/>
+      <c r="R29" s="9" t="n"/>
+      <c r="S29" s="9" t="n"/>
+      <c r="T29" s="9" t="n"/>
     </row>
     <row r="30" ht="23" customHeight="1">
       <c r="A30" s="10" t="n"/>
@@ -1152,14 +1276,18 @@
       <c r="F30" s="10" t="n"/>
       <c r="G30" s="12" t="n"/>
       <c r="H30" s="10" t="n"/>
-      <c r="I30" s="10" t="n"/>
+      <c r="I30" s="12" t="n"/>
       <c r="J30" s="12" t="n"/>
-      <c r="K30" s="10" t="n"/>
+      <c r="K30" s="13" t="n"/>
       <c r="L30" s="10" t="n"/>
-      <c r="M30" s="13" t="n"/>
-      <c r="N30" s="13" t="n"/>
-      <c r="O30" s="13" t="n"/>
-      <c r="P30" s="13" t="n"/>
+      <c r="M30" s="10" t="n"/>
+      <c r="N30" s="12" t="n"/>
+      <c r="O30" s="10" t="n"/>
+      <c r="P30" s="10" t="n"/>
+      <c r="Q30" s="13" t="n"/>
+      <c r="R30" s="13" t="n"/>
+      <c r="S30" s="13" t="n"/>
+      <c r="T30" s="13" t="n"/>
     </row>
     <row r="31" ht="23" customHeight="1">
       <c r="A31" s="6" t="n"/>
@@ -1170,14 +1298,18 @@
       <c r="F31" s="6" t="n"/>
       <c r="G31" s="8" t="n"/>
       <c r="H31" s="6" t="n"/>
-      <c r="I31" s="6" t="n"/>
+      <c r="I31" s="8" t="n"/>
       <c r="J31" s="8" t="n"/>
-      <c r="K31" s="6" t="n"/>
+      <c r="K31" s="9" t="n"/>
       <c r="L31" s="6" t="n"/>
-      <c r="M31" s="9" t="n"/>
-      <c r="N31" s="9" t="n"/>
-      <c r="O31" s="9" t="n"/>
-      <c r="P31" s="9" t="n"/>
+      <c r="M31" s="6" t="n"/>
+      <c r="N31" s="8" t="n"/>
+      <c r="O31" s="6" t="n"/>
+      <c r="P31" s="6" t="n"/>
+      <c r="Q31" s="9" t="n"/>
+      <c r="R31" s="9" t="n"/>
+      <c r="S31" s="9" t="n"/>
+      <c r="T31" s="9" t="n"/>
     </row>
     <row r="32" ht="23" customHeight="1">
       <c r="A32" s="10" t="n"/>
@@ -1188,14 +1320,18 @@
       <c r="F32" s="10" t="n"/>
       <c r="G32" s="12" t="n"/>
       <c r="H32" s="10" t="n"/>
-      <c r="I32" s="10" t="n"/>
+      <c r="I32" s="12" t="n"/>
       <c r="J32" s="12" t="n"/>
-      <c r="K32" s="10" t="n"/>
+      <c r="K32" s="13" t="n"/>
       <c r="L32" s="10" t="n"/>
-      <c r="M32" s="13" t="n"/>
-      <c r="N32" s="13" t="n"/>
-      <c r="O32" s="13" t="n"/>
-      <c r="P32" s="13" t="n"/>
+      <c r="M32" s="10" t="n"/>
+      <c r="N32" s="12" t="n"/>
+      <c r="O32" s="10" t="n"/>
+      <c r="P32" s="10" t="n"/>
+      <c r="Q32" s="13" t="n"/>
+      <c r="R32" s="13" t="n"/>
+      <c r="S32" s="13" t="n"/>
+      <c r="T32" s="13" t="n"/>
     </row>
     <row r="33" ht="23" customHeight="1">
       <c r="A33" s="6" t="n"/>
@@ -1206,14 +1342,18 @@
       <c r="F33" s="6" t="n"/>
       <c r="G33" s="8" t="n"/>
       <c r="H33" s="6" t="n"/>
-      <c r="I33" s="6" t="n"/>
+      <c r="I33" s="8" t="n"/>
       <c r="J33" s="8" t="n"/>
-      <c r="K33" s="6" t="n"/>
+      <c r="K33" s="9" t="n"/>
       <c r="L33" s="6" t="n"/>
-      <c r="M33" s="9" t="n"/>
-      <c r="N33" s="9" t="n"/>
-      <c r="O33" s="9" t="n"/>
-      <c r="P33" s="9" t="n"/>
+      <c r="M33" s="6" t="n"/>
+      <c r="N33" s="8" t="n"/>
+      <c r="O33" s="6" t="n"/>
+      <c r="P33" s="6" t="n"/>
+      <c r="Q33" s="9" t="n"/>
+      <c r="R33" s="9" t="n"/>
+      <c r="S33" s="9" t="n"/>
+      <c r="T33" s="9" t="n"/>
     </row>
     <row r="34" ht="23" customHeight="1">
       <c r="A34" s="10" t="n"/>
@@ -1224,14 +1364,18 @@
       <c r="F34" s="10" t="n"/>
       <c r="G34" s="12" t="n"/>
       <c r="H34" s="10" t="n"/>
-      <c r="I34" s="10" t="n"/>
+      <c r="I34" s="12" t="n"/>
       <c r="J34" s="12" t="n"/>
-      <c r="K34" s="10" t="n"/>
+      <c r="K34" s="13" t="n"/>
       <c r="L34" s="10" t="n"/>
-      <c r="M34" s="13" t="n"/>
-      <c r="N34" s="13" t="n"/>
-      <c r="O34" s="13" t="n"/>
-      <c r="P34" s="13" t="n"/>
+      <c r="M34" s="10" t="n"/>
+      <c r="N34" s="12" t="n"/>
+      <c r="O34" s="10" t="n"/>
+      <c r="P34" s="10" t="n"/>
+      <c r="Q34" s="13" t="n"/>
+      <c r="R34" s="13" t="n"/>
+      <c r="S34" s="13" t="n"/>
+      <c r="T34" s="13" t="n"/>
     </row>
     <row r="35" ht="23" customHeight="1">
       <c r="A35" s="6" t="n"/>
@@ -1242,14 +1386,18 @@
       <c r="F35" s="6" t="n"/>
       <c r="G35" s="8" t="n"/>
       <c r="H35" s="6" t="n"/>
-      <c r="I35" s="6" t="n"/>
+      <c r="I35" s="8" t="n"/>
       <c r="J35" s="8" t="n"/>
-      <c r="K35" s="6" t="n"/>
+      <c r="K35" s="9" t="n"/>
       <c r="L35" s="6" t="n"/>
-      <c r="M35" s="9" t="n"/>
-      <c r="N35" s="9" t="n"/>
-      <c r="O35" s="9" t="n"/>
-      <c r="P35" s="9" t="n"/>
+      <c r="M35" s="6" t="n"/>
+      <c r="N35" s="8" t="n"/>
+      <c r="O35" s="6" t="n"/>
+      <c r="P35" s="6" t="n"/>
+      <c r="Q35" s="9" t="n"/>
+      <c r="R35" s="9" t="n"/>
+      <c r="S35" s="9" t="n"/>
+      <c r="T35" s="9" t="n"/>
     </row>
     <row r="36" ht="23" customHeight="1">
       <c r="A36" s="10" t="n"/>
@@ -1260,14 +1408,18 @@
       <c r="F36" s="10" t="n"/>
       <c r="G36" s="12" t="n"/>
       <c r="H36" s="10" t="n"/>
-      <c r="I36" s="10" t="n"/>
+      <c r="I36" s="12" t="n"/>
       <c r="J36" s="12" t="n"/>
-      <c r="K36" s="10" t="n"/>
+      <c r="K36" s="13" t="n"/>
       <c r="L36" s="10" t="n"/>
-      <c r="M36" s="13" t="n"/>
-      <c r="N36" s="13" t="n"/>
-      <c r="O36" s="13" t="n"/>
-      <c r="P36" s="13" t="n"/>
+      <c r="M36" s="10" t="n"/>
+      <c r="N36" s="12" t="n"/>
+      <c r="O36" s="10" t="n"/>
+      <c r="P36" s="10" t="n"/>
+      <c r="Q36" s="13" t="n"/>
+      <c r="R36" s="13" t="n"/>
+      <c r="S36" s="13" t="n"/>
+      <c r="T36" s="13" t="n"/>
     </row>
     <row r="37" ht="23" customHeight="1">
       <c r="A37" s="6" t="n"/>
@@ -1278,14 +1430,18 @@
       <c r="F37" s="6" t="n"/>
       <c r="G37" s="8" t="n"/>
       <c r="H37" s="6" t="n"/>
-      <c r="I37" s="6" t="n"/>
+      <c r="I37" s="8" t="n"/>
       <c r="J37" s="8" t="n"/>
-      <c r="K37" s="6" t="n"/>
+      <c r="K37" s="9" t="n"/>
       <c r="L37" s="6" t="n"/>
-      <c r="M37" s="9" t="n"/>
-      <c r="N37" s="9" t="n"/>
-      <c r="O37" s="9" t="n"/>
-      <c r="P37" s="9" t="n"/>
+      <c r="M37" s="6" t="n"/>
+      <c r="N37" s="8" t="n"/>
+      <c r="O37" s="6" t="n"/>
+      <c r="P37" s="6" t="n"/>
+      <c r="Q37" s="9" t="n"/>
+      <c r="R37" s="9" t="n"/>
+      <c r="S37" s="9" t="n"/>
+      <c r="T37" s="9" t="n"/>
     </row>
     <row r="38" ht="23" customHeight="1">
       <c r="A38" s="10" t="n"/>
@@ -1296,14 +1452,18 @@
       <c r="F38" s="10" t="n"/>
       <c r="G38" s="12" t="n"/>
       <c r="H38" s="10" t="n"/>
-      <c r="I38" s="10" t="n"/>
+      <c r="I38" s="12" t="n"/>
       <c r="J38" s="12" t="n"/>
-      <c r="K38" s="10" t="n"/>
+      <c r="K38" s="13" t="n"/>
       <c r="L38" s="10" t="n"/>
-      <c r="M38" s="13" t="n"/>
-      <c r="N38" s="13" t="n"/>
-      <c r="O38" s="13" t="n"/>
-      <c r="P38" s="13" t="n"/>
+      <c r="M38" s="10" t="n"/>
+      <c r="N38" s="12" t="n"/>
+      <c r="O38" s="10" t="n"/>
+      <c r="P38" s="10" t="n"/>
+      <c r="Q38" s="13" t="n"/>
+      <c r="R38" s="13" t="n"/>
+      <c r="S38" s="13" t="n"/>
+      <c r="T38" s="13" t="n"/>
     </row>
     <row r="39" ht="23" customHeight="1">
       <c r="A39" s="6" t="n"/>
@@ -1314,14 +1474,18 @@
       <c r="F39" s="6" t="n"/>
       <c r="G39" s="8" t="n"/>
       <c r="H39" s="6" t="n"/>
-      <c r="I39" s="6" t="n"/>
+      <c r="I39" s="8" t="n"/>
       <c r="J39" s="8" t="n"/>
-      <c r="K39" s="6" t="n"/>
+      <c r="K39" s="9" t="n"/>
       <c r="L39" s="6" t="n"/>
-      <c r="M39" s="9" t="n"/>
-      <c r="N39" s="9" t="n"/>
-      <c r="O39" s="9" t="n"/>
-      <c r="P39" s="9" t="n"/>
+      <c r="M39" s="6" t="n"/>
+      <c r="N39" s="8" t="n"/>
+      <c r="O39" s="6" t="n"/>
+      <c r="P39" s="6" t="n"/>
+      <c r="Q39" s="9" t="n"/>
+      <c r="R39" s="9" t="n"/>
+      <c r="S39" s="9" t="n"/>
+      <c r="T39" s="9" t="n"/>
     </row>
     <row r="40" ht="23" customHeight="1">
       <c r="A40" s="10" t="n"/>
@@ -1332,14 +1496,18 @@
       <c r="F40" s="10" t="n"/>
       <c r="G40" s="12" t="n"/>
       <c r="H40" s="10" t="n"/>
-      <c r="I40" s="10" t="n"/>
+      <c r="I40" s="12" t="n"/>
       <c r="J40" s="12" t="n"/>
-      <c r="K40" s="10" t="n"/>
+      <c r="K40" s="13" t="n"/>
       <c r="L40" s="10" t="n"/>
-      <c r="M40" s="13" t="n"/>
-      <c r="N40" s="13" t="n"/>
-      <c r="O40" s="13" t="n"/>
-      <c r="P40" s="13" t="n"/>
+      <c r="M40" s="10" t="n"/>
+      <c r="N40" s="12" t="n"/>
+      <c r="O40" s="10" t="n"/>
+      <c r="P40" s="10" t="n"/>
+      <c r="Q40" s="13" t="n"/>
+      <c r="R40" s="13" t="n"/>
+      <c r="S40" s="13" t="n"/>
+      <c r="T40" s="13" t="n"/>
     </row>
     <row r="41" ht="23" customHeight="1">
       <c r="A41" s="6" t="n"/>
@@ -1350,14 +1518,18 @@
       <c r="F41" s="6" t="n"/>
       <c r="G41" s="8" t="n"/>
       <c r="H41" s="6" t="n"/>
-      <c r="I41" s="6" t="n"/>
+      <c r="I41" s="8" t="n"/>
       <c r="J41" s="8" t="n"/>
-      <c r="K41" s="6" t="n"/>
+      <c r="K41" s="9" t="n"/>
       <c r="L41" s="6" t="n"/>
-      <c r="M41" s="9" t="n"/>
-      <c r="N41" s="9" t="n"/>
-      <c r="O41" s="9" t="n"/>
-      <c r="P41" s="9" t="n"/>
+      <c r="M41" s="6" t="n"/>
+      <c r="N41" s="8" t="n"/>
+      <c r="O41" s="6" t="n"/>
+      <c r="P41" s="6" t="n"/>
+      <c r="Q41" s="9" t="n"/>
+      <c r="R41" s="9" t="n"/>
+      <c r="S41" s="9" t="n"/>
+      <c r="T41" s="9" t="n"/>
     </row>
     <row r="42" ht="23" customHeight="1">
       <c r="A42" s="10" t="n"/>
@@ -1368,14 +1540,18 @@
       <c r="F42" s="10" t="n"/>
       <c r="G42" s="12" t="n"/>
       <c r="H42" s="10" t="n"/>
-      <c r="I42" s="10" t="n"/>
+      <c r="I42" s="12" t="n"/>
       <c r="J42" s="12" t="n"/>
-      <c r="K42" s="10" t="n"/>
+      <c r="K42" s="13" t="n"/>
       <c r="L42" s="10" t="n"/>
-      <c r="M42" s="13" t="n"/>
-      <c r="N42" s="13" t="n"/>
-      <c r="O42" s="13" t="n"/>
-      <c r="P42" s="13" t="n"/>
+      <c r="M42" s="10" t="n"/>
+      <c r="N42" s="12" t="n"/>
+      <c r="O42" s="10" t="n"/>
+      <c r="P42" s="10" t="n"/>
+      <c r="Q42" s="13" t="n"/>
+      <c r="R42" s="13" t="n"/>
+      <c r="S42" s="13" t="n"/>
+      <c r="T42" s="13" t="n"/>
     </row>
     <row r="43" ht="23" customHeight="1">
       <c r="A43" s="6" t="n"/>
@@ -1386,14 +1562,18 @@
       <c r="F43" s="6" t="n"/>
       <c r="G43" s="8" t="n"/>
       <c r="H43" s="6" t="n"/>
-      <c r="I43" s="6" t="n"/>
+      <c r="I43" s="8" t="n"/>
       <c r="J43" s="8" t="n"/>
-      <c r="K43" s="6" t="n"/>
+      <c r="K43" s="9" t="n"/>
       <c r="L43" s="6" t="n"/>
-      <c r="M43" s="9" t="n"/>
-      <c r="N43" s="9" t="n"/>
-      <c r="O43" s="9" t="n"/>
-      <c r="P43" s="9" t="n"/>
+      <c r="M43" s="6" t="n"/>
+      <c r="N43" s="8" t="n"/>
+      <c r="O43" s="6" t="n"/>
+      <c r="P43" s="6" t="n"/>
+      <c r="Q43" s="9" t="n"/>
+      <c r="R43" s="9" t="n"/>
+      <c r="S43" s="9" t="n"/>
+      <c r="T43" s="9" t="n"/>
     </row>
     <row r="44" ht="23" customHeight="1">
       <c r="A44" s="10" t="n"/>
@@ -1404,14 +1584,18 @@
       <c r="F44" s="10" t="n"/>
       <c r="G44" s="12" t="n"/>
       <c r="H44" s="10" t="n"/>
-      <c r="I44" s="10" t="n"/>
+      <c r="I44" s="12" t="n"/>
       <c r="J44" s="12" t="n"/>
-      <c r="K44" s="10" t="n"/>
+      <c r="K44" s="13" t="n"/>
       <c r="L44" s="10" t="n"/>
-      <c r="M44" s="13" t="n"/>
-      <c r="N44" s="13" t="n"/>
-      <c r="O44" s="13" t="n"/>
-      <c r="P44" s="13" t="n"/>
+      <c r="M44" s="10" t="n"/>
+      <c r="N44" s="12" t="n"/>
+      <c r="O44" s="10" t="n"/>
+      <c r="P44" s="10" t="n"/>
+      <c r="Q44" s="13" t="n"/>
+      <c r="R44" s="13" t="n"/>
+      <c r="S44" s="13" t="n"/>
+      <c r="T44" s="13" t="n"/>
     </row>
     <row r="45" ht="23" customHeight="1">
       <c r="A45" s="6" t="n"/>
@@ -1422,14 +1606,18 @@
       <c r="F45" s="6" t="n"/>
       <c r="G45" s="8" t="n"/>
       <c r="H45" s="6" t="n"/>
-      <c r="I45" s="6" t="n"/>
+      <c r="I45" s="8" t="n"/>
       <c r="J45" s="8" t="n"/>
-      <c r="K45" s="6" t="n"/>
+      <c r="K45" s="9" t="n"/>
       <c r="L45" s="6" t="n"/>
-      <c r="M45" s="9" t="n"/>
-      <c r="N45" s="9" t="n"/>
-      <c r="O45" s="9" t="n"/>
-      <c r="P45" s="9" t="n"/>
+      <c r="M45" s="6" t="n"/>
+      <c r="N45" s="8" t="n"/>
+      <c r="O45" s="6" t="n"/>
+      <c r="P45" s="6" t="n"/>
+      <c r="Q45" s="9" t="n"/>
+      <c r="R45" s="9" t="n"/>
+      <c r="S45" s="9" t="n"/>
+      <c r="T45" s="9" t="n"/>
     </row>
     <row r="46" ht="23" customHeight="1">
       <c r="A46" s="10" t="n"/>
@@ -1440,14 +1628,18 @@
       <c r="F46" s="10" t="n"/>
       <c r="G46" s="12" t="n"/>
       <c r="H46" s="10" t="n"/>
-      <c r="I46" s="10" t="n"/>
+      <c r="I46" s="12" t="n"/>
       <c r="J46" s="12" t="n"/>
-      <c r="K46" s="10" t="n"/>
+      <c r="K46" s="13" t="n"/>
       <c r="L46" s="10" t="n"/>
-      <c r="M46" s="13" t="n"/>
-      <c r="N46" s="13" t="n"/>
-      <c r="O46" s="13" t="n"/>
-      <c r="P46" s="13" t="n"/>
+      <c r="M46" s="10" t="n"/>
+      <c r="N46" s="12" t="n"/>
+      <c r="O46" s="10" t="n"/>
+      <c r="P46" s="10" t="n"/>
+      <c r="Q46" s="13" t="n"/>
+      <c r="R46" s="13" t="n"/>
+      <c r="S46" s="13" t="n"/>
+      <c r="T46" s="13" t="n"/>
     </row>
     <row r="47" ht="23" customHeight="1">
       <c r="A47" s="6" t="n"/>
@@ -1458,14 +1650,18 @@
       <c r="F47" s="6" t="n"/>
       <c r="G47" s="8" t="n"/>
       <c r="H47" s="6" t="n"/>
-      <c r="I47" s="6" t="n"/>
+      <c r="I47" s="8" t="n"/>
       <c r="J47" s="8" t="n"/>
-      <c r="K47" s="6" t="n"/>
+      <c r="K47" s="9" t="n"/>
       <c r="L47" s="6" t="n"/>
-      <c r="M47" s="9" t="n"/>
-      <c r="N47" s="9" t="n"/>
-      <c r="O47" s="9" t="n"/>
-      <c r="P47" s="9" t="n"/>
+      <c r="M47" s="6" t="n"/>
+      <c r="N47" s="8" t="n"/>
+      <c r="O47" s="6" t="n"/>
+      <c r="P47" s="6" t="n"/>
+      <c r="Q47" s="9" t="n"/>
+      <c r="R47" s="9" t="n"/>
+      <c r="S47" s="9" t="n"/>
+      <c r="T47" s="9" t="n"/>
     </row>
     <row r="48" ht="23" customHeight="1">
       <c r="A48" s="10" t="n"/>
@@ -1476,14 +1672,18 @@
       <c r="F48" s="10" t="n"/>
       <c r="G48" s="12" t="n"/>
       <c r="H48" s="10" t="n"/>
-      <c r="I48" s="10" t="n"/>
+      <c r="I48" s="12" t="n"/>
       <c r="J48" s="12" t="n"/>
-      <c r="K48" s="10" t="n"/>
+      <c r="K48" s="13" t="n"/>
       <c r="L48" s="10" t="n"/>
-      <c r="M48" s="13" t="n"/>
-      <c r="N48" s="13" t="n"/>
-      <c r="O48" s="13" t="n"/>
-      <c r="P48" s="13" t="n"/>
+      <c r="M48" s="10" t="n"/>
+      <c r="N48" s="12" t="n"/>
+      <c r="O48" s="10" t="n"/>
+      <c r="P48" s="10" t="n"/>
+      <c r="Q48" s="13" t="n"/>
+      <c r="R48" s="13" t="n"/>
+      <c r="S48" s="13" t="n"/>
+      <c r="T48" s="13" t="n"/>
     </row>
     <row r="49" ht="23" customHeight="1">
       <c r="A49" s="6" t="n"/>
@@ -1494,14 +1694,18 @@
       <c r="F49" s="6" t="n"/>
       <c r="G49" s="8" t="n"/>
       <c r="H49" s="6" t="n"/>
-      <c r="I49" s="6" t="n"/>
+      <c r="I49" s="8" t="n"/>
       <c r="J49" s="8" t="n"/>
-      <c r="K49" s="6" t="n"/>
+      <c r="K49" s="9" t="n"/>
       <c r="L49" s="6" t="n"/>
-      <c r="M49" s="9" t="n"/>
-      <c r="N49" s="9" t="n"/>
-      <c r="O49" s="9" t="n"/>
-      <c r="P49" s="9" t="n"/>
+      <c r="M49" s="6" t="n"/>
+      <c r="N49" s="8" t="n"/>
+      <c r="O49" s="6" t="n"/>
+      <c r="P49" s="6" t="n"/>
+      <c r="Q49" s="9" t="n"/>
+      <c r="R49" s="9" t="n"/>
+      <c r="S49" s="9" t="n"/>
+      <c r="T49" s="9" t="n"/>
     </row>
     <row r="50" ht="23" customHeight="1">
       <c r="A50" s="10" t="n"/>
@@ -1512,14 +1716,18 @@
       <c r="F50" s="10" t="n"/>
       <c r="G50" s="12" t="n"/>
       <c r="H50" s="10" t="n"/>
-      <c r="I50" s="10" t="n"/>
+      <c r="I50" s="12" t="n"/>
       <c r="J50" s="12" t="n"/>
-      <c r="K50" s="10" t="n"/>
+      <c r="K50" s="13" t="n"/>
       <c r="L50" s="10" t="n"/>
-      <c r="M50" s="13" t="n"/>
-      <c r="N50" s="13" t="n"/>
-      <c r="O50" s="13" t="n"/>
-      <c r="P50" s="13" t="n"/>
+      <c r="M50" s="10" t="n"/>
+      <c r="N50" s="12" t="n"/>
+      <c r="O50" s="10" t="n"/>
+      <c r="P50" s="10" t="n"/>
+      <c r="Q50" s="13" t="n"/>
+      <c r="R50" s="13" t="n"/>
+      <c r="S50" s="13" t="n"/>
+      <c r="T50" s="13" t="n"/>
     </row>
     <row r="51" ht="23" customHeight="1">
       <c r="A51" s="6" t="n"/>
@@ -1530,14 +1738,18 @@
       <c r="F51" s="6" t="n"/>
       <c r="G51" s="8" t="n"/>
       <c r="H51" s="6" t="n"/>
-      <c r="I51" s="6" t="n"/>
+      <c r="I51" s="8" t="n"/>
       <c r="J51" s="8" t="n"/>
-      <c r="K51" s="6" t="n"/>
+      <c r="K51" s="9" t="n"/>
       <c r="L51" s="6" t="n"/>
-      <c r="M51" s="9" t="n"/>
-      <c r="N51" s="9" t="n"/>
-      <c r="O51" s="9" t="n"/>
-      <c r="P51" s="9" t="n"/>
+      <c r="M51" s="6" t="n"/>
+      <c r="N51" s="8" t="n"/>
+      <c r="O51" s="6" t="n"/>
+      <c r="P51" s="6" t="n"/>
+      <c r="Q51" s="9" t="n"/>
+      <c r="R51" s="9" t="n"/>
+      <c r="S51" s="9" t="n"/>
+      <c r="T51" s="9" t="n"/>
     </row>
     <row r="52" ht="23" customHeight="1">
       <c r="A52" s="10" t="n"/>
@@ -1548,14 +1760,18 @@
       <c r="F52" s="10" t="n"/>
       <c r="G52" s="12" t="n"/>
       <c r="H52" s="10" t="n"/>
-      <c r="I52" s="10" t="n"/>
+      <c r="I52" s="12" t="n"/>
       <c r="J52" s="12" t="n"/>
-      <c r="K52" s="10" t="n"/>
+      <c r="K52" s="13" t="n"/>
       <c r="L52" s="10" t="n"/>
-      <c r="M52" s="13" t="n"/>
-      <c r="N52" s="13" t="n"/>
-      <c r="O52" s="13" t="n"/>
-      <c r="P52" s="13" t="n"/>
+      <c r="M52" s="10" t="n"/>
+      <c r="N52" s="12" t="n"/>
+      <c r="O52" s="10" t="n"/>
+      <c r="P52" s="10" t="n"/>
+      <c r="Q52" s="13" t="n"/>
+      <c r="R52" s="13" t="n"/>
+      <c r="S52" s="13" t="n"/>
+      <c r="T52" s="13" t="n"/>
     </row>
     <row r="53" ht="23" customHeight="1">
       <c r="A53" s="6" t="n"/>
@@ -1566,14 +1782,18 @@
       <c r="F53" s="6" t="n"/>
       <c r="G53" s="8" t="n"/>
       <c r="H53" s="6" t="n"/>
-      <c r="I53" s="6" t="n"/>
+      <c r="I53" s="8" t="n"/>
       <c r="J53" s="8" t="n"/>
-      <c r="K53" s="6" t="n"/>
+      <c r="K53" s="9" t="n"/>
       <c r="L53" s="6" t="n"/>
-      <c r="M53" s="9" t="n"/>
-      <c r="N53" s="9" t="n"/>
-      <c r="O53" s="9" t="n"/>
-      <c r="P53" s="9" t="n"/>
+      <c r="M53" s="6" t="n"/>
+      <c r="N53" s="8" t="n"/>
+      <c r="O53" s="6" t="n"/>
+      <c r="P53" s="6" t="n"/>
+      <c r="Q53" s="9" t="n"/>
+      <c r="R53" s="9" t="n"/>
+      <c r="S53" s="9" t="n"/>
+      <c r="T53" s="9" t="n"/>
     </row>
     <row r="54" ht="23" customHeight="1">
       <c r="A54" s="10" t="n"/>
@@ -1584,14 +1804,18 @@
       <c r="F54" s="10" t="n"/>
       <c r="G54" s="12" t="n"/>
       <c r="H54" s="10" t="n"/>
-      <c r="I54" s="10" t="n"/>
+      <c r="I54" s="12" t="n"/>
       <c r="J54" s="12" t="n"/>
-      <c r="K54" s="10" t="n"/>
+      <c r="K54" s="13" t="n"/>
       <c r="L54" s="10" t="n"/>
-      <c r="M54" s="13" t="n"/>
-      <c r="N54" s="13" t="n"/>
-      <c r="O54" s="13" t="n"/>
-      <c r="P54" s="13" t="n"/>
+      <c r="M54" s="10" t="n"/>
+      <c r="N54" s="12" t="n"/>
+      <c r="O54" s="10" t="n"/>
+      <c r="P54" s="10" t="n"/>
+      <c r="Q54" s="13" t="n"/>
+      <c r="R54" s="13" t="n"/>
+      <c r="S54" s="13" t="n"/>
+      <c r="T54" s="13" t="n"/>
     </row>
     <row r="55" ht="23" customHeight="1">
       <c r="A55" s="6" t="n"/>
@@ -1602,14 +1826,18 @@
       <c r="F55" s="6" t="n"/>
       <c r="G55" s="8" t="n"/>
       <c r="H55" s="6" t="n"/>
-      <c r="I55" s="6" t="n"/>
+      <c r="I55" s="8" t="n"/>
       <c r="J55" s="8" t="n"/>
-      <c r="K55" s="6" t="n"/>
+      <c r="K55" s="9" t="n"/>
       <c r="L55" s="6" t="n"/>
-      <c r="M55" s="9" t="n"/>
-      <c r="N55" s="9" t="n"/>
-      <c r="O55" s="9" t="n"/>
-      <c r="P55" s="9" t="n"/>
+      <c r="M55" s="6" t="n"/>
+      <c r="N55" s="8" t="n"/>
+      <c r="O55" s="6" t="n"/>
+      <c r="P55" s="6" t="n"/>
+      <c r="Q55" s="9" t="n"/>
+      <c r="R55" s="9" t="n"/>
+      <c r="S55" s="9" t="n"/>
+      <c r="T55" s="9" t="n"/>
     </row>
     <row r="56" ht="23" customHeight="1">
       <c r="A56" s="10" t="n"/>
@@ -1620,14 +1848,18 @@
       <c r="F56" s="10" t="n"/>
       <c r="G56" s="12" t="n"/>
       <c r="H56" s="10" t="n"/>
-      <c r="I56" s="10" t="n"/>
+      <c r="I56" s="12" t="n"/>
       <c r="J56" s="12" t="n"/>
-      <c r="K56" s="10" t="n"/>
+      <c r="K56" s="13" t="n"/>
       <c r="L56" s="10" t="n"/>
-      <c r="M56" s="13" t="n"/>
-      <c r="N56" s="13" t="n"/>
-      <c r="O56" s="13" t="n"/>
-      <c r="P56" s="13" t="n"/>
+      <c r="M56" s="10" t="n"/>
+      <c r="N56" s="12" t="n"/>
+      <c r="O56" s="10" t="n"/>
+      <c r="P56" s="10" t="n"/>
+      <c r="Q56" s="13" t="n"/>
+      <c r="R56" s="13" t="n"/>
+      <c r="S56" s="13" t="n"/>
+      <c r="T56" s="13" t="n"/>
     </row>
     <row r="57" ht="23" customHeight="1">
       <c r="A57" s="6" t="n"/>
@@ -1638,14 +1870,18 @@
       <c r="F57" s="6" t="n"/>
       <c r="G57" s="8" t="n"/>
       <c r="H57" s="6" t="n"/>
-      <c r="I57" s="6" t="n"/>
+      <c r="I57" s="8" t="n"/>
       <c r="J57" s="8" t="n"/>
-      <c r="K57" s="6" t="n"/>
+      <c r="K57" s="9" t="n"/>
       <c r="L57" s="6" t="n"/>
-      <c r="M57" s="9" t="n"/>
-      <c r="N57" s="9" t="n"/>
-      <c r="O57" s="9" t="n"/>
-      <c r="P57" s="9" t="n"/>
+      <c r="M57" s="6" t="n"/>
+      <c r="N57" s="8" t="n"/>
+      <c r="O57" s="6" t="n"/>
+      <c r="P57" s="6" t="n"/>
+      <c r="Q57" s="9" t="n"/>
+      <c r="R57" s="9" t="n"/>
+      <c r="S57" s="9" t="n"/>
+      <c r="T57" s="9" t="n"/>
     </row>
     <row r="58" ht="23" customHeight="1">
       <c r="A58" s="10" t="n"/>
@@ -1656,14 +1892,18 @@
       <c r="F58" s="10" t="n"/>
       <c r="G58" s="12" t="n"/>
       <c r="H58" s="10" t="n"/>
-      <c r="I58" s="10" t="n"/>
+      <c r="I58" s="12" t="n"/>
       <c r="J58" s="12" t="n"/>
-      <c r="K58" s="10" t="n"/>
+      <c r="K58" s="13" t="n"/>
       <c r="L58" s="10" t="n"/>
-      <c r="M58" s="13" t="n"/>
-      <c r="N58" s="13" t="n"/>
-      <c r="O58" s="13" t="n"/>
-      <c r="P58" s="13" t="n"/>
+      <c r="M58" s="10" t="n"/>
+      <c r="N58" s="12" t="n"/>
+      <c r="O58" s="10" t="n"/>
+      <c r="P58" s="10" t="n"/>
+      <c r="Q58" s="13" t="n"/>
+      <c r="R58" s="13" t="n"/>
+      <c r="S58" s="13" t="n"/>
+      <c r="T58" s="13" t="n"/>
     </row>
     <row r="59" ht="23" customHeight="1">
       <c r="A59" s="6" t="n"/>
@@ -1674,14 +1914,18 @@
       <c r="F59" s="6" t="n"/>
       <c r="G59" s="8" t="n"/>
       <c r="H59" s="6" t="n"/>
-      <c r="I59" s="6" t="n"/>
+      <c r="I59" s="8" t="n"/>
       <c r="J59" s="8" t="n"/>
-      <c r="K59" s="6" t="n"/>
+      <c r="K59" s="9" t="n"/>
       <c r="L59" s="6" t="n"/>
-      <c r="M59" s="9" t="n"/>
-      <c r="N59" s="9" t="n"/>
-      <c r="O59" s="9" t="n"/>
-      <c r="P59" s="9" t="n"/>
+      <c r="M59" s="6" t="n"/>
+      <c r="N59" s="8" t="n"/>
+      <c r="O59" s="6" t="n"/>
+      <c r="P59" s="6" t="n"/>
+      <c r="Q59" s="9" t="n"/>
+      <c r="R59" s="9" t="n"/>
+      <c r="S59" s="9" t="n"/>
+      <c r="T59" s="9" t="n"/>
     </row>
     <row r="60" ht="23" customHeight="1">
       <c r="A60" s="10" t="n"/>
@@ -1692,14 +1936,18 @@
       <c r="F60" s="10" t="n"/>
       <c r="G60" s="12" t="n"/>
       <c r="H60" s="10" t="n"/>
-      <c r="I60" s="10" t="n"/>
+      <c r="I60" s="12" t="n"/>
       <c r="J60" s="12" t="n"/>
-      <c r="K60" s="10" t="n"/>
+      <c r="K60" s="13" t="n"/>
       <c r="L60" s="10" t="n"/>
-      <c r="M60" s="13" t="n"/>
-      <c r="N60" s="13" t="n"/>
-      <c r="O60" s="13" t="n"/>
-      <c r="P60" s="13" t="n"/>
+      <c r="M60" s="10" t="n"/>
+      <c r="N60" s="12" t="n"/>
+      <c r="O60" s="10" t="n"/>
+      <c r="P60" s="10" t="n"/>
+      <c r="Q60" s="13" t="n"/>
+      <c r="R60" s="13" t="n"/>
+      <c r="S60" s="13" t="n"/>
+      <c r="T60" s="13" t="n"/>
     </row>
     <row r="61" ht="23" customHeight="1">
       <c r="A61" s="6" t="n"/>
@@ -1710,14 +1958,18 @@
       <c r="F61" s="6" t="n"/>
       <c r="G61" s="8" t="n"/>
       <c r="H61" s="6" t="n"/>
-      <c r="I61" s="6" t="n"/>
+      <c r="I61" s="8" t="n"/>
       <c r="J61" s="8" t="n"/>
-      <c r="K61" s="6" t="n"/>
+      <c r="K61" s="9" t="n"/>
       <c r="L61" s="6" t="n"/>
-      <c r="M61" s="9" t="n"/>
-      <c r="N61" s="9" t="n"/>
-      <c r="O61" s="9" t="n"/>
-      <c r="P61" s="9" t="n"/>
+      <c r="M61" s="6" t="n"/>
+      <c r="N61" s="8" t="n"/>
+      <c r="O61" s="6" t="n"/>
+      <c r="P61" s="6" t="n"/>
+      <c r="Q61" s="9" t="n"/>
+      <c r="R61" s="9" t="n"/>
+      <c r="S61" s="9" t="n"/>
+      <c r="T61" s="9" t="n"/>
     </row>
     <row r="62" ht="23" customHeight="1">
       <c r="A62" s="10" t="n"/>
@@ -1728,14 +1980,18 @@
       <c r="F62" s="10" t="n"/>
       <c r="G62" s="12" t="n"/>
       <c r="H62" s="10" t="n"/>
-      <c r="I62" s="10" t="n"/>
+      <c r="I62" s="12" t="n"/>
       <c r="J62" s="12" t="n"/>
-      <c r="K62" s="10" t="n"/>
+      <c r="K62" s="13" t="n"/>
       <c r="L62" s="10" t="n"/>
-      <c r="M62" s="13" t="n"/>
-      <c r="N62" s="13" t="n"/>
-      <c r="O62" s="13" t="n"/>
-      <c r="P62" s="13" t="n"/>
+      <c r="M62" s="10" t="n"/>
+      <c r="N62" s="12" t="n"/>
+      <c r="O62" s="10" t="n"/>
+      <c r="P62" s="10" t="n"/>
+      <c r="Q62" s="13" t="n"/>
+      <c r="R62" s="13" t="n"/>
+      <c r="S62" s="13" t="n"/>
+      <c r="T62" s="13" t="n"/>
     </row>
     <row r="63" ht="23" customHeight="1">
       <c r="A63" s="6" t="n"/>
@@ -1746,14 +2002,18 @@
       <c r="F63" s="6" t="n"/>
       <c r="G63" s="8" t="n"/>
       <c r="H63" s="6" t="n"/>
-      <c r="I63" s="6" t="n"/>
+      <c r="I63" s="8" t="n"/>
       <c r="J63" s="8" t="n"/>
-      <c r="K63" s="6" t="n"/>
+      <c r="K63" s="9" t="n"/>
       <c r="L63" s="6" t="n"/>
-      <c r="M63" s="9" t="n"/>
-      <c r="N63" s="9" t="n"/>
-      <c r="O63" s="9" t="n"/>
-      <c r="P63" s="9" t="n"/>
+      <c r="M63" s="6" t="n"/>
+      <c r="N63" s="8" t="n"/>
+      <c r="O63" s="6" t="n"/>
+      <c r="P63" s="6" t="n"/>
+      <c r="Q63" s="9" t="n"/>
+      <c r="R63" s="9" t="n"/>
+      <c r="S63" s="9" t="n"/>
+      <c r="T63" s="9" t="n"/>
     </row>
     <row r="64" ht="23" customHeight="1">
       <c r="A64" s="10" t="n"/>
@@ -1764,14 +2024,18 @@
       <c r="F64" s="10" t="n"/>
       <c r="G64" s="12" t="n"/>
       <c r="H64" s="10" t="n"/>
-      <c r="I64" s="10" t="n"/>
+      <c r="I64" s="12" t="n"/>
       <c r="J64" s="12" t="n"/>
-      <c r="K64" s="10" t="n"/>
+      <c r="K64" s="13" t="n"/>
       <c r="L64" s="10" t="n"/>
-      <c r="M64" s="13" t="n"/>
-      <c r="N64" s="13" t="n"/>
-      <c r="O64" s="13" t="n"/>
-      <c r="P64" s="13" t="n"/>
+      <c r="M64" s="10" t="n"/>
+      <c r="N64" s="12" t="n"/>
+      <c r="O64" s="10" t="n"/>
+      <c r="P64" s="10" t="n"/>
+      <c r="Q64" s="13" t="n"/>
+      <c r="R64" s="13" t="n"/>
+      <c r="S64" s="13" t="n"/>
+      <c r="T64" s="13" t="n"/>
     </row>
     <row r="65" ht="23" customHeight="1">
       <c r="A65" s="6" t="n"/>
@@ -1782,14 +2046,18 @@
       <c r="F65" s="6" t="n"/>
       <c r="G65" s="8" t="n"/>
       <c r="H65" s="6" t="n"/>
-      <c r="I65" s="6" t="n"/>
+      <c r="I65" s="8" t="n"/>
       <c r="J65" s="8" t="n"/>
-      <c r="K65" s="6" t="n"/>
+      <c r="K65" s="9" t="n"/>
       <c r="L65" s="6" t="n"/>
-      <c r="M65" s="9" t="n"/>
-      <c r="N65" s="9" t="n"/>
-      <c r="O65" s="9" t="n"/>
-      <c r="P65" s="9" t="n"/>
+      <c r="M65" s="6" t="n"/>
+      <c r="N65" s="8" t="n"/>
+      <c r="O65" s="6" t="n"/>
+      <c r="P65" s="6" t="n"/>
+      <c r="Q65" s="9" t="n"/>
+      <c r="R65" s="9" t="n"/>
+      <c r="S65" s="9" t="n"/>
+      <c r="T65" s="9" t="n"/>
     </row>
     <row r="66" ht="23" customHeight="1">
       <c r="A66" s="10" t="n"/>
@@ -1800,14 +2068,18 @@
       <c r="F66" s="10" t="n"/>
       <c r="G66" s="12" t="n"/>
       <c r="H66" s="10" t="n"/>
-      <c r="I66" s="10" t="n"/>
+      <c r="I66" s="12" t="n"/>
       <c r="J66" s="12" t="n"/>
-      <c r="K66" s="10" t="n"/>
+      <c r="K66" s="13" t="n"/>
       <c r="L66" s="10" t="n"/>
-      <c r="M66" s="13" t="n"/>
-      <c r="N66" s="13" t="n"/>
-      <c r="O66" s="13" t="n"/>
-      <c r="P66" s="13" t="n"/>
+      <c r="M66" s="10" t="n"/>
+      <c r="N66" s="12" t="n"/>
+      <c r="O66" s="10" t="n"/>
+      <c r="P66" s="10" t="n"/>
+      <c r="Q66" s="13" t="n"/>
+      <c r="R66" s="13" t="n"/>
+      <c r="S66" s="13" t="n"/>
+      <c r="T66" s="13" t="n"/>
     </row>
     <row r="67" ht="23" customHeight="1">
       <c r="A67" s="6" t="n"/>
@@ -1818,14 +2090,18 @@
       <c r="F67" s="6" t="n"/>
       <c r="G67" s="8" t="n"/>
       <c r="H67" s="6" t="n"/>
-      <c r="I67" s="6" t="n"/>
+      <c r="I67" s="8" t="n"/>
       <c r="J67" s="8" t="n"/>
-      <c r="K67" s="6" t="n"/>
+      <c r="K67" s="9" t="n"/>
       <c r="L67" s="6" t="n"/>
-      <c r="M67" s="9" t="n"/>
-      <c r="N67" s="9" t="n"/>
-      <c r="O67" s="9" t="n"/>
-      <c r="P67" s="9" t="n"/>
+      <c r="M67" s="6" t="n"/>
+      <c r="N67" s="8" t="n"/>
+      <c r="O67" s="6" t="n"/>
+      <c r="P67" s="6" t="n"/>
+      <c r="Q67" s="9" t="n"/>
+      <c r="R67" s="9" t="n"/>
+      <c r="S67" s="9" t="n"/>
+      <c r="T67" s="9" t="n"/>
     </row>
     <row r="68" ht="23" customHeight="1">
       <c r="A68" s="10" t="n"/>
@@ -1836,14 +2112,18 @@
       <c r="F68" s="10" t="n"/>
       <c r="G68" s="12" t="n"/>
       <c r="H68" s="10" t="n"/>
-      <c r="I68" s="10" t="n"/>
+      <c r="I68" s="12" t="n"/>
       <c r="J68" s="12" t="n"/>
-      <c r="K68" s="10" t="n"/>
+      <c r="K68" s="13" t="n"/>
       <c r="L68" s="10" t="n"/>
-      <c r="M68" s="13" t="n"/>
-      <c r="N68" s="13" t="n"/>
-      <c r="O68" s="13" t="n"/>
-      <c r="P68" s="13" t="n"/>
+      <c r="M68" s="10" t="n"/>
+      <c r="N68" s="12" t="n"/>
+      <c r="O68" s="10" t="n"/>
+      <c r="P68" s="10" t="n"/>
+      <c r="Q68" s="13" t="n"/>
+      <c r="R68" s="13" t="n"/>
+      <c r="S68" s="13" t="n"/>
+      <c r="T68" s="13" t="n"/>
     </row>
     <row r="69" ht="23" customHeight="1">
       <c r="A69" s="6" t="n"/>
@@ -1854,14 +2134,18 @@
       <c r="F69" s="6" t="n"/>
       <c r="G69" s="8" t="n"/>
       <c r="H69" s="6" t="n"/>
-      <c r="I69" s="6" t="n"/>
+      <c r="I69" s="8" t="n"/>
       <c r="J69" s="8" t="n"/>
-      <c r="K69" s="6" t="n"/>
+      <c r="K69" s="9" t="n"/>
       <c r="L69" s="6" t="n"/>
-      <c r="M69" s="9" t="n"/>
-      <c r="N69" s="9" t="n"/>
-      <c r="O69" s="9" t="n"/>
-      <c r="P69" s="9" t="n"/>
+      <c r="M69" s="6" t="n"/>
+      <c r="N69" s="8" t="n"/>
+      <c r="O69" s="6" t="n"/>
+      <c r="P69" s="6" t="n"/>
+      <c r="Q69" s="9" t="n"/>
+      <c r="R69" s="9" t="n"/>
+      <c r="S69" s="9" t="n"/>
+      <c r="T69" s="9" t="n"/>
     </row>
     <row r="70" ht="23" customHeight="1">
       <c r="A70" s="10" t="n"/>
@@ -1872,14 +2156,18 @@
       <c r="F70" s="10" t="n"/>
       <c r="G70" s="12" t="n"/>
       <c r="H70" s="10" t="n"/>
-      <c r="I70" s="10" t="n"/>
+      <c r="I70" s="12" t="n"/>
       <c r="J70" s="12" t="n"/>
-      <c r="K70" s="10" t="n"/>
+      <c r="K70" s="13" t="n"/>
       <c r="L70" s="10" t="n"/>
-      <c r="M70" s="13" t="n"/>
-      <c r="N70" s="13" t="n"/>
-      <c r="O70" s="13" t="n"/>
-      <c r="P70" s="13" t="n"/>
+      <c r="M70" s="10" t="n"/>
+      <c r="N70" s="12" t="n"/>
+      <c r="O70" s="10" t="n"/>
+      <c r="P70" s="10" t="n"/>
+      <c r="Q70" s="13" t="n"/>
+      <c r="R70" s="13" t="n"/>
+      <c r="S70" s="13" t="n"/>
+      <c r="T70" s="13" t="n"/>
     </row>
     <row r="71" ht="23" customHeight="1">
       <c r="A71" s="6" t="n"/>
@@ -1890,14 +2178,18 @@
       <c r="F71" s="6" t="n"/>
       <c r="G71" s="8" t="n"/>
       <c r="H71" s="6" t="n"/>
-      <c r="I71" s="6" t="n"/>
+      <c r="I71" s="8" t="n"/>
       <c r="J71" s="8" t="n"/>
-      <c r="K71" s="6" t="n"/>
+      <c r="K71" s="9" t="n"/>
       <c r="L71" s="6" t="n"/>
-      <c r="M71" s="9" t="n"/>
-      <c r="N71" s="9" t="n"/>
-      <c r="O71" s="9" t="n"/>
-      <c r="P71" s="9" t="n"/>
+      <c r="M71" s="6" t="n"/>
+      <c r="N71" s="8" t="n"/>
+      <c r="O71" s="6" t="n"/>
+      <c r="P71" s="6" t="n"/>
+      <c r="Q71" s="9" t="n"/>
+      <c r="R71" s="9" t="n"/>
+      <c r="S71" s="9" t="n"/>
+      <c r="T71" s="9" t="n"/>
     </row>
     <row r="72" ht="23" customHeight="1">
       <c r="A72" s="10" t="n"/>
@@ -1908,14 +2200,18 @@
       <c r="F72" s="10" t="n"/>
       <c r="G72" s="12" t="n"/>
       <c r="H72" s="10" t="n"/>
-      <c r="I72" s="10" t="n"/>
+      <c r="I72" s="12" t="n"/>
       <c r="J72" s="12" t="n"/>
-      <c r="K72" s="10" t="n"/>
+      <c r="K72" s="13" t="n"/>
       <c r="L72" s="10" t="n"/>
-      <c r="M72" s="13" t="n"/>
-      <c r="N72" s="13" t="n"/>
-      <c r="O72" s="13" t="n"/>
-      <c r="P72" s="13" t="n"/>
+      <c r="M72" s="10" t="n"/>
+      <c r="N72" s="12" t="n"/>
+      <c r="O72" s="10" t="n"/>
+      <c r="P72" s="10" t="n"/>
+      <c r="Q72" s="13" t="n"/>
+      <c r="R72" s="13" t="n"/>
+      <c r="S72" s="13" t="n"/>
+      <c r="T72" s="13" t="n"/>
     </row>
     <row r="73" ht="23" customHeight="1">
       <c r="A73" s="6" t="n"/>
@@ -1926,14 +2222,18 @@
       <c r="F73" s="6" t="n"/>
       <c r="G73" s="8" t="n"/>
       <c r="H73" s="6" t="n"/>
-      <c r="I73" s="6" t="n"/>
+      <c r="I73" s="8" t="n"/>
       <c r="J73" s="8" t="n"/>
-      <c r="K73" s="6" t="n"/>
+      <c r="K73" s="9" t="n"/>
       <c r="L73" s="6" t="n"/>
-      <c r="M73" s="9" t="n"/>
-      <c r="N73" s="9" t="n"/>
-      <c r="O73" s="9" t="n"/>
-      <c r="P73" s="9" t="n"/>
+      <c r="M73" s="6" t="n"/>
+      <c r="N73" s="8" t="n"/>
+      <c r="O73" s="6" t="n"/>
+      <c r="P73" s="6" t="n"/>
+      <c r="Q73" s="9" t="n"/>
+      <c r="R73" s="9" t="n"/>
+      <c r="S73" s="9" t="n"/>
+      <c r="T73" s="9" t="n"/>
     </row>
     <row r="74" ht="23" customHeight="1">
       <c r="A74" s="10" t="n"/>
@@ -1944,14 +2244,18 @@
       <c r="F74" s="10" t="n"/>
       <c r="G74" s="12" t="n"/>
       <c r="H74" s="10" t="n"/>
-      <c r="I74" s="10" t="n"/>
+      <c r="I74" s="12" t="n"/>
       <c r="J74" s="12" t="n"/>
-      <c r="K74" s="10" t="n"/>
+      <c r="K74" s="13" t="n"/>
       <c r="L74" s="10" t="n"/>
-      <c r="M74" s="13" t="n"/>
-      <c r="N74" s="13" t="n"/>
-      <c r="O74" s="13" t="n"/>
-      <c r="P74" s="13" t="n"/>
+      <c r="M74" s="10" t="n"/>
+      <c r="N74" s="12" t="n"/>
+      <c r="O74" s="10" t="n"/>
+      <c r="P74" s="10" t="n"/>
+      <c r="Q74" s="13" t="n"/>
+      <c r="R74" s="13" t="n"/>
+      <c r="S74" s="13" t="n"/>
+      <c r="T74" s="13" t="n"/>
     </row>
     <row r="75" ht="23" customHeight="1">
       <c r="A75" s="6" t="n"/>
@@ -1962,14 +2266,18 @@
       <c r="F75" s="6" t="n"/>
       <c r="G75" s="8" t="n"/>
       <c r="H75" s="6" t="n"/>
-      <c r="I75" s="6" t="n"/>
+      <c r="I75" s="8" t="n"/>
       <c r="J75" s="8" t="n"/>
-      <c r="K75" s="6" t="n"/>
+      <c r="K75" s="9" t="n"/>
       <c r="L75" s="6" t="n"/>
-      <c r="M75" s="9" t="n"/>
-      <c r="N75" s="9" t="n"/>
-      <c r="O75" s="9" t="n"/>
-      <c r="P75" s="9" t="n"/>
+      <c r="M75" s="6" t="n"/>
+      <c r="N75" s="8" t="n"/>
+      <c r="O75" s="6" t="n"/>
+      <c r="P75" s="6" t="n"/>
+      <c r="Q75" s="9" t="n"/>
+      <c r="R75" s="9" t="n"/>
+      <c r="S75" s="9" t="n"/>
+      <c r="T75" s="9" t="n"/>
     </row>
     <row r="76" ht="23" customHeight="1">
       <c r="A76" s="10" t="n"/>
@@ -1980,14 +2288,18 @@
       <c r="F76" s="10" t="n"/>
       <c r="G76" s="12" t="n"/>
       <c r="H76" s="10" t="n"/>
-      <c r="I76" s="10" t="n"/>
+      <c r="I76" s="12" t="n"/>
       <c r="J76" s="12" t="n"/>
-      <c r="K76" s="10" t="n"/>
+      <c r="K76" s="13" t="n"/>
       <c r="L76" s="10" t="n"/>
-      <c r="M76" s="13" t="n"/>
-      <c r="N76" s="13" t="n"/>
-      <c r="O76" s="13" t="n"/>
-      <c r="P76" s="13" t="n"/>
+      <c r="M76" s="10" t="n"/>
+      <c r="N76" s="12" t="n"/>
+      <c r="O76" s="10" t="n"/>
+      <c r="P76" s="10" t="n"/>
+      <c r="Q76" s="13" t="n"/>
+      <c r="R76" s="13" t="n"/>
+      <c r="S76" s="13" t="n"/>
+      <c r="T76" s="13" t="n"/>
     </row>
     <row r="77" ht="23" customHeight="1">
       <c r="A77" s="6" t="n"/>
@@ -1998,14 +2310,18 @@
       <c r="F77" s="6" t="n"/>
       <c r="G77" s="8" t="n"/>
       <c r="H77" s="6" t="n"/>
-      <c r="I77" s="6" t="n"/>
+      <c r="I77" s="8" t="n"/>
       <c r="J77" s="8" t="n"/>
-      <c r="K77" s="6" t="n"/>
+      <c r="K77" s="9" t="n"/>
       <c r="L77" s="6" t="n"/>
-      <c r="M77" s="9" t="n"/>
-      <c r="N77" s="9" t="n"/>
-      <c r="O77" s="9" t="n"/>
-      <c r="P77" s="9" t="n"/>
+      <c r="M77" s="6" t="n"/>
+      <c r="N77" s="8" t="n"/>
+      <c r="O77" s="6" t="n"/>
+      <c r="P77" s="6" t="n"/>
+      <c r="Q77" s="9" t="n"/>
+      <c r="R77" s="9" t="n"/>
+      <c r="S77" s="9" t="n"/>
+      <c r="T77" s="9" t="n"/>
     </row>
     <row r="78" ht="23" customHeight="1">
       <c r="A78" s="10" t="n"/>
@@ -2016,14 +2332,18 @@
       <c r="F78" s="10" t="n"/>
       <c r="G78" s="12" t="n"/>
       <c r="H78" s="10" t="n"/>
-      <c r="I78" s="10" t="n"/>
+      <c r="I78" s="12" t="n"/>
       <c r="J78" s="12" t="n"/>
-      <c r="K78" s="10" t="n"/>
+      <c r="K78" s="13" t="n"/>
       <c r="L78" s="10" t="n"/>
-      <c r="M78" s="13" t="n"/>
-      <c r="N78" s="13" t="n"/>
-      <c r="O78" s="13" t="n"/>
-      <c r="P78" s="13" t="n"/>
+      <c r="M78" s="10" t="n"/>
+      <c r="N78" s="12" t="n"/>
+      <c r="O78" s="10" t="n"/>
+      <c r="P78" s="10" t="n"/>
+      <c r="Q78" s="13" t="n"/>
+      <c r="R78" s="13" t="n"/>
+      <c r="S78" s="13" t="n"/>
+      <c r="T78" s="13" t="n"/>
     </row>
     <row r="79" ht="23" customHeight="1">
       <c r="A79" s="6" t="n"/>
@@ -2034,14 +2354,18 @@
       <c r="F79" s="6" t="n"/>
       <c r="G79" s="8" t="n"/>
       <c r="H79" s="6" t="n"/>
-      <c r="I79" s="6" t="n"/>
+      <c r="I79" s="8" t="n"/>
       <c r="J79" s="8" t="n"/>
-      <c r="K79" s="6" t="n"/>
+      <c r="K79" s="9" t="n"/>
       <c r="L79" s="6" t="n"/>
-      <c r="M79" s="9" t="n"/>
-      <c r="N79" s="9" t="n"/>
-      <c r="O79" s="9" t="n"/>
-      <c r="P79" s="9" t="n"/>
+      <c r="M79" s="6" t="n"/>
+      <c r="N79" s="8" t="n"/>
+      <c r="O79" s="6" t="n"/>
+      <c r="P79" s="6" t="n"/>
+      <c r="Q79" s="9" t="n"/>
+      <c r="R79" s="9" t="n"/>
+      <c r="S79" s="9" t="n"/>
+      <c r="T79" s="9" t="n"/>
     </row>
     <row r="80" ht="23" customHeight="1">
       <c r="A80" s="10" t="n"/>
@@ -2052,14 +2376,18 @@
       <c r="F80" s="10" t="n"/>
       <c r="G80" s="12" t="n"/>
       <c r="H80" s="10" t="n"/>
-      <c r="I80" s="10" t="n"/>
+      <c r="I80" s="12" t="n"/>
       <c r="J80" s="12" t="n"/>
-      <c r="K80" s="10" t="n"/>
+      <c r="K80" s="13" t="n"/>
       <c r="L80" s="10" t="n"/>
-      <c r="M80" s="13" t="n"/>
-      <c r="N80" s="13" t="n"/>
-      <c r="O80" s="13" t="n"/>
-      <c r="P80" s="13" t="n"/>
+      <c r="M80" s="10" t="n"/>
+      <c r="N80" s="12" t="n"/>
+      <c r="O80" s="10" t="n"/>
+      <c r="P80" s="10" t="n"/>
+      <c r="Q80" s="13" t="n"/>
+      <c r="R80" s="13" t="n"/>
+      <c r="S80" s="13" t="n"/>
+      <c r="T80" s="13" t="n"/>
     </row>
     <row r="81" ht="23" customHeight="1">
       <c r="A81" s="6" t="n"/>
@@ -2070,14 +2398,18 @@
       <c r="F81" s="6" t="n"/>
       <c r="G81" s="8" t="n"/>
       <c r="H81" s="6" t="n"/>
-      <c r="I81" s="6" t="n"/>
+      <c r="I81" s="8" t="n"/>
       <c r="J81" s="8" t="n"/>
-      <c r="K81" s="6" t="n"/>
+      <c r="K81" s="9" t="n"/>
       <c r="L81" s="6" t="n"/>
-      <c r="M81" s="9" t="n"/>
-      <c r="N81" s="9" t="n"/>
-      <c r="O81" s="9" t="n"/>
-      <c r="P81" s="9" t="n"/>
+      <c r="M81" s="6" t="n"/>
+      <c r="N81" s="8" t="n"/>
+      <c r="O81" s="6" t="n"/>
+      <c r="P81" s="6" t="n"/>
+      <c r="Q81" s="9" t="n"/>
+      <c r="R81" s="9" t="n"/>
+      <c r="S81" s="9" t="n"/>
+      <c r="T81" s="9" t="n"/>
     </row>
     <row r="82" ht="23" customHeight="1">
       <c r="A82" s="10" t="n"/>
@@ -2088,14 +2420,18 @@
       <c r="F82" s="10" t="n"/>
       <c r="G82" s="12" t="n"/>
       <c r="H82" s="10" t="n"/>
-      <c r="I82" s="10" t="n"/>
+      <c r="I82" s="12" t="n"/>
       <c r="J82" s="12" t="n"/>
-      <c r="K82" s="10" t="n"/>
+      <c r="K82" s="13" t="n"/>
       <c r="L82" s="10" t="n"/>
-      <c r="M82" s="13" t="n"/>
-      <c r="N82" s="13" t="n"/>
-      <c r="O82" s="13" t="n"/>
-      <c r="P82" s="13" t="n"/>
+      <c r="M82" s="10" t="n"/>
+      <c r="N82" s="12" t="n"/>
+      <c r="O82" s="10" t="n"/>
+      <c r="P82" s="10" t="n"/>
+      <c r="Q82" s="13" t="n"/>
+      <c r="R82" s="13" t="n"/>
+      <c r="S82" s="13" t="n"/>
+      <c r="T82" s="13" t="n"/>
     </row>
     <row r="83" ht="23" customHeight="1">
       <c r="A83" s="6" t="n"/>
@@ -2106,14 +2442,18 @@
       <c r="F83" s="6" t="n"/>
       <c r="G83" s="8" t="n"/>
       <c r="H83" s="6" t="n"/>
-      <c r="I83" s="6" t="n"/>
+      <c r="I83" s="8" t="n"/>
       <c r="J83" s="8" t="n"/>
-      <c r="K83" s="6" t="n"/>
+      <c r="K83" s="9" t="n"/>
       <c r="L83" s="6" t="n"/>
-      <c r="M83" s="9" t="n"/>
-      <c r="N83" s="9" t="n"/>
-      <c r="O83" s="9" t="n"/>
-      <c r="P83" s="9" t="n"/>
+      <c r="M83" s="6" t="n"/>
+      <c r="N83" s="8" t="n"/>
+      <c r="O83" s="6" t="n"/>
+      <c r="P83" s="6" t="n"/>
+      <c r="Q83" s="9" t="n"/>
+      <c r="R83" s="9" t="n"/>
+      <c r="S83" s="9" t="n"/>
+      <c r="T83" s="9" t="n"/>
     </row>
     <row r="84" ht="23" customHeight="1">
       <c r="A84" s="10" t="n"/>
@@ -2124,14 +2464,18 @@
       <c r="F84" s="10" t="n"/>
       <c r="G84" s="12" t="n"/>
       <c r="H84" s="10" t="n"/>
-      <c r="I84" s="10" t="n"/>
+      <c r="I84" s="12" t="n"/>
       <c r="J84" s="12" t="n"/>
-      <c r="K84" s="10" t="n"/>
+      <c r="K84" s="13" t="n"/>
       <c r="L84" s="10" t="n"/>
-      <c r="M84" s="13" t="n"/>
-      <c r="N84" s="13" t="n"/>
-      <c r="O84" s="13" t="n"/>
-      <c r="P84" s="13" t="n"/>
+      <c r="M84" s="10" t="n"/>
+      <c r="N84" s="12" t="n"/>
+      <c r="O84" s="10" t="n"/>
+      <c r="P84" s="10" t="n"/>
+      <c r="Q84" s="13" t="n"/>
+      <c r="R84" s="13" t="n"/>
+      <c r="S84" s="13" t="n"/>
+      <c r="T84" s="13" t="n"/>
     </row>
     <row r="85" ht="23" customHeight="1">
       <c r="A85" s="6" t="n"/>
@@ -2142,14 +2486,18 @@
       <c r="F85" s="6" t="n"/>
       <c r="G85" s="8" t="n"/>
       <c r="H85" s="6" t="n"/>
-      <c r="I85" s="6" t="n"/>
+      <c r="I85" s="8" t="n"/>
       <c r="J85" s="8" t="n"/>
-      <c r="K85" s="6" t="n"/>
+      <c r="K85" s="9" t="n"/>
       <c r="L85" s="6" t="n"/>
-      <c r="M85" s="9" t="n"/>
-      <c r="N85" s="9" t="n"/>
-      <c r="O85" s="9" t="n"/>
-      <c r="P85" s="9" t="n"/>
+      <c r="M85" s="6" t="n"/>
+      <c r="N85" s="8" t="n"/>
+      <c r="O85" s="6" t="n"/>
+      <c r="P85" s="6" t="n"/>
+      <c r="Q85" s="9" t="n"/>
+      <c r="R85" s="9" t="n"/>
+      <c r="S85" s="9" t="n"/>
+      <c r="T85" s="9" t="n"/>
     </row>
     <row r="86" ht="23" customHeight="1">
       <c r="A86" s="10" t="n"/>
@@ -2160,14 +2508,18 @@
       <c r="F86" s="10" t="n"/>
       <c r="G86" s="12" t="n"/>
       <c r="H86" s="10" t="n"/>
-      <c r="I86" s="10" t="n"/>
+      <c r="I86" s="12" t="n"/>
       <c r="J86" s="12" t="n"/>
-      <c r="K86" s="10" t="n"/>
+      <c r="K86" s="13" t="n"/>
       <c r="L86" s="10" t="n"/>
-      <c r="M86" s="13" t="n"/>
-      <c r="N86" s="13" t="n"/>
-      <c r="O86" s="13" t="n"/>
-      <c r="P86" s="13" t="n"/>
+      <c r="M86" s="10" t="n"/>
+      <c r="N86" s="12" t="n"/>
+      <c r="O86" s="10" t="n"/>
+      <c r="P86" s="10" t="n"/>
+      <c r="Q86" s="13" t="n"/>
+      <c r="R86" s="13" t="n"/>
+      <c r="S86" s="13" t="n"/>
+      <c r="T86" s="13" t="n"/>
     </row>
     <row r="87" ht="23" customHeight="1">
       <c r="A87" s="6" t="n"/>
@@ -2178,14 +2530,18 @@
       <c r="F87" s="6" t="n"/>
       <c r="G87" s="8" t="n"/>
       <c r="H87" s="6" t="n"/>
-      <c r="I87" s="6" t="n"/>
+      <c r="I87" s="8" t="n"/>
       <c r="J87" s="8" t="n"/>
-      <c r="K87" s="6" t="n"/>
+      <c r="K87" s="9" t="n"/>
       <c r="L87" s="6" t="n"/>
-      <c r="M87" s="9" t="n"/>
-      <c r="N87" s="9" t="n"/>
-      <c r="O87" s="9" t="n"/>
-      <c r="P87" s="9" t="n"/>
+      <c r="M87" s="6" t="n"/>
+      <c r="N87" s="8" t="n"/>
+      <c r="O87" s="6" t="n"/>
+      <c r="P87" s="6" t="n"/>
+      <c r="Q87" s="9" t="n"/>
+      <c r="R87" s="9" t="n"/>
+      <c r="S87" s="9" t="n"/>
+      <c r="T87" s="9" t="n"/>
     </row>
     <row r="88" ht="23" customHeight="1">
       <c r="A88" s="10" t="n"/>
@@ -2196,14 +2552,18 @@
       <c r="F88" s="10" t="n"/>
       <c r="G88" s="12" t="n"/>
       <c r="H88" s="10" t="n"/>
-      <c r="I88" s="10" t="n"/>
+      <c r="I88" s="12" t="n"/>
       <c r="J88" s="12" t="n"/>
-      <c r="K88" s="10" t="n"/>
+      <c r="K88" s="13" t="n"/>
       <c r="L88" s="10" t="n"/>
-      <c r="M88" s="13" t="n"/>
-      <c r="N88" s="13" t="n"/>
-      <c r="O88" s="13" t="n"/>
-      <c r="P88" s="13" t="n"/>
+      <c r="M88" s="10" t="n"/>
+      <c r="N88" s="12" t="n"/>
+      <c r="O88" s="10" t="n"/>
+      <c r="P88" s="10" t="n"/>
+      <c r="Q88" s="13" t="n"/>
+      <c r="R88" s="13" t="n"/>
+      <c r="S88" s="13" t="n"/>
+      <c r="T88" s="13" t="n"/>
     </row>
     <row r="89" ht="23" customHeight="1">
       <c r="A89" s="6" t="n"/>
@@ -2214,14 +2574,18 @@
       <c r="F89" s="6" t="n"/>
       <c r="G89" s="8" t="n"/>
       <c r="H89" s="6" t="n"/>
-      <c r="I89" s="6" t="n"/>
+      <c r="I89" s="8" t="n"/>
       <c r="J89" s="8" t="n"/>
-      <c r="K89" s="6" t="n"/>
+      <c r="K89" s="9" t="n"/>
       <c r="L89" s="6" t="n"/>
-      <c r="M89" s="9" t="n"/>
-      <c r="N89" s="9" t="n"/>
-      <c r="O89" s="9" t="n"/>
-      <c r="P89" s="9" t="n"/>
+      <c r="M89" s="6" t="n"/>
+      <c r="N89" s="8" t="n"/>
+      <c r="O89" s="6" t="n"/>
+      <c r="P89" s="6" t="n"/>
+      <c r="Q89" s="9" t="n"/>
+      <c r="R89" s="9" t="n"/>
+      <c r="S89" s="9" t="n"/>
+      <c r="T89" s="9" t="n"/>
     </row>
     <row r="90" ht="23" customHeight="1">
       <c r="A90" s="10" t="n"/>
@@ -2232,14 +2596,18 @@
       <c r="F90" s="10" t="n"/>
       <c r="G90" s="12" t="n"/>
       <c r="H90" s="10" t="n"/>
-      <c r="I90" s="10" t="n"/>
+      <c r="I90" s="12" t="n"/>
       <c r="J90" s="12" t="n"/>
-      <c r="K90" s="10" t="n"/>
+      <c r="K90" s="13" t="n"/>
       <c r="L90" s="10" t="n"/>
-      <c r="M90" s="13" t="n"/>
-      <c r="N90" s="13" t="n"/>
-      <c r="O90" s="13" t="n"/>
-      <c r="P90" s="13" t="n"/>
+      <c r="M90" s="10" t="n"/>
+      <c r="N90" s="12" t="n"/>
+      <c r="O90" s="10" t="n"/>
+      <c r="P90" s="10" t="n"/>
+      <c r="Q90" s="13" t="n"/>
+      <c r="R90" s="13" t="n"/>
+      <c r="S90" s="13" t="n"/>
+      <c r="T90" s="13" t="n"/>
     </row>
     <row r="91" ht="23" customHeight="1">
       <c r="A91" s="6" t="n"/>
@@ -2250,14 +2618,18 @@
       <c r="F91" s="6" t="n"/>
       <c r="G91" s="8" t="n"/>
       <c r="H91" s="6" t="n"/>
-      <c r="I91" s="6" t="n"/>
+      <c r="I91" s="8" t="n"/>
       <c r="J91" s="8" t="n"/>
-      <c r="K91" s="6" t="n"/>
+      <c r="K91" s="9" t="n"/>
       <c r="L91" s="6" t="n"/>
-      <c r="M91" s="9" t="n"/>
-      <c r="N91" s="9" t="n"/>
-      <c r="O91" s="9" t="n"/>
-      <c r="P91" s="9" t="n"/>
+      <c r="M91" s="6" t="n"/>
+      <c r="N91" s="8" t="n"/>
+      <c r="O91" s="6" t="n"/>
+      <c r="P91" s="6" t="n"/>
+      <c r="Q91" s="9" t="n"/>
+      <c r="R91" s="9" t="n"/>
+      <c r="S91" s="9" t="n"/>
+      <c r="T91" s="9" t="n"/>
     </row>
     <row r="92" ht="23" customHeight="1">
       <c r="A92" s="10" t="n"/>
@@ -2268,14 +2640,18 @@
       <c r="F92" s="10" t="n"/>
       <c r="G92" s="12" t="n"/>
       <c r="H92" s="10" t="n"/>
-      <c r="I92" s="10" t="n"/>
+      <c r="I92" s="12" t="n"/>
       <c r="J92" s="12" t="n"/>
-      <c r="K92" s="10" t="n"/>
+      <c r="K92" s="13" t="n"/>
       <c r="L92" s="10" t="n"/>
-      <c r="M92" s="13" t="n"/>
-      <c r="N92" s="13" t="n"/>
-      <c r="O92" s="13" t="n"/>
-      <c r="P92" s="13" t="n"/>
+      <c r="M92" s="10" t="n"/>
+      <c r="N92" s="12" t="n"/>
+      <c r="O92" s="10" t="n"/>
+      <c r="P92" s="10" t="n"/>
+      <c r="Q92" s="13" t="n"/>
+      <c r="R92" s="13" t="n"/>
+      <c r="S92" s="13" t="n"/>
+      <c r="T92" s="13" t="n"/>
     </row>
     <row r="93" ht="23" customHeight="1">
       <c r="A93" s="6" t="n"/>
@@ -2286,14 +2662,18 @@
       <c r="F93" s="6" t="n"/>
       <c r="G93" s="8" t="n"/>
       <c r="H93" s="6" t="n"/>
-      <c r="I93" s="6" t="n"/>
+      <c r="I93" s="8" t="n"/>
       <c r="J93" s="8" t="n"/>
-      <c r="K93" s="6" t="n"/>
+      <c r="K93" s="9" t="n"/>
       <c r="L93" s="6" t="n"/>
-      <c r="M93" s="9" t="n"/>
-      <c r="N93" s="9" t="n"/>
-      <c r="O93" s="9" t="n"/>
-      <c r="P93" s="9" t="n"/>
+      <c r="M93" s="6" t="n"/>
+      <c r="N93" s="8" t="n"/>
+      <c r="O93" s="6" t="n"/>
+      <c r="P93" s="6" t="n"/>
+      <c r="Q93" s="9" t="n"/>
+      <c r="R93" s="9" t="n"/>
+      <c r="S93" s="9" t="n"/>
+      <c r="T93" s="9" t="n"/>
     </row>
     <row r="94" ht="23" customHeight="1">
       <c r="A94" s="10" t="n"/>
@@ -2304,14 +2684,18 @@
       <c r="F94" s="10" t="n"/>
       <c r="G94" s="12" t="n"/>
       <c r="H94" s="10" t="n"/>
-      <c r="I94" s="10" t="n"/>
+      <c r="I94" s="12" t="n"/>
       <c r="J94" s="12" t="n"/>
-      <c r="K94" s="10" t="n"/>
+      <c r="K94" s="13" t="n"/>
       <c r="L94" s="10" t="n"/>
-      <c r="M94" s="13" t="n"/>
-      <c r="N94" s="13" t="n"/>
-      <c r="O94" s="13" t="n"/>
-      <c r="P94" s="13" t="n"/>
+      <c r="M94" s="10" t="n"/>
+      <c r="N94" s="12" t="n"/>
+      <c r="O94" s="10" t="n"/>
+      <c r="P94" s="10" t="n"/>
+      <c r="Q94" s="13" t="n"/>
+      <c r="R94" s="13" t="n"/>
+      <c r="S94" s="13" t="n"/>
+      <c r="T94" s="13" t="n"/>
     </row>
     <row r="95" ht="23" customHeight="1">
       <c r="A95" s="6" t="n"/>
@@ -2322,14 +2706,18 @@
       <c r="F95" s="6" t="n"/>
       <c r="G95" s="8" t="n"/>
       <c r="H95" s="6" t="n"/>
-      <c r="I95" s="6" t="n"/>
+      <c r="I95" s="8" t="n"/>
       <c r="J95" s="8" t="n"/>
-      <c r="K95" s="6" t="n"/>
+      <c r="K95" s="9" t="n"/>
       <c r="L95" s="6" t="n"/>
-      <c r="M95" s="9" t="n"/>
-      <c r="N95" s="9" t="n"/>
-      <c r="O95" s="9" t="n"/>
-      <c r="P95" s="9" t="n"/>
+      <c r="M95" s="6" t="n"/>
+      <c r="N95" s="8" t="n"/>
+      <c r="O95" s="6" t="n"/>
+      <c r="P95" s="6" t="n"/>
+      <c r="Q95" s="9" t="n"/>
+      <c r="R95" s="9" t="n"/>
+      <c r="S95" s="9" t="n"/>
+      <c r="T95" s="9" t="n"/>
     </row>
     <row r="96" ht="23" customHeight="1">
       <c r="A96" s="10" t="n"/>
@@ -2340,14 +2728,18 @@
       <c r="F96" s="10" t="n"/>
       <c r="G96" s="12" t="n"/>
       <c r="H96" s="10" t="n"/>
-      <c r="I96" s="10" t="n"/>
+      <c r="I96" s="12" t="n"/>
       <c r="J96" s="12" t="n"/>
-      <c r="K96" s="10" t="n"/>
+      <c r="K96" s="13" t="n"/>
       <c r="L96" s="10" t="n"/>
-      <c r="M96" s="13" t="n"/>
-      <c r="N96" s="13" t="n"/>
-      <c r="O96" s="13" t="n"/>
-      <c r="P96" s="13" t="n"/>
+      <c r="M96" s="10" t="n"/>
+      <c r="N96" s="12" t="n"/>
+      <c r="O96" s="10" t="n"/>
+      <c r="P96" s="10" t="n"/>
+      <c r="Q96" s="13" t="n"/>
+      <c r="R96" s="13" t="n"/>
+      <c r="S96" s="13" t="n"/>
+      <c r="T96" s="13" t="n"/>
     </row>
     <row r="97" ht="23" customHeight="1">
       <c r="A97" s="6" t="n"/>
@@ -2358,14 +2750,18 @@
       <c r="F97" s="6" t="n"/>
       <c r="G97" s="8" t="n"/>
       <c r="H97" s="6" t="n"/>
-      <c r="I97" s="6" t="n"/>
+      <c r="I97" s="8" t="n"/>
       <c r="J97" s="8" t="n"/>
-      <c r="K97" s="6" t="n"/>
+      <c r="K97" s="9" t="n"/>
       <c r="L97" s="6" t="n"/>
-      <c r="M97" s="9" t="n"/>
-      <c r="N97" s="9" t="n"/>
-      <c r="O97" s="9" t="n"/>
-      <c r="P97" s="9" t="n"/>
+      <c r="M97" s="6" t="n"/>
+      <c r="N97" s="8" t="n"/>
+      <c r="O97" s="6" t="n"/>
+      <c r="P97" s="6" t="n"/>
+      <c r="Q97" s="9" t="n"/>
+      <c r="R97" s="9" t="n"/>
+      <c r="S97" s="9" t="n"/>
+      <c r="T97" s="9" t="n"/>
     </row>
     <row r="98" ht="23" customHeight="1">
       <c r="A98" s="10" t="n"/>
@@ -2376,14 +2772,18 @@
       <c r="F98" s="10" t="n"/>
       <c r="G98" s="12" t="n"/>
       <c r="H98" s="10" t="n"/>
-      <c r="I98" s="10" t="n"/>
+      <c r="I98" s="12" t="n"/>
       <c r="J98" s="12" t="n"/>
-      <c r="K98" s="10" t="n"/>
+      <c r="K98" s="13" t="n"/>
       <c r="L98" s="10" t="n"/>
-      <c r="M98" s="13" t="n"/>
-      <c r="N98" s="13" t="n"/>
-      <c r="O98" s="13" t="n"/>
-      <c r="P98" s="13" t="n"/>
+      <c r="M98" s="10" t="n"/>
+      <c r="N98" s="12" t="n"/>
+      <c r="O98" s="10" t="n"/>
+      <c r="P98" s="10" t="n"/>
+      <c r="Q98" s="13" t="n"/>
+      <c r="R98" s="13" t="n"/>
+      <c r="S98" s="13" t="n"/>
+      <c r="T98" s="13" t="n"/>
     </row>
     <row r="99" ht="23" customHeight="1">
       <c r="A99" s="6" t="n"/>
@@ -2394,14 +2794,18 @@
       <c r="F99" s="6" t="n"/>
       <c r="G99" s="8" t="n"/>
       <c r="H99" s="6" t="n"/>
-      <c r="I99" s="6" t="n"/>
+      <c r="I99" s="8" t="n"/>
       <c r="J99" s="8" t="n"/>
-      <c r="K99" s="6" t="n"/>
+      <c r="K99" s="9" t="n"/>
       <c r="L99" s="6" t="n"/>
-      <c r="M99" s="9" t="n"/>
-      <c r="N99" s="9" t="n"/>
-      <c r="O99" s="9" t="n"/>
-      <c r="P99" s="9" t="n"/>
+      <c r="M99" s="6" t="n"/>
+      <c r="N99" s="8" t="n"/>
+      <c r="O99" s="6" t="n"/>
+      <c r="P99" s="6" t="n"/>
+      <c r="Q99" s="9" t="n"/>
+      <c r="R99" s="9" t="n"/>
+      <c r="S99" s="9" t="n"/>
+      <c r="T99" s="9" t="n"/>
     </row>
     <row r="100" ht="23" customHeight="1">
       <c r="A100" s="10" t="n"/>
@@ -2412,14 +2816,18 @@
       <c r="F100" s="10" t="n"/>
       <c r="G100" s="12" t="n"/>
       <c r="H100" s="10" t="n"/>
-      <c r="I100" s="10" t="n"/>
+      <c r="I100" s="12" t="n"/>
       <c r="J100" s="12" t="n"/>
-      <c r="K100" s="10" t="n"/>
+      <c r="K100" s="13" t="n"/>
       <c r="L100" s="10" t="n"/>
-      <c r="M100" s="13" t="n"/>
-      <c r="N100" s="13" t="n"/>
-      <c r="O100" s="13" t="n"/>
-      <c r="P100" s="13" t="n"/>
+      <c r="M100" s="10" t="n"/>
+      <c r="N100" s="12" t="n"/>
+      <c r="O100" s="10" t="n"/>
+      <c r="P100" s="10" t="n"/>
+      <c r="Q100" s="13" t="n"/>
+      <c r="R100" s="13" t="n"/>
+      <c r="S100" s="13" t="n"/>
+      <c r="T100" s="13" t="n"/>
     </row>
     <row r="101" ht="23" customHeight="1">
       <c r="A101" s="6" t="n"/>
@@ -2430,14 +2838,18 @@
       <c r="F101" s="6" t="n"/>
       <c r="G101" s="8" t="n"/>
       <c r="H101" s="6" t="n"/>
-      <c r="I101" s="6" t="n"/>
+      <c r="I101" s="8" t="n"/>
       <c r="J101" s="8" t="n"/>
-      <c r="K101" s="6" t="n"/>
+      <c r="K101" s="9" t="n"/>
       <c r="L101" s="6" t="n"/>
-      <c r="M101" s="9" t="n"/>
-      <c r="N101" s="9" t="n"/>
-      <c r="O101" s="9" t="n"/>
-      <c r="P101" s="9" t="n"/>
+      <c r="M101" s="6" t="n"/>
+      <c r="N101" s="8" t="n"/>
+      <c r="O101" s="6" t="n"/>
+      <c r="P101" s="6" t="n"/>
+      <c r="Q101" s="9" t="n"/>
+      <c r="R101" s="9" t="n"/>
+      <c r="S101" s="9" t="n"/>
+      <c r="T101" s="9" t="n"/>
     </row>
     <row r="102" ht="23" customHeight="1">
       <c r="A102" s="10" t="n"/>
@@ -2448,14 +2860,18 @@
       <c r="F102" s="10" t="n"/>
       <c r="G102" s="12" t="n"/>
       <c r="H102" s="10" t="n"/>
-      <c r="I102" s="10" t="n"/>
+      <c r="I102" s="12" t="n"/>
       <c r="J102" s="12" t="n"/>
-      <c r="K102" s="10" t="n"/>
+      <c r="K102" s="13" t="n"/>
       <c r="L102" s="10" t="n"/>
-      <c r="M102" s="13" t="n"/>
-      <c r="N102" s="13" t="n"/>
-      <c r="O102" s="13" t="n"/>
-      <c r="P102" s="13" t="n"/>
+      <c r="M102" s="10" t="n"/>
+      <c r="N102" s="12" t="n"/>
+      <c r="O102" s="10" t="n"/>
+      <c r="P102" s="10" t="n"/>
+      <c r="Q102" s="13" t="n"/>
+      <c r="R102" s="13" t="n"/>
+      <c r="S102" s="13" t="n"/>
+      <c r="T102" s="13" t="n"/>
     </row>
     <row r="103" ht="23" customHeight="1">
       <c r="A103" s="6" t="n"/>
@@ -2466,14 +2882,18 @@
       <c r="F103" s="6" t="n"/>
       <c r="G103" s="8" t="n"/>
       <c r="H103" s="6" t="n"/>
-      <c r="I103" s="6" t="n"/>
+      <c r="I103" s="8" t="n"/>
       <c r="J103" s="8" t="n"/>
-      <c r="K103" s="6" t="n"/>
+      <c r="K103" s="9" t="n"/>
       <c r="L103" s="6" t="n"/>
-      <c r="M103" s="9" t="n"/>
-      <c r="N103" s="9" t="n"/>
-      <c r="O103" s="9" t="n"/>
-      <c r="P103" s="9" t="n"/>
+      <c r="M103" s="6" t="n"/>
+      <c r="N103" s="8" t="n"/>
+      <c r="O103" s="6" t="n"/>
+      <c r="P103" s="6" t="n"/>
+      <c r="Q103" s="9" t="n"/>
+      <c r="R103" s="9" t="n"/>
+      <c r="S103" s="9" t="n"/>
+      <c r="T103" s="9" t="n"/>
     </row>
     <row r="104" ht="23" customHeight="1">
       <c r="A104" s="10" t="n"/>
@@ -2484,14 +2904,18 @@
       <c r="F104" s="10" t="n"/>
       <c r="G104" s="12" t="n"/>
       <c r="H104" s="10" t="n"/>
-      <c r="I104" s="10" t="n"/>
+      <c r="I104" s="12" t="n"/>
       <c r="J104" s="12" t="n"/>
-      <c r="K104" s="10" t="n"/>
+      <c r="K104" s="13" t="n"/>
       <c r="L104" s="10" t="n"/>
-      <c r="M104" s="13" t="n"/>
-      <c r="N104" s="13" t="n"/>
-      <c r="O104" s="13" t="n"/>
-      <c r="P104" s="13" t="n"/>
+      <c r="M104" s="10" t="n"/>
+      <c r="N104" s="12" t="n"/>
+      <c r="O104" s="10" t="n"/>
+      <c r="P104" s="10" t="n"/>
+      <c r="Q104" s="13" t="n"/>
+      <c r="R104" s="13" t="n"/>
+      <c r="S104" s="13" t="n"/>
+      <c r="T104" s="13" t="n"/>
     </row>
     <row r="105" ht="23" customHeight="1">
       <c r="A105" s="6" t="n"/>
@@ -2502,14 +2926,18 @@
       <c r="F105" s="6" t="n"/>
       <c r="G105" s="8" t="n"/>
       <c r="H105" s="6" t="n"/>
-      <c r="I105" s="6" t="n"/>
+      <c r="I105" s="8" t="n"/>
       <c r="J105" s="8" t="n"/>
-      <c r="K105" s="6" t="n"/>
+      <c r="K105" s="9" t="n"/>
       <c r="L105" s="6" t="n"/>
-      <c r="M105" s="9" t="n"/>
-      <c r="N105" s="9" t="n"/>
-      <c r="O105" s="9" t="n"/>
-      <c r="P105" s="9" t="n"/>
+      <c r="M105" s="6" t="n"/>
+      <c r="N105" s="8" t="n"/>
+      <c r="O105" s="6" t="n"/>
+      <c r="P105" s="6" t="n"/>
+      <c r="Q105" s="9" t="n"/>
+      <c r="R105" s="9" t="n"/>
+      <c r="S105" s="9" t="n"/>
+      <c r="T105" s="9" t="n"/>
     </row>
     <row r="106" ht="23" customHeight="1">
       <c r="A106" s="10" t="n"/>
@@ -2520,14 +2948,18 @@
       <c r="F106" s="10" t="n"/>
       <c r="G106" s="12" t="n"/>
       <c r="H106" s="10" t="n"/>
-      <c r="I106" s="10" t="n"/>
+      <c r="I106" s="12" t="n"/>
       <c r="J106" s="12" t="n"/>
-      <c r="K106" s="10" t="n"/>
+      <c r="K106" s="13" t="n"/>
       <c r="L106" s="10" t="n"/>
-      <c r="M106" s="13" t="n"/>
-      <c r="N106" s="13" t="n"/>
-      <c r="O106" s="13" t="n"/>
-      <c r="P106" s="13" t="n"/>
+      <c r="M106" s="10" t="n"/>
+      <c r="N106" s="12" t="n"/>
+      <c r="O106" s="10" t="n"/>
+      <c r="P106" s="10" t="n"/>
+      <c r="Q106" s="13" t="n"/>
+      <c r="R106" s="13" t="n"/>
+      <c r="S106" s="13" t="n"/>
+      <c r="T106" s="13" t="n"/>
     </row>
     <row r="107" ht="23" customHeight="1">
       <c r="A107" s="6" t="n"/>
@@ -2538,14 +2970,18 @@
       <c r="F107" s="6" t="n"/>
       <c r="G107" s="8" t="n"/>
       <c r="H107" s="6" t="n"/>
-      <c r="I107" s="6" t="n"/>
+      <c r="I107" s="8" t="n"/>
       <c r="J107" s="8" t="n"/>
-      <c r="K107" s="6" t="n"/>
+      <c r="K107" s="9" t="n"/>
       <c r="L107" s="6" t="n"/>
-      <c r="M107" s="9" t="n"/>
-      <c r="N107" s="9" t="n"/>
-      <c r="O107" s="9" t="n"/>
-      <c r="P107" s="9" t="n"/>
+      <c r="M107" s="6" t="n"/>
+      <c r="N107" s="8" t="n"/>
+      <c r="O107" s="6" t="n"/>
+      <c r="P107" s="6" t="n"/>
+      <c r="Q107" s="9" t="n"/>
+      <c r="R107" s="9" t="n"/>
+      <c r="S107" s="9" t="n"/>
+      <c r="T107" s="9" t="n"/>
     </row>
     <row r="108" ht="23" customHeight="1">
       <c r="A108" s="10" t="n"/>
@@ -2556,14 +2992,18 @@
       <c r="F108" s="10" t="n"/>
       <c r="G108" s="12" t="n"/>
       <c r="H108" s="10" t="n"/>
-      <c r="I108" s="10" t="n"/>
+      <c r="I108" s="12" t="n"/>
       <c r="J108" s="12" t="n"/>
-      <c r="K108" s="10" t="n"/>
+      <c r="K108" s="13" t="n"/>
       <c r="L108" s="10" t="n"/>
-      <c r="M108" s="13" t="n"/>
-      <c r="N108" s="13" t="n"/>
-      <c r="O108" s="13" t="n"/>
-      <c r="P108" s="13" t="n"/>
+      <c r="M108" s="10" t="n"/>
+      <c r="N108" s="12" t="n"/>
+      <c r="O108" s="10" t="n"/>
+      <c r="P108" s="10" t="n"/>
+      <c r="Q108" s="13" t="n"/>
+      <c r="R108" s="13" t="n"/>
+      <c r="S108" s="13" t="n"/>
+      <c r="T108" s="13" t="n"/>
     </row>
     <row r="109" ht="23" customHeight="1">
       <c r="A109" s="6" t="n"/>
@@ -2574,14 +3014,18 @@
       <c r="F109" s="6" t="n"/>
       <c r="G109" s="8" t="n"/>
       <c r="H109" s="6" t="n"/>
-      <c r="I109" s="6" t="n"/>
+      <c r="I109" s="8" t="n"/>
       <c r="J109" s="8" t="n"/>
-      <c r="K109" s="6" t="n"/>
+      <c r="K109" s="9" t="n"/>
       <c r="L109" s="6" t="n"/>
-      <c r="M109" s="9" t="n"/>
-      <c r="N109" s="9" t="n"/>
-      <c r="O109" s="9" t="n"/>
-      <c r="P109" s="9" t="n"/>
+      <c r="M109" s="6" t="n"/>
+      <c r="N109" s="8" t="n"/>
+      <c r="O109" s="6" t="n"/>
+      <c r="P109" s="6" t="n"/>
+      <c r="Q109" s="9" t="n"/>
+      <c r="R109" s="9" t="n"/>
+      <c r="S109" s="9" t="n"/>
+      <c r="T109" s="9" t="n"/>
     </row>
     <row r="110" ht="23" customHeight="1">
       <c r="A110" s="10" t="n"/>
@@ -2592,14 +3036,18 @@
       <c r="F110" s="10" t="n"/>
       <c r="G110" s="12" t="n"/>
       <c r="H110" s="10" t="n"/>
-      <c r="I110" s="10" t="n"/>
+      <c r="I110" s="12" t="n"/>
       <c r="J110" s="12" t="n"/>
-      <c r="K110" s="10" t="n"/>
+      <c r="K110" s="13" t="n"/>
       <c r="L110" s="10" t="n"/>
-      <c r="M110" s="13" t="n"/>
-      <c r="N110" s="13" t="n"/>
-      <c r="O110" s="13" t="n"/>
-      <c r="P110" s="13" t="n"/>
+      <c r="M110" s="10" t="n"/>
+      <c r="N110" s="12" t="n"/>
+      <c r="O110" s="10" t="n"/>
+      <c r="P110" s="10" t="n"/>
+      <c r="Q110" s="13" t="n"/>
+      <c r="R110" s="13" t="n"/>
+      <c r="S110" s="13" t="n"/>
+      <c r="T110" s="13" t="n"/>
     </row>
     <row r="111" ht="23" customHeight="1">
       <c r="A111" s="6" t="n"/>
@@ -2610,14 +3058,18 @@
       <c r="F111" s="6" t="n"/>
       <c r="G111" s="8" t="n"/>
       <c r="H111" s="6" t="n"/>
-      <c r="I111" s="6" t="n"/>
+      <c r="I111" s="8" t="n"/>
       <c r="J111" s="8" t="n"/>
-      <c r="K111" s="6" t="n"/>
+      <c r="K111" s="9" t="n"/>
       <c r="L111" s="6" t="n"/>
-      <c r="M111" s="9" t="n"/>
-      <c r="N111" s="9" t="n"/>
-      <c r="O111" s="9" t="n"/>
-      <c r="P111" s="9" t="n"/>
+      <c r="M111" s="6" t="n"/>
+      <c r="N111" s="8" t="n"/>
+      <c r="O111" s="6" t="n"/>
+      <c r="P111" s="6" t="n"/>
+      <c r="Q111" s="9" t="n"/>
+      <c r="R111" s="9" t="n"/>
+      <c r="S111" s="9" t="n"/>
+      <c r="T111" s="9" t="n"/>
     </row>
     <row r="112" ht="23" customHeight="1">
       <c r="A112" s="10" t="n"/>
@@ -2628,14 +3080,18 @@
       <c r="F112" s="10" t="n"/>
       <c r="G112" s="12" t="n"/>
       <c r="H112" s="10" t="n"/>
-      <c r="I112" s="10" t="n"/>
+      <c r="I112" s="12" t="n"/>
       <c r="J112" s="12" t="n"/>
-      <c r="K112" s="10" t="n"/>
+      <c r="K112" s="13" t="n"/>
       <c r="L112" s="10" t="n"/>
-      <c r="M112" s="13" t="n"/>
-      <c r="N112" s="13" t="n"/>
-      <c r="O112" s="13" t="n"/>
-      <c r="P112" s="13" t="n"/>
+      <c r="M112" s="10" t="n"/>
+      <c r="N112" s="12" t="n"/>
+      <c r="O112" s="10" t="n"/>
+      <c r="P112" s="10" t="n"/>
+      <c r="Q112" s="13" t="n"/>
+      <c r="R112" s="13" t="n"/>
+      <c r="S112" s="13" t="n"/>
+      <c r="T112" s="13" t="n"/>
     </row>
     <row r="113" ht="23" customHeight="1">
       <c r="A113" s="6" t="n"/>
@@ -2646,14 +3102,18 @@
       <c r="F113" s="6" t="n"/>
       <c r="G113" s="8" t="n"/>
       <c r="H113" s="6" t="n"/>
-      <c r="I113" s="6" t="n"/>
+      <c r="I113" s="8" t="n"/>
       <c r="J113" s="8" t="n"/>
-      <c r="K113" s="6" t="n"/>
+      <c r="K113" s="9" t="n"/>
       <c r="L113" s="6" t="n"/>
-      <c r="M113" s="9" t="n"/>
-      <c r="N113" s="9" t="n"/>
-      <c r="O113" s="9" t="n"/>
-      <c r="P113" s="9" t="n"/>
+      <c r="M113" s="6" t="n"/>
+      <c r="N113" s="8" t="n"/>
+      <c r="O113" s="6" t="n"/>
+      <c r="P113" s="6" t="n"/>
+      <c r="Q113" s="9" t="n"/>
+      <c r="R113" s="9" t="n"/>
+      <c r="S113" s="9" t="n"/>
+      <c r="T113" s="9" t="n"/>
     </row>
     <row r="114" ht="23" customHeight="1">
       <c r="A114" s="10" t="n"/>
@@ -2664,14 +3124,18 @@
       <c r="F114" s="10" t="n"/>
       <c r="G114" s="12" t="n"/>
       <c r="H114" s="10" t="n"/>
-      <c r="I114" s="10" t="n"/>
+      <c r="I114" s="12" t="n"/>
       <c r="J114" s="12" t="n"/>
-      <c r="K114" s="10" t="n"/>
+      <c r="K114" s="13" t="n"/>
       <c r="L114" s="10" t="n"/>
-      <c r="M114" s="13" t="n"/>
-      <c r="N114" s="13" t="n"/>
-      <c r="O114" s="13" t="n"/>
-      <c r="P114" s="13" t="n"/>
+      <c r="M114" s="10" t="n"/>
+      <c r="N114" s="12" t="n"/>
+      <c r="O114" s="10" t="n"/>
+      <c r="P114" s="10" t="n"/>
+      <c r="Q114" s="13" t="n"/>
+      <c r="R114" s="13" t="n"/>
+      <c r="S114" s="13" t="n"/>
+      <c r="T114" s="13" t="n"/>
     </row>
     <row r="115" ht="23" customHeight="1">
       <c r="A115" s="6" t="n"/>
@@ -2682,14 +3146,18 @@
       <c r="F115" s="6" t="n"/>
       <c r="G115" s="8" t="n"/>
       <c r="H115" s="6" t="n"/>
-      <c r="I115" s="6" t="n"/>
+      <c r="I115" s="8" t="n"/>
       <c r="J115" s="8" t="n"/>
-      <c r="K115" s="6" t="n"/>
+      <c r="K115" s="9" t="n"/>
       <c r="L115" s="6" t="n"/>
-      <c r="M115" s="9" t="n"/>
-      <c r="N115" s="9" t="n"/>
-      <c r="O115" s="9" t="n"/>
-      <c r="P115" s="9" t="n"/>
+      <c r="M115" s="6" t="n"/>
+      <c r="N115" s="8" t="n"/>
+      <c r="O115" s="6" t="n"/>
+      <c r="P115" s="6" t="n"/>
+      <c r="Q115" s="9" t="n"/>
+      <c r="R115" s="9" t="n"/>
+      <c r="S115" s="9" t="n"/>
+      <c r="T115" s="9" t="n"/>
     </row>
     <row r="116" ht="23" customHeight="1">
       <c r="A116" s="10" t="n"/>
@@ -2700,14 +3168,18 @@
       <c r="F116" s="10" t="n"/>
       <c r="G116" s="12" t="n"/>
       <c r="H116" s="10" t="n"/>
-      <c r="I116" s="10" t="n"/>
+      <c r="I116" s="12" t="n"/>
       <c r="J116" s="12" t="n"/>
-      <c r="K116" s="10" t="n"/>
+      <c r="K116" s="13" t="n"/>
       <c r="L116" s="10" t="n"/>
-      <c r="M116" s="13" t="n"/>
-      <c r="N116" s="13" t="n"/>
-      <c r="O116" s="13" t="n"/>
-      <c r="P116" s="13" t="n"/>
+      <c r="M116" s="10" t="n"/>
+      <c r="N116" s="12" t="n"/>
+      <c r="O116" s="10" t="n"/>
+      <c r="P116" s="10" t="n"/>
+      <c r="Q116" s="13" t="n"/>
+      <c r="R116" s="13" t="n"/>
+      <c r="S116" s="13" t="n"/>
+      <c r="T116" s="13" t="n"/>
     </row>
     <row r="117" ht="23" customHeight="1">
       <c r="A117" s="6" t="n"/>
@@ -2718,14 +3190,18 @@
       <c r="F117" s="6" t="n"/>
       <c r="G117" s="8" t="n"/>
       <c r="H117" s="6" t="n"/>
-      <c r="I117" s="6" t="n"/>
+      <c r="I117" s="8" t="n"/>
       <c r="J117" s="8" t="n"/>
-      <c r="K117" s="6" t="n"/>
+      <c r="K117" s="9" t="n"/>
       <c r="L117" s="6" t="n"/>
-      <c r="M117" s="9" t="n"/>
-      <c r="N117" s="9" t="n"/>
-      <c r="O117" s="9" t="n"/>
-      <c r="P117" s="9" t="n"/>
+      <c r="M117" s="6" t="n"/>
+      <c r="N117" s="8" t="n"/>
+      <c r="O117" s="6" t="n"/>
+      <c r="P117" s="6" t="n"/>
+      <c r="Q117" s="9" t="n"/>
+      <c r="R117" s="9" t="n"/>
+      <c r="S117" s="9" t="n"/>
+      <c r="T117" s="9" t="n"/>
     </row>
     <row r="118" ht="23" customHeight="1">
       <c r="A118" s="10" t="n"/>
@@ -2736,14 +3212,18 @@
       <c r="F118" s="10" t="n"/>
       <c r="G118" s="12" t="n"/>
       <c r="H118" s="10" t="n"/>
-      <c r="I118" s="10" t="n"/>
+      <c r="I118" s="12" t="n"/>
       <c r="J118" s="12" t="n"/>
-      <c r="K118" s="10" t="n"/>
+      <c r="K118" s="13" t="n"/>
       <c r="L118" s="10" t="n"/>
-      <c r="M118" s="13" t="n"/>
-      <c r="N118" s="13" t="n"/>
-      <c r="O118" s="13" t="n"/>
-      <c r="P118" s="13" t="n"/>
+      <c r="M118" s="10" t="n"/>
+      <c r="N118" s="12" t="n"/>
+      <c r="O118" s="10" t="n"/>
+      <c r="P118" s="10" t="n"/>
+      <c r="Q118" s="13" t="n"/>
+      <c r="R118" s="13" t="n"/>
+      <c r="S118" s="13" t="n"/>
+      <c r="T118" s="13" t="n"/>
     </row>
     <row r="119" ht="23" customHeight="1">
       <c r="A119" s="6" t="n"/>
@@ -2754,14 +3234,18 @@
       <c r="F119" s="6" t="n"/>
       <c r="G119" s="8" t="n"/>
       <c r="H119" s="6" t="n"/>
-      <c r="I119" s="6" t="n"/>
+      <c r="I119" s="8" t="n"/>
       <c r="J119" s="8" t="n"/>
-      <c r="K119" s="6" t="n"/>
+      <c r="K119" s="9" t="n"/>
       <c r="L119" s="6" t="n"/>
-      <c r="M119" s="9" t="n"/>
-      <c r="N119" s="9" t="n"/>
-      <c r="O119" s="9" t="n"/>
-      <c r="P119" s="9" t="n"/>
+      <c r="M119" s="6" t="n"/>
+      <c r="N119" s="8" t="n"/>
+      <c r="O119" s="6" t="n"/>
+      <c r="P119" s="6" t="n"/>
+      <c r="Q119" s="9" t="n"/>
+      <c r="R119" s="9" t="n"/>
+      <c r="S119" s="9" t="n"/>
+      <c r="T119" s="9" t="n"/>
     </row>
     <row r="120" ht="23" customHeight="1">
       <c r="A120" s="10" t="n"/>
@@ -2772,14 +3256,18 @@
       <c r="F120" s="10" t="n"/>
       <c r="G120" s="12" t="n"/>
       <c r="H120" s="10" t="n"/>
-      <c r="I120" s="10" t="n"/>
+      <c r="I120" s="12" t="n"/>
       <c r="J120" s="12" t="n"/>
-      <c r="K120" s="10" t="n"/>
+      <c r="K120" s="13" t="n"/>
       <c r="L120" s="10" t="n"/>
-      <c r="M120" s="13" t="n"/>
-      <c r="N120" s="13" t="n"/>
-      <c r="O120" s="13" t="n"/>
-      <c r="P120" s="13" t="n"/>
+      <c r="M120" s="10" t="n"/>
+      <c r="N120" s="12" t="n"/>
+      <c r="O120" s="10" t="n"/>
+      <c r="P120" s="10" t="n"/>
+      <c r="Q120" s="13" t="n"/>
+      <c r="R120" s="13" t="n"/>
+      <c r="S120" s="13" t="n"/>
+      <c r="T120" s="13" t="n"/>
     </row>
     <row r="121" ht="23" customHeight="1">
       <c r="A121" s="6" t="n"/>
@@ -2790,14 +3278,18 @@
       <c r="F121" s="6" t="n"/>
       <c r="G121" s="8" t="n"/>
       <c r="H121" s="6" t="n"/>
-      <c r="I121" s="6" t="n"/>
+      <c r="I121" s="8" t="n"/>
       <c r="J121" s="8" t="n"/>
-      <c r="K121" s="6" t="n"/>
+      <c r="K121" s="9" t="n"/>
       <c r="L121" s="6" t="n"/>
-      <c r="M121" s="9" t="n"/>
-      <c r="N121" s="9" t="n"/>
-      <c r="O121" s="9" t="n"/>
-      <c r="P121" s="9" t="n"/>
+      <c r="M121" s="6" t="n"/>
+      <c r="N121" s="8" t="n"/>
+      <c r="O121" s="6" t="n"/>
+      <c r="P121" s="6" t="n"/>
+      <c r="Q121" s="9" t="n"/>
+      <c r="R121" s="9" t="n"/>
+      <c r="S121" s="9" t="n"/>
+      <c r="T121" s="9" t="n"/>
     </row>
     <row r="122" ht="23" customHeight="1">
       <c r="A122" s="10" t="n"/>
@@ -2808,14 +3300,18 @@
       <c r="F122" s="10" t="n"/>
       <c r="G122" s="12" t="n"/>
       <c r="H122" s="10" t="n"/>
-      <c r="I122" s="10" t="n"/>
+      <c r="I122" s="12" t="n"/>
       <c r="J122" s="12" t="n"/>
-      <c r="K122" s="10" t="n"/>
+      <c r="K122" s="13" t="n"/>
       <c r="L122" s="10" t="n"/>
-      <c r="M122" s="13" t="n"/>
-      <c r="N122" s="13" t="n"/>
-      <c r="O122" s="13" t="n"/>
-      <c r="P122" s="13" t="n"/>
+      <c r="M122" s="10" t="n"/>
+      <c r="N122" s="12" t="n"/>
+      <c r="O122" s="10" t="n"/>
+      <c r="P122" s="10" t="n"/>
+      <c r="Q122" s="13" t="n"/>
+      <c r="R122" s="13" t="n"/>
+      <c r="S122" s="13" t="n"/>
+      <c r="T122" s="13" t="n"/>
     </row>
     <row r="123" ht="23" customHeight="1">
       <c r="A123" s="6" t="n"/>
@@ -2826,14 +3322,18 @@
       <c r="F123" s="6" t="n"/>
       <c r="G123" s="8" t="n"/>
       <c r="H123" s="6" t="n"/>
-      <c r="I123" s="6" t="n"/>
+      <c r="I123" s="8" t="n"/>
       <c r="J123" s="8" t="n"/>
-      <c r="K123" s="6" t="n"/>
+      <c r="K123" s="9" t="n"/>
       <c r="L123" s="6" t="n"/>
-      <c r="M123" s="9" t="n"/>
-      <c r="N123" s="9" t="n"/>
-      <c r="O123" s="9" t="n"/>
-      <c r="P123" s="9" t="n"/>
+      <c r="M123" s="6" t="n"/>
+      <c r="N123" s="8" t="n"/>
+      <c r="O123" s="6" t="n"/>
+      <c r="P123" s="6" t="n"/>
+      <c r="Q123" s="9" t="n"/>
+      <c r="R123" s="9" t="n"/>
+      <c r="S123" s="9" t="n"/>
+      <c r="T123" s="9" t="n"/>
     </row>
     <row r="124" ht="23" customHeight="1">
       <c r="A124" s="10" t="n"/>
@@ -2844,14 +3344,18 @@
       <c r="F124" s="10" t="n"/>
       <c r="G124" s="12" t="n"/>
       <c r="H124" s="10" t="n"/>
-      <c r="I124" s="10" t="n"/>
+      <c r="I124" s="12" t="n"/>
       <c r="J124" s="12" t="n"/>
-      <c r="K124" s="10" t="n"/>
+      <c r="K124" s="13" t="n"/>
       <c r="L124" s="10" t="n"/>
-      <c r="M124" s="13" t="n"/>
-      <c r="N124" s="13" t="n"/>
-      <c r="O124" s="13" t="n"/>
-      <c r="P124" s="13" t="n"/>
+      <c r="M124" s="10" t="n"/>
+      <c r="N124" s="12" t="n"/>
+      <c r="O124" s="10" t="n"/>
+      <c r="P124" s="10" t="n"/>
+      <c r="Q124" s="13" t="n"/>
+      <c r="R124" s="13" t="n"/>
+      <c r="S124" s="13" t="n"/>
+      <c r="T124" s="13" t="n"/>
     </row>
     <row r="125" ht="23" customHeight="1">
       <c r="A125" s="6" t="n"/>
@@ -2862,14 +3366,18 @@
       <c r="F125" s="6" t="n"/>
       <c r="G125" s="8" t="n"/>
       <c r="H125" s="6" t="n"/>
-      <c r="I125" s="6" t="n"/>
+      <c r="I125" s="8" t="n"/>
       <c r="J125" s="8" t="n"/>
-      <c r="K125" s="6" t="n"/>
+      <c r="K125" s="9" t="n"/>
       <c r="L125" s="6" t="n"/>
-      <c r="M125" s="9" t="n"/>
-      <c r="N125" s="9" t="n"/>
-      <c r="O125" s="9" t="n"/>
-      <c r="P125" s="9" t="n"/>
+      <c r="M125" s="6" t="n"/>
+      <c r="N125" s="8" t="n"/>
+      <c r="O125" s="6" t="n"/>
+      <c r="P125" s="6" t="n"/>
+      <c r="Q125" s="9" t="n"/>
+      <c r="R125" s="9" t="n"/>
+      <c r="S125" s="9" t="n"/>
+      <c r="T125" s="9" t="n"/>
     </row>
     <row r="126" ht="23" customHeight="1">
       <c r="A126" s="10" t="n"/>
@@ -2880,14 +3388,18 @@
       <c r="F126" s="10" t="n"/>
       <c r="G126" s="12" t="n"/>
       <c r="H126" s="10" t="n"/>
-      <c r="I126" s="10" t="n"/>
+      <c r="I126" s="12" t="n"/>
       <c r="J126" s="12" t="n"/>
-      <c r="K126" s="10" t="n"/>
+      <c r="K126" s="13" t="n"/>
       <c r="L126" s="10" t="n"/>
-      <c r="M126" s="13" t="n"/>
-      <c r="N126" s="13" t="n"/>
-      <c r="O126" s="13" t="n"/>
-      <c r="P126" s="13" t="n"/>
+      <c r="M126" s="10" t="n"/>
+      <c r="N126" s="12" t="n"/>
+      <c r="O126" s="10" t="n"/>
+      <c r="P126" s="10" t="n"/>
+      <c r="Q126" s="13" t="n"/>
+      <c r="R126" s="13" t="n"/>
+      <c r="S126" s="13" t="n"/>
+      <c r="T126" s="13" t="n"/>
     </row>
     <row r="127" ht="23" customHeight="1">
       <c r="A127" s="6" t="n"/>
@@ -2898,14 +3410,18 @@
       <c r="F127" s="6" t="n"/>
       <c r="G127" s="8" t="n"/>
       <c r="H127" s="6" t="n"/>
-      <c r="I127" s="6" t="n"/>
+      <c r="I127" s="8" t="n"/>
       <c r="J127" s="8" t="n"/>
-      <c r="K127" s="6" t="n"/>
+      <c r="K127" s="9" t="n"/>
       <c r="L127" s="6" t="n"/>
-      <c r="M127" s="9" t="n"/>
-      <c r="N127" s="9" t="n"/>
-      <c r="O127" s="9" t="n"/>
-      <c r="P127" s="9" t="n"/>
+      <c r="M127" s="6" t="n"/>
+      <c r="N127" s="8" t="n"/>
+      <c r="O127" s="6" t="n"/>
+      <c r="P127" s="6" t="n"/>
+      <c r="Q127" s="9" t="n"/>
+      <c r="R127" s="9" t="n"/>
+      <c r="S127" s="9" t="n"/>
+      <c r="T127" s="9" t="n"/>
     </row>
     <row r="128" ht="23" customHeight="1">
       <c r="A128" s="10" t="n"/>
@@ -2916,14 +3432,18 @@
       <c r="F128" s="10" t="n"/>
       <c r="G128" s="12" t="n"/>
       <c r="H128" s="10" t="n"/>
-      <c r="I128" s="10" t="n"/>
+      <c r="I128" s="12" t="n"/>
       <c r="J128" s="12" t="n"/>
-      <c r="K128" s="10" t="n"/>
+      <c r="K128" s="13" t="n"/>
       <c r="L128" s="10" t="n"/>
-      <c r="M128" s="13" t="n"/>
-      <c r="N128" s="13" t="n"/>
-      <c r="O128" s="13" t="n"/>
-      <c r="P128" s="13" t="n"/>
+      <c r="M128" s="10" t="n"/>
+      <c r="N128" s="12" t="n"/>
+      <c r="O128" s="10" t="n"/>
+      <c r="P128" s="10" t="n"/>
+      <c r="Q128" s="13" t="n"/>
+      <c r="R128" s="13" t="n"/>
+      <c r="S128" s="13" t="n"/>
+      <c r="T128" s="13" t="n"/>
     </row>
     <row r="129" ht="23" customHeight="1">
       <c r="A129" s="6" t="n"/>
@@ -2934,14 +3454,18 @@
       <c r="F129" s="6" t="n"/>
       <c r="G129" s="8" t="n"/>
       <c r="H129" s="6" t="n"/>
-      <c r="I129" s="6" t="n"/>
+      <c r="I129" s="8" t="n"/>
       <c r="J129" s="8" t="n"/>
-      <c r="K129" s="6" t="n"/>
+      <c r="K129" s="9" t="n"/>
       <c r="L129" s="6" t="n"/>
-      <c r="M129" s="9" t="n"/>
-      <c r="N129" s="9" t="n"/>
-      <c r="O129" s="9" t="n"/>
-      <c r="P129" s="9" t="n"/>
+      <c r="M129" s="6" t="n"/>
+      <c r="N129" s="8" t="n"/>
+      <c r="O129" s="6" t="n"/>
+      <c r="P129" s="6" t="n"/>
+      <c r="Q129" s="9" t="n"/>
+      <c r="R129" s="9" t="n"/>
+      <c r="S129" s="9" t="n"/>
+      <c r="T129" s="9" t="n"/>
     </row>
     <row r="130" ht="23" customHeight="1">
       <c r="A130" s="10" t="n"/>
@@ -2952,14 +3476,18 @@
       <c r="F130" s="10" t="n"/>
       <c r="G130" s="12" t="n"/>
       <c r="H130" s="10" t="n"/>
-      <c r="I130" s="10" t="n"/>
+      <c r="I130" s="12" t="n"/>
       <c r="J130" s="12" t="n"/>
-      <c r="K130" s="10" t="n"/>
+      <c r="K130" s="13" t="n"/>
       <c r="L130" s="10" t="n"/>
-      <c r="M130" s="13" t="n"/>
-      <c r="N130" s="13" t="n"/>
-      <c r="O130" s="13" t="n"/>
-      <c r="P130" s="13" t="n"/>
+      <c r="M130" s="10" t="n"/>
+      <c r="N130" s="12" t="n"/>
+      <c r="O130" s="10" t="n"/>
+      <c r="P130" s="10" t="n"/>
+      <c r="Q130" s="13" t="n"/>
+      <c r="R130" s="13" t="n"/>
+      <c r="S130" s="13" t="n"/>
+      <c r="T130" s="13" t="n"/>
     </row>
     <row r="131" ht="23" customHeight="1">
       <c r="A131" s="6" t="n"/>
@@ -2970,14 +3498,18 @@
       <c r="F131" s="6" t="n"/>
       <c r="G131" s="8" t="n"/>
       <c r="H131" s="6" t="n"/>
-      <c r="I131" s="6" t="n"/>
+      <c r="I131" s="8" t="n"/>
       <c r="J131" s="8" t="n"/>
-      <c r="K131" s="6" t="n"/>
+      <c r="K131" s="9" t="n"/>
       <c r="L131" s="6" t="n"/>
-      <c r="M131" s="9" t="n"/>
-      <c r="N131" s="9" t="n"/>
-      <c r="O131" s="9" t="n"/>
-      <c r="P131" s="9" t="n"/>
+      <c r="M131" s="6" t="n"/>
+      <c r="N131" s="8" t="n"/>
+      <c r="O131" s="6" t="n"/>
+      <c r="P131" s="6" t="n"/>
+      <c r="Q131" s="9" t="n"/>
+      <c r="R131" s="9" t="n"/>
+      <c r="S131" s="9" t="n"/>
+      <c r="T131" s="9" t="n"/>
     </row>
     <row r="132" ht="23" customHeight="1">
       <c r="A132" s="10" t="n"/>
@@ -2988,14 +3520,18 @@
       <c r="F132" s="10" t="n"/>
       <c r="G132" s="12" t="n"/>
       <c r="H132" s="10" t="n"/>
-      <c r="I132" s="10" t="n"/>
+      <c r="I132" s="12" t="n"/>
       <c r="J132" s="12" t="n"/>
-      <c r="K132" s="10" t="n"/>
+      <c r="K132" s="13" t="n"/>
       <c r="L132" s="10" t="n"/>
-      <c r="M132" s="13" t="n"/>
-      <c r="N132" s="13" t="n"/>
-      <c r="O132" s="13" t="n"/>
-      <c r="P132" s="13" t="n"/>
+      <c r="M132" s="10" t="n"/>
+      <c r="N132" s="12" t="n"/>
+      <c r="O132" s="10" t="n"/>
+      <c r="P132" s="10" t="n"/>
+      <c r="Q132" s="13" t="n"/>
+      <c r="R132" s="13" t="n"/>
+      <c r="S132" s="13" t="n"/>
+      <c r="T132" s="13" t="n"/>
     </row>
     <row r="133" ht="23" customHeight="1">
       <c r="A133" s="6" t="n"/>
@@ -3006,14 +3542,18 @@
       <c r="F133" s="6" t="n"/>
       <c r="G133" s="8" t="n"/>
       <c r="H133" s="6" t="n"/>
-      <c r="I133" s="6" t="n"/>
+      <c r="I133" s="8" t="n"/>
       <c r="J133" s="8" t="n"/>
-      <c r="K133" s="6" t="n"/>
+      <c r="K133" s="9" t="n"/>
       <c r="L133" s="6" t="n"/>
-      <c r="M133" s="9" t="n"/>
-      <c r="N133" s="9" t="n"/>
-      <c r="O133" s="9" t="n"/>
-      <c r="P133" s="9" t="n"/>
+      <c r="M133" s="6" t="n"/>
+      <c r="N133" s="8" t="n"/>
+      <c r="O133" s="6" t="n"/>
+      <c r="P133" s="6" t="n"/>
+      <c r="Q133" s="9" t="n"/>
+      <c r="R133" s="9" t="n"/>
+      <c r="S133" s="9" t="n"/>
+      <c r="T133" s="9" t="n"/>
     </row>
     <row r="134" ht="23" customHeight="1">
       <c r="A134" s="10" t="n"/>
@@ -3024,14 +3564,18 @@
       <c r="F134" s="10" t="n"/>
       <c r="G134" s="12" t="n"/>
       <c r="H134" s="10" t="n"/>
-      <c r="I134" s="10" t="n"/>
+      <c r="I134" s="12" t="n"/>
       <c r="J134" s="12" t="n"/>
-      <c r="K134" s="10" t="n"/>
+      <c r="K134" s="13" t="n"/>
       <c r="L134" s="10" t="n"/>
-      <c r="M134" s="13" t="n"/>
-      <c r="N134" s="13" t="n"/>
-      <c r="O134" s="13" t="n"/>
-      <c r="P134" s="13" t="n"/>
+      <c r="M134" s="10" t="n"/>
+      <c r="N134" s="12" t="n"/>
+      <c r="O134" s="10" t="n"/>
+      <c r="P134" s="10" t="n"/>
+      <c r="Q134" s="13" t="n"/>
+      <c r="R134" s="13" t="n"/>
+      <c r="S134" s="13" t="n"/>
+      <c r="T134" s="13" t="n"/>
     </row>
     <row r="135" ht="23" customHeight="1">
       <c r="A135" s="6" t="n"/>
@@ -3042,14 +3586,18 @@
       <c r="F135" s="6" t="n"/>
       <c r="G135" s="8" t="n"/>
       <c r="H135" s="6" t="n"/>
-      <c r="I135" s="6" t="n"/>
+      <c r="I135" s="8" t="n"/>
       <c r="J135" s="8" t="n"/>
-      <c r="K135" s="6" t="n"/>
+      <c r="K135" s="9" t="n"/>
       <c r="L135" s="6" t="n"/>
-      <c r="M135" s="9" t="n"/>
-      <c r="N135" s="9" t="n"/>
-      <c r="O135" s="9" t="n"/>
-      <c r="P135" s="9" t="n"/>
+      <c r="M135" s="6" t="n"/>
+      <c r="N135" s="8" t="n"/>
+      <c r="O135" s="6" t="n"/>
+      <c r="P135" s="6" t="n"/>
+      <c r="Q135" s="9" t="n"/>
+      <c r="R135" s="9" t="n"/>
+      <c r="S135" s="9" t="n"/>
+      <c r="T135" s="9" t="n"/>
     </row>
     <row r="136" ht="23" customHeight="1">
       <c r="A136" s="10" t="n"/>
@@ -3060,14 +3608,18 @@
       <c r="F136" s="10" t="n"/>
       <c r="G136" s="12" t="n"/>
       <c r="H136" s="10" t="n"/>
-      <c r="I136" s="10" t="n"/>
+      <c r="I136" s="12" t="n"/>
       <c r="J136" s="12" t="n"/>
-      <c r="K136" s="10" t="n"/>
+      <c r="K136" s="13" t="n"/>
       <c r="L136" s="10" t="n"/>
-      <c r="M136" s="13" t="n"/>
-      <c r="N136" s="13" t="n"/>
-      <c r="O136" s="13" t="n"/>
-      <c r="P136" s="13" t="n"/>
+      <c r="M136" s="10" t="n"/>
+      <c r="N136" s="12" t="n"/>
+      <c r="O136" s="10" t="n"/>
+      <c r="P136" s="10" t="n"/>
+      <c r="Q136" s="13" t="n"/>
+      <c r="R136" s="13" t="n"/>
+      <c r="S136" s="13" t="n"/>
+      <c r="T136" s="13" t="n"/>
     </row>
     <row r="137" ht="23" customHeight="1">
       <c r="A137" s="6" t="n"/>
@@ -3078,14 +3630,18 @@
       <c r="F137" s="6" t="n"/>
       <c r="G137" s="8" t="n"/>
       <c r="H137" s="6" t="n"/>
-      <c r="I137" s="6" t="n"/>
+      <c r="I137" s="8" t="n"/>
       <c r="J137" s="8" t="n"/>
-      <c r="K137" s="6" t="n"/>
+      <c r="K137" s="9" t="n"/>
       <c r="L137" s="6" t="n"/>
-      <c r="M137" s="9" t="n"/>
-      <c r="N137" s="9" t="n"/>
-      <c r="O137" s="9" t="n"/>
-      <c r="P137" s="9" t="n"/>
+      <c r="M137" s="6" t="n"/>
+      <c r="N137" s="8" t="n"/>
+      <c r="O137" s="6" t="n"/>
+      <c r="P137" s="6" t="n"/>
+      <c r="Q137" s="9" t="n"/>
+      <c r="R137" s="9" t="n"/>
+      <c r="S137" s="9" t="n"/>
+      <c r="T137" s="9" t="n"/>
     </row>
     <row r="138" ht="23" customHeight="1">
       <c r="A138" s="10" t="n"/>
@@ -3096,14 +3652,18 @@
       <c r="F138" s="10" t="n"/>
       <c r="G138" s="12" t="n"/>
       <c r="H138" s="10" t="n"/>
-      <c r="I138" s="10" t="n"/>
+      <c r="I138" s="12" t="n"/>
       <c r="J138" s="12" t="n"/>
-      <c r="K138" s="10" t="n"/>
+      <c r="K138" s="13" t="n"/>
       <c r="L138" s="10" t="n"/>
-      <c r="M138" s="13" t="n"/>
-      <c r="N138" s="13" t="n"/>
-      <c r="O138" s="13" t="n"/>
-      <c r="P138" s="13" t="n"/>
+      <c r="M138" s="10" t="n"/>
+      <c r="N138" s="12" t="n"/>
+      <c r="O138" s="10" t="n"/>
+      <c r="P138" s="10" t="n"/>
+      <c r="Q138" s="13" t="n"/>
+      <c r="R138" s="13" t="n"/>
+      <c r="S138" s="13" t="n"/>
+      <c r="T138" s="13" t="n"/>
     </row>
     <row r="139" ht="23" customHeight="1">
       <c r="A139" s="6" t="n"/>
@@ -3114,14 +3674,18 @@
       <c r="F139" s="6" t="n"/>
       <c r="G139" s="8" t="n"/>
       <c r="H139" s="6" t="n"/>
-      <c r="I139" s="6" t="n"/>
+      <c r="I139" s="8" t="n"/>
       <c r="J139" s="8" t="n"/>
-      <c r="K139" s="6" t="n"/>
+      <c r="K139" s="9" t="n"/>
       <c r="L139" s="6" t="n"/>
-      <c r="M139" s="9" t="n"/>
-      <c r="N139" s="9" t="n"/>
-      <c r="O139" s="9" t="n"/>
-      <c r="P139" s="9" t="n"/>
+      <c r="M139" s="6" t="n"/>
+      <c r="N139" s="8" t="n"/>
+      <c r="O139" s="6" t="n"/>
+      <c r="P139" s="6" t="n"/>
+      <c r="Q139" s="9" t="n"/>
+      <c r="R139" s="9" t="n"/>
+      <c r="S139" s="9" t="n"/>
+      <c r="T139" s="9" t="n"/>
     </row>
     <row r="140" ht="23" customHeight="1">
       <c r="A140" s="10" t="n"/>
@@ -3132,14 +3696,18 @@
       <c r="F140" s="10" t="n"/>
       <c r="G140" s="12" t="n"/>
       <c r="H140" s="10" t="n"/>
-      <c r="I140" s="10" t="n"/>
+      <c r="I140" s="12" t="n"/>
       <c r="J140" s="12" t="n"/>
-      <c r="K140" s="10" t="n"/>
+      <c r="K140" s="13" t="n"/>
       <c r="L140" s="10" t="n"/>
-      <c r="M140" s="13" t="n"/>
-      <c r="N140" s="13" t="n"/>
-      <c r="O140" s="13" t="n"/>
-      <c r="P140" s="13" t="n"/>
+      <c r="M140" s="10" t="n"/>
+      <c r="N140" s="12" t="n"/>
+      <c r="O140" s="10" t="n"/>
+      <c r="P140" s="10" t="n"/>
+      <c r="Q140" s="13" t="n"/>
+      <c r="R140" s="13" t="n"/>
+      <c r="S140" s="13" t="n"/>
+      <c r="T140" s="13" t="n"/>
     </row>
     <row r="141" ht="23" customHeight="1">
       <c r="A141" s="6" t="n"/>
@@ -3150,14 +3718,18 @@
       <c r="F141" s="6" t="n"/>
       <c r="G141" s="8" t="n"/>
       <c r="H141" s="6" t="n"/>
-      <c r="I141" s="6" t="n"/>
+      <c r="I141" s="8" t="n"/>
       <c r="J141" s="8" t="n"/>
-      <c r="K141" s="6" t="n"/>
+      <c r="K141" s="9" t="n"/>
       <c r="L141" s="6" t="n"/>
-      <c r="M141" s="9" t="n"/>
-      <c r="N141" s="9" t="n"/>
-      <c r="O141" s="9" t="n"/>
-      <c r="P141" s="9" t="n"/>
+      <c r="M141" s="6" t="n"/>
+      <c r="N141" s="8" t="n"/>
+      <c r="O141" s="6" t="n"/>
+      <c r="P141" s="6" t="n"/>
+      <c r="Q141" s="9" t="n"/>
+      <c r="R141" s="9" t="n"/>
+      <c r="S141" s="9" t="n"/>
+      <c r="T141" s="9" t="n"/>
     </row>
     <row r="142" ht="23" customHeight="1">
       <c r="A142" s="10" t="n"/>
@@ -3168,14 +3740,18 @@
       <c r="F142" s="10" t="n"/>
       <c r="G142" s="12" t="n"/>
       <c r="H142" s="10" t="n"/>
-      <c r="I142" s="10" t="n"/>
+      <c r="I142" s="12" t="n"/>
       <c r="J142" s="12" t="n"/>
-      <c r="K142" s="10" t="n"/>
+      <c r="K142" s="13" t="n"/>
       <c r="L142" s="10" t="n"/>
-      <c r="M142" s="13" t="n"/>
-      <c r="N142" s="13" t="n"/>
-      <c r="O142" s="13" t="n"/>
-      <c r="P142" s="13" t="n"/>
+      <c r="M142" s="10" t="n"/>
+      <c r="N142" s="12" t="n"/>
+      <c r="O142" s="10" t="n"/>
+      <c r="P142" s="10" t="n"/>
+      <c r="Q142" s="13" t="n"/>
+      <c r="R142" s="13" t="n"/>
+      <c r="S142" s="13" t="n"/>
+      <c r="T142" s="13" t="n"/>
     </row>
     <row r="143" ht="23" customHeight="1">
       <c r="A143" s="6" t="n"/>
@@ -3186,14 +3762,18 @@
       <c r="F143" s="6" t="n"/>
       <c r="G143" s="8" t="n"/>
       <c r="H143" s="6" t="n"/>
-      <c r="I143" s="6" t="n"/>
+      <c r="I143" s="8" t="n"/>
       <c r="J143" s="8" t="n"/>
-      <c r="K143" s="6" t="n"/>
+      <c r="K143" s="9" t="n"/>
       <c r="L143" s="6" t="n"/>
-      <c r="M143" s="9" t="n"/>
-      <c r="N143" s="9" t="n"/>
-      <c r="O143" s="9" t="n"/>
-      <c r="P143" s="9" t="n"/>
+      <c r="M143" s="6" t="n"/>
+      <c r="N143" s="8" t="n"/>
+      <c r="O143" s="6" t="n"/>
+      <c r="P143" s="6" t="n"/>
+      <c r="Q143" s="9" t="n"/>
+      <c r="R143" s="9" t="n"/>
+      <c r="S143" s="9" t="n"/>
+      <c r="T143" s="9" t="n"/>
     </row>
     <row r="144" ht="23" customHeight="1">
       <c r="A144" s="10" t="n"/>
@@ -3204,14 +3784,18 @@
       <c r="F144" s="10" t="n"/>
       <c r="G144" s="12" t="n"/>
       <c r="H144" s="10" t="n"/>
-      <c r="I144" s="10" t="n"/>
+      <c r="I144" s="12" t="n"/>
       <c r="J144" s="12" t="n"/>
-      <c r="K144" s="10" t="n"/>
+      <c r="K144" s="13" t="n"/>
       <c r="L144" s="10" t="n"/>
-      <c r="M144" s="13" t="n"/>
-      <c r="N144" s="13" t="n"/>
-      <c r="O144" s="13" t="n"/>
-      <c r="P144" s="13" t="n"/>
+      <c r="M144" s="10" t="n"/>
+      <c r="N144" s="12" t="n"/>
+      <c r="O144" s="10" t="n"/>
+      <c r="P144" s="10" t="n"/>
+      <c r="Q144" s="13" t="n"/>
+      <c r="R144" s="13" t="n"/>
+      <c r="S144" s="13" t="n"/>
+      <c r="T144" s="13" t="n"/>
     </row>
     <row r="145" ht="23" customHeight="1">
       <c r="A145" s="6" t="n"/>
@@ -3222,14 +3806,18 @@
       <c r="F145" s="6" t="n"/>
       <c r="G145" s="8" t="n"/>
       <c r="H145" s="6" t="n"/>
-      <c r="I145" s="6" t="n"/>
+      <c r="I145" s="8" t="n"/>
       <c r="J145" s="8" t="n"/>
-      <c r="K145" s="6" t="n"/>
+      <c r="K145" s="9" t="n"/>
       <c r="L145" s="6" t="n"/>
-      <c r="M145" s="9" t="n"/>
-      <c r="N145" s="9" t="n"/>
-      <c r="O145" s="9" t="n"/>
-      <c r="P145" s="9" t="n"/>
+      <c r="M145" s="6" t="n"/>
+      <c r="N145" s="8" t="n"/>
+      <c r="O145" s="6" t="n"/>
+      <c r="P145" s="6" t="n"/>
+      <c r="Q145" s="9" t="n"/>
+      <c r="R145" s="9" t="n"/>
+      <c r="S145" s="9" t="n"/>
+      <c r="T145" s="9" t="n"/>
     </row>
     <row r="146" ht="23" customHeight="1">
       <c r="A146" s="10" t="n"/>
@@ -3240,14 +3828,18 @@
       <c r="F146" s="10" t="n"/>
       <c r="G146" s="12" t="n"/>
       <c r="H146" s="10" t="n"/>
-      <c r="I146" s="10" t="n"/>
+      <c r="I146" s="12" t="n"/>
       <c r="J146" s="12" t="n"/>
-      <c r="K146" s="10" t="n"/>
+      <c r="K146" s="13" t="n"/>
       <c r="L146" s="10" t="n"/>
-      <c r="M146" s="13" t="n"/>
-      <c r="N146" s="13" t="n"/>
-      <c r="O146" s="13" t="n"/>
-      <c r="P146" s="13" t="n"/>
+      <c r="M146" s="10" t="n"/>
+      <c r="N146" s="12" t="n"/>
+      <c r="O146" s="10" t="n"/>
+      <c r="P146" s="10" t="n"/>
+      <c r="Q146" s="13" t="n"/>
+      <c r="R146" s="13" t="n"/>
+      <c r="S146" s="13" t="n"/>
+      <c r="T146" s="13" t="n"/>
     </row>
     <row r="147" ht="23" customHeight="1">
       <c r="A147" s="6" t="n"/>
@@ -3258,14 +3850,18 @@
       <c r="F147" s="6" t="n"/>
       <c r="G147" s="8" t="n"/>
       <c r="H147" s="6" t="n"/>
-      <c r="I147" s="6" t="n"/>
+      <c r="I147" s="8" t="n"/>
       <c r="J147" s="8" t="n"/>
-      <c r="K147" s="6" t="n"/>
+      <c r="K147" s="9" t="n"/>
       <c r="L147" s="6" t="n"/>
-      <c r="M147" s="9" t="n"/>
-      <c r="N147" s="9" t="n"/>
-      <c r="O147" s="9" t="n"/>
-      <c r="P147" s="9" t="n"/>
+      <c r="M147" s="6" t="n"/>
+      <c r="N147" s="8" t="n"/>
+      <c r="O147" s="6" t="n"/>
+      <c r="P147" s="6" t="n"/>
+      <c r="Q147" s="9" t="n"/>
+      <c r="R147" s="9" t="n"/>
+      <c r="S147" s="9" t="n"/>
+      <c r="T147" s="9" t="n"/>
     </row>
     <row r="148" ht="23" customHeight="1">
       <c r="A148" s="10" t="n"/>
@@ -3276,14 +3872,18 @@
       <c r="F148" s="10" t="n"/>
       <c r="G148" s="12" t="n"/>
       <c r="H148" s="10" t="n"/>
-      <c r="I148" s="10" t="n"/>
+      <c r="I148" s="12" t="n"/>
       <c r="J148" s="12" t="n"/>
-      <c r="K148" s="10" t="n"/>
+      <c r="K148" s="13" t="n"/>
       <c r="L148" s="10" t="n"/>
-      <c r="M148" s="13" t="n"/>
-      <c r="N148" s="13" t="n"/>
-      <c r="O148" s="13" t="n"/>
-      <c r="P148" s="13" t="n"/>
+      <c r="M148" s="10" t="n"/>
+      <c r="N148" s="12" t="n"/>
+      <c r="O148" s="10" t="n"/>
+      <c r="P148" s="10" t="n"/>
+      <c r="Q148" s="13" t="n"/>
+      <c r="R148" s="13" t="n"/>
+      <c r="S148" s="13" t="n"/>
+      <c r="T148" s="13" t="n"/>
     </row>
     <row r="149" ht="23" customHeight="1">
       <c r="A149" s="6" t="n"/>
@@ -3294,14 +3894,18 @@
       <c r="F149" s="6" t="n"/>
       <c r="G149" s="8" t="n"/>
       <c r="H149" s="6" t="n"/>
-      <c r="I149" s="6" t="n"/>
+      <c r="I149" s="8" t="n"/>
       <c r="J149" s="8" t="n"/>
-      <c r="K149" s="6" t="n"/>
+      <c r="K149" s="9" t="n"/>
       <c r="L149" s="6" t="n"/>
-      <c r="M149" s="9" t="n"/>
-      <c r="N149" s="9" t="n"/>
-      <c r="O149" s="9" t="n"/>
-      <c r="P149" s="9" t="n"/>
+      <c r="M149" s="6" t="n"/>
+      <c r="N149" s="8" t="n"/>
+      <c r="O149" s="6" t="n"/>
+      <c r="P149" s="6" t="n"/>
+      <c r="Q149" s="9" t="n"/>
+      <c r="R149" s="9" t="n"/>
+      <c r="S149" s="9" t="n"/>
+      <c r="T149" s="9" t="n"/>
     </row>
     <row r="150" ht="23" customHeight="1">
       <c r="A150" s="10" t="n"/>
@@ -3312,14 +3916,18 @@
       <c r="F150" s="10" t="n"/>
       <c r="G150" s="12" t="n"/>
       <c r="H150" s="10" t="n"/>
-      <c r="I150" s="10" t="n"/>
+      <c r="I150" s="12" t="n"/>
       <c r="J150" s="12" t="n"/>
-      <c r="K150" s="10" t="n"/>
+      <c r="K150" s="13" t="n"/>
       <c r="L150" s="10" t="n"/>
-      <c r="M150" s="13" t="n"/>
-      <c r="N150" s="13" t="n"/>
-      <c r="O150" s="13" t="n"/>
-      <c r="P150" s="13" t="n"/>
+      <c r="M150" s="10" t="n"/>
+      <c r="N150" s="12" t="n"/>
+      <c r="O150" s="10" t="n"/>
+      <c r="P150" s="10" t="n"/>
+      <c r="Q150" s="13" t="n"/>
+      <c r="R150" s="13" t="n"/>
+      <c r="S150" s="13" t="n"/>
+      <c r="T150" s="13" t="n"/>
     </row>
     <row r="151" ht="23" customHeight="1">
       <c r="A151" s="6" t="n"/>
@@ -3330,14 +3938,18 @@
       <c r="F151" s="6" t="n"/>
       <c r="G151" s="8" t="n"/>
       <c r="H151" s="6" t="n"/>
-      <c r="I151" s="6" t="n"/>
+      <c r="I151" s="8" t="n"/>
       <c r="J151" s="8" t="n"/>
-      <c r="K151" s="6" t="n"/>
+      <c r="K151" s="9" t="n"/>
       <c r="L151" s="6" t="n"/>
-      <c r="M151" s="9" t="n"/>
-      <c r="N151" s="9" t="n"/>
-      <c r="O151" s="9" t="n"/>
-      <c r="P151" s="9" t="n"/>
+      <c r="M151" s="6" t="n"/>
+      <c r="N151" s="8" t="n"/>
+      <c r="O151" s="6" t="n"/>
+      <c r="P151" s="6" t="n"/>
+      <c r="Q151" s="9" t="n"/>
+      <c r="R151" s="9" t="n"/>
+      <c r="S151" s="9" t="n"/>
+      <c r="T151" s="9" t="n"/>
     </row>
     <row r="152" ht="23" customHeight="1">
       <c r="A152" s="10" t="n"/>
@@ -3348,14 +3960,18 @@
       <c r="F152" s="10" t="n"/>
       <c r="G152" s="12" t="n"/>
       <c r="H152" s="10" t="n"/>
-      <c r="I152" s="10" t="n"/>
+      <c r="I152" s="12" t="n"/>
       <c r="J152" s="12" t="n"/>
-      <c r="K152" s="10" t="n"/>
+      <c r="K152" s="13" t="n"/>
       <c r="L152" s="10" t="n"/>
-      <c r="M152" s="13" t="n"/>
-      <c r="N152" s="13" t="n"/>
-      <c r="O152" s="13" t="n"/>
-      <c r="P152" s="13" t="n"/>
+      <c r="M152" s="10" t="n"/>
+      <c r="N152" s="12" t="n"/>
+      <c r="O152" s="10" t="n"/>
+      <c r="P152" s="10" t="n"/>
+      <c r="Q152" s="13" t="n"/>
+      <c r="R152" s="13" t="n"/>
+      <c r="S152" s="13" t="n"/>
+      <c r="T152" s="13" t="n"/>
     </row>
     <row r="153" ht="23" customHeight="1">
       <c r="A153" s="6" t="n"/>
@@ -3366,14 +3982,18 @@
       <c r="F153" s="6" t="n"/>
       <c r="G153" s="8" t="n"/>
       <c r="H153" s="6" t="n"/>
-      <c r="I153" s="6" t="n"/>
+      <c r="I153" s="8" t="n"/>
       <c r="J153" s="8" t="n"/>
-      <c r="K153" s="6" t="n"/>
+      <c r="K153" s="9" t="n"/>
       <c r="L153" s="6" t="n"/>
-      <c r="M153" s="9" t="n"/>
-      <c r="N153" s="9" t="n"/>
-      <c r="O153" s="9" t="n"/>
-      <c r="P153" s="9" t="n"/>
+      <c r="M153" s="6" t="n"/>
+      <c r="N153" s="8" t="n"/>
+      <c r="O153" s="6" t="n"/>
+      <c r="P153" s="6" t="n"/>
+      <c r="Q153" s="9" t="n"/>
+      <c r="R153" s="9" t="n"/>
+      <c r="S153" s="9" t="n"/>
+      <c r="T153" s="9" t="n"/>
     </row>
     <row r="154" ht="23" customHeight="1">
       <c r="A154" s="10" t="n"/>
@@ -3384,14 +4004,18 @@
       <c r="F154" s="10" t="n"/>
       <c r="G154" s="12" t="n"/>
       <c r="H154" s="10" t="n"/>
-      <c r="I154" s="10" t="n"/>
+      <c r="I154" s="12" t="n"/>
       <c r="J154" s="12" t="n"/>
-      <c r="K154" s="10" t="n"/>
+      <c r="K154" s="13" t="n"/>
       <c r="L154" s="10" t="n"/>
-      <c r="M154" s="13" t="n"/>
-      <c r="N154" s="13" t="n"/>
-      <c r="O154" s="13" t="n"/>
-      <c r="P154" s="13" t="n"/>
+      <c r="M154" s="10" t="n"/>
+      <c r="N154" s="12" t="n"/>
+      <c r="O154" s="10" t="n"/>
+      <c r="P154" s="10" t="n"/>
+      <c r="Q154" s="13" t="n"/>
+      <c r="R154" s="13" t="n"/>
+      <c r="S154" s="13" t="n"/>
+      <c r="T154" s="13" t="n"/>
     </row>
     <row r="155" ht="23" customHeight="1">
       <c r="A155" s="6" t="n"/>
@@ -3402,14 +4026,18 @@
       <c r="F155" s="6" t="n"/>
       <c r="G155" s="8" t="n"/>
       <c r="H155" s="6" t="n"/>
-      <c r="I155" s="6" t="n"/>
+      <c r="I155" s="8" t="n"/>
       <c r="J155" s="8" t="n"/>
-      <c r="K155" s="6" t="n"/>
+      <c r="K155" s="9" t="n"/>
       <c r="L155" s="6" t="n"/>
-      <c r="M155" s="9" t="n"/>
-      <c r="N155" s="9" t="n"/>
-      <c r="O155" s="9" t="n"/>
-      <c r="P155" s="9" t="n"/>
+      <c r="M155" s="6" t="n"/>
+      <c r="N155" s="8" t="n"/>
+      <c r="O155" s="6" t="n"/>
+      <c r="P155" s="6" t="n"/>
+      <c r="Q155" s="9" t="n"/>
+      <c r="R155" s="9" t="n"/>
+      <c r="S155" s="9" t="n"/>
+      <c r="T155" s="9" t="n"/>
     </row>
     <row r="156" ht="23" customHeight="1">
       <c r="A156" s="10" t="n"/>
@@ -3420,14 +4048,18 @@
       <c r="F156" s="10" t="n"/>
       <c r="G156" s="12" t="n"/>
       <c r="H156" s="10" t="n"/>
-      <c r="I156" s="10" t="n"/>
+      <c r="I156" s="12" t="n"/>
       <c r="J156" s="12" t="n"/>
-      <c r="K156" s="10" t="n"/>
+      <c r="K156" s="13" t="n"/>
       <c r="L156" s="10" t="n"/>
-      <c r="M156" s="13" t="n"/>
-      <c r="N156" s="13" t="n"/>
-      <c r="O156" s="13" t="n"/>
-      <c r="P156" s="13" t="n"/>
+      <c r="M156" s="10" t="n"/>
+      <c r="N156" s="12" t="n"/>
+      <c r="O156" s="10" t="n"/>
+      <c r="P156" s="10" t="n"/>
+      <c r="Q156" s="13" t="n"/>
+      <c r="R156" s="13" t="n"/>
+      <c r="S156" s="13" t="n"/>
+      <c r="T156" s="13" t="n"/>
     </row>
     <row r="157" ht="23" customHeight="1">
       <c r="A157" s="6" t="n"/>
@@ -3438,14 +4070,18 @@
       <c r="F157" s="6" t="n"/>
       <c r="G157" s="8" t="n"/>
       <c r="H157" s="6" t="n"/>
-      <c r="I157" s="6" t="n"/>
+      <c r="I157" s="8" t="n"/>
       <c r="J157" s="8" t="n"/>
-      <c r="K157" s="6" t="n"/>
+      <c r="K157" s="9" t="n"/>
       <c r="L157" s="6" t="n"/>
-      <c r="M157" s="9" t="n"/>
-      <c r="N157" s="9" t="n"/>
-      <c r="O157" s="9" t="n"/>
-      <c r="P157" s="9" t="n"/>
+      <c r="M157" s="6" t="n"/>
+      <c r="N157" s="8" t="n"/>
+      <c r="O157" s="6" t="n"/>
+      <c r="P157" s="6" t="n"/>
+      <c r="Q157" s="9" t="n"/>
+      <c r="R157" s="9" t="n"/>
+      <c r="S157" s="9" t="n"/>
+      <c r="T157" s="9" t="n"/>
     </row>
     <row r="158" ht="23" customHeight="1">
       <c r="A158" s="10" t="n"/>
@@ -3456,14 +4092,18 @@
       <c r="F158" s="10" t="n"/>
       <c r="G158" s="12" t="n"/>
       <c r="H158" s="10" t="n"/>
-      <c r="I158" s="10" t="n"/>
+      <c r="I158" s="12" t="n"/>
       <c r="J158" s="12" t="n"/>
-      <c r="K158" s="10" t="n"/>
+      <c r="K158" s="13" t="n"/>
       <c r="L158" s="10" t="n"/>
-      <c r="M158" s="13" t="n"/>
-      <c r="N158" s="13" t="n"/>
-      <c r="O158" s="13" t="n"/>
-      <c r="P158" s="13" t="n"/>
+      <c r="M158" s="10" t="n"/>
+      <c r="N158" s="12" t="n"/>
+      <c r="O158" s="10" t="n"/>
+      <c r="P158" s="10" t="n"/>
+      <c r="Q158" s="13" t="n"/>
+      <c r="R158" s="13" t="n"/>
+      <c r="S158" s="13" t="n"/>
+      <c r="T158" s="13" t="n"/>
     </row>
     <row r="159" ht="23" customHeight="1">
       <c r="A159" s="6" t="n"/>
@@ -3474,14 +4114,18 @@
       <c r="F159" s="6" t="n"/>
       <c r="G159" s="8" t="n"/>
       <c r="H159" s="6" t="n"/>
-      <c r="I159" s="6" t="n"/>
+      <c r="I159" s="8" t="n"/>
       <c r="J159" s="8" t="n"/>
-      <c r="K159" s="6" t="n"/>
+      <c r="K159" s="9" t="n"/>
       <c r="L159" s="6" t="n"/>
-      <c r="M159" s="9" t="n"/>
-      <c r="N159" s="9" t="n"/>
-      <c r="O159" s="9" t="n"/>
-      <c r="P159" s="9" t="n"/>
+      <c r="M159" s="6" t="n"/>
+      <c r="N159" s="8" t="n"/>
+      <c r="O159" s="6" t="n"/>
+      <c r="P159" s="6" t="n"/>
+      <c r="Q159" s="9" t="n"/>
+      <c r="R159" s="9" t="n"/>
+      <c r="S159" s="9" t="n"/>
+      <c r="T159" s="9" t="n"/>
     </row>
     <row r="160" ht="23" customHeight="1">
       <c r="A160" s="10" t="n"/>
@@ -3492,14 +4136,18 @@
       <c r="F160" s="10" t="n"/>
       <c r="G160" s="12" t="n"/>
       <c r="H160" s="10" t="n"/>
-      <c r="I160" s="10" t="n"/>
+      <c r="I160" s="12" t="n"/>
       <c r="J160" s="12" t="n"/>
-      <c r="K160" s="10" t="n"/>
+      <c r="K160" s="13" t="n"/>
       <c r="L160" s="10" t="n"/>
-      <c r="M160" s="13" t="n"/>
-      <c r="N160" s="13" t="n"/>
-      <c r="O160" s="13" t="n"/>
-      <c r="P160" s="13" t="n"/>
+      <c r="M160" s="10" t="n"/>
+      <c r="N160" s="12" t="n"/>
+      <c r="O160" s="10" t="n"/>
+      <c r="P160" s="10" t="n"/>
+      <c r="Q160" s="13" t="n"/>
+      <c r="R160" s="13" t="n"/>
+      <c r="S160" s="13" t="n"/>
+      <c r="T160" s="13" t="n"/>
     </row>
     <row r="161" ht="23" customHeight="1">
       <c r="A161" s="6" t="n"/>
@@ -3510,14 +4158,18 @@
       <c r="F161" s="6" t="n"/>
       <c r="G161" s="8" t="n"/>
       <c r="H161" s="6" t="n"/>
-      <c r="I161" s="6" t="n"/>
+      <c r="I161" s="8" t="n"/>
       <c r="J161" s="8" t="n"/>
-      <c r="K161" s="6" t="n"/>
+      <c r="K161" s="9" t="n"/>
       <c r="L161" s="6" t="n"/>
-      <c r="M161" s="9" t="n"/>
-      <c r="N161" s="9" t="n"/>
-      <c r="O161" s="9" t="n"/>
-      <c r="P161" s="9" t="n"/>
+      <c r="M161" s="6" t="n"/>
+      <c r="N161" s="8" t="n"/>
+      <c r="O161" s="6" t="n"/>
+      <c r="P161" s="6" t="n"/>
+      <c r="Q161" s="9" t="n"/>
+      <c r="R161" s="9" t="n"/>
+      <c r="S161" s="9" t="n"/>
+      <c r="T161" s="9" t="n"/>
     </row>
     <row r="162" ht="23" customHeight="1">
       <c r="A162" s="10" t="n"/>
@@ -3528,14 +4180,18 @@
       <c r="F162" s="10" t="n"/>
       <c r="G162" s="12" t="n"/>
       <c r="H162" s="10" t="n"/>
-      <c r="I162" s="10" t="n"/>
+      <c r="I162" s="12" t="n"/>
       <c r="J162" s="12" t="n"/>
-      <c r="K162" s="10" t="n"/>
+      <c r="K162" s="13" t="n"/>
       <c r="L162" s="10" t="n"/>
-      <c r="M162" s="13" t="n"/>
-      <c r="N162" s="13" t="n"/>
-      <c r="O162" s="13" t="n"/>
-      <c r="P162" s="13" t="n"/>
+      <c r="M162" s="10" t="n"/>
+      <c r="N162" s="12" t="n"/>
+      <c r="O162" s="10" t="n"/>
+      <c r="P162" s="10" t="n"/>
+      <c r="Q162" s="13" t="n"/>
+      <c r="R162" s="13" t="n"/>
+      <c r="S162" s="13" t="n"/>
+      <c r="T162" s="13" t="n"/>
     </row>
     <row r="163" ht="23" customHeight="1">
       <c r="A163" s="6" t="n"/>
@@ -3546,14 +4202,18 @@
       <c r="F163" s="6" t="n"/>
       <c r="G163" s="8" t="n"/>
       <c r="H163" s="6" t="n"/>
-      <c r="I163" s="6" t="n"/>
+      <c r="I163" s="8" t="n"/>
       <c r="J163" s="8" t="n"/>
-      <c r="K163" s="6" t="n"/>
+      <c r="K163" s="9" t="n"/>
       <c r="L163" s="6" t="n"/>
-      <c r="M163" s="9" t="n"/>
-      <c r="N163" s="9" t="n"/>
-      <c r="O163" s="9" t="n"/>
-      <c r="P163" s="9" t="n"/>
+      <c r="M163" s="6" t="n"/>
+      <c r="N163" s="8" t="n"/>
+      <c r="O163" s="6" t="n"/>
+      <c r="P163" s="6" t="n"/>
+      <c r="Q163" s="9" t="n"/>
+      <c r="R163" s="9" t="n"/>
+      <c r="S163" s="9" t="n"/>
+      <c r="T163" s="9" t="n"/>
     </row>
     <row r="164" ht="23" customHeight="1">
       <c r="A164" s="10" t="n"/>
@@ -3564,14 +4224,18 @@
       <c r="F164" s="10" t="n"/>
       <c r="G164" s="12" t="n"/>
       <c r="H164" s="10" t="n"/>
-      <c r="I164" s="10" t="n"/>
+      <c r="I164" s="12" t="n"/>
       <c r="J164" s="12" t="n"/>
-      <c r="K164" s="10" t="n"/>
+      <c r="K164" s="13" t="n"/>
       <c r="L164" s="10" t="n"/>
-      <c r="M164" s="13" t="n"/>
-      <c r="N164" s="13" t="n"/>
-      <c r="O164" s="13" t="n"/>
-      <c r="P164" s="13" t="n"/>
+      <c r="M164" s="10" t="n"/>
+      <c r="N164" s="12" t="n"/>
+      <c r="O164" s="10" t="n"/>
+      <c r="P164" s="10" t="n"/>
+      <c r="Q164" s="13" t="n"/>
+      <c r="R164" s="13" t="n"/>
+      <c r="S164" s="13" t="n"/>
+      <c r="T164" s="13" t="n"/>
     </row>
     <row r="165" ht="23" customHeight="1">
       <c r="A165" s="6" t="n"/>
@@ -3582,14 +4246,18 @@
       <c r="F165" s="6" t="n"/>
       <c r="G165" s="8" t="n"/>
       <c r="H165" s="6" t="n"/>
-      <c r="I165" s="6" t="n"/>
+      <c r="I165" s="8" t="n"/>
       <c r="J165" s="8" t="n"/>
-      <c r="K165" s="6" t="n"/>
+      <c r="K165" s="9" t="n"/>
       <c r="L165" s="6" t="n"/>
-      <c r="M165" s="9" t="n"/>
-      <c r="N165" s="9" t="n"/>
-      <c r="O165" s="9" t="n"/>
-      <c r="P165" s="9" t="n"/>
+      <c r="M165" s="6" t="n"/>
+      <c r="N165" s="8" t="n"/>
+      <c r="O165" s="6" t="n"/>
+      <c r="P165" s="6" t="n"/>
+      <c r="Q165" s="9" t="n"/>
+      <c r="R165" s="9" t="n"/>
+      <c r="S165" s="9" t="n"/>
+      <c r="T165" s="9" t="n"/>
     </row>
     <row r="166" ht="23" customHeight="1">
       <c r="A166" s="10" t="n"/>
@@ -3600,14 +4268,18 @@
       <c r="F166" s="10" t="n"/>
       <c r="G166" s="12" t="n"/>
       <c r="H166" s="10" t="n"/>
-      <c r="I166" s="10" t="n"/>
+      <c r="I166" s="12" t="n"/>
       <c r="J166" s="12" t="n"/>
-      <c r="K166" s="10" t="n"/>
+      <c r="K166" s="13" t="n"/>
       <c r="L166" s="10" t="n"/>
-      <c r="M166" s="13" t="n"/>
-      <c r="N166" s="13" t="n"/>
-      <c r="O166" s="13" t="n"/>
-      <c r="P166" s="13" t="n"/>
+      <c r="M166" s="10" t="n"/>
+      <c r="N166" s="12" t="n"/>
+      <c r="O166" s="10" t="n"/>
+      <c r="P166" s="10" t="n"/>
+      <c r="Q166" s="13" t="n"/>
+      <c r="R166" s="13" t="n"/>
+      <c r="S166" s="13" t="n"/>
+      <c r="T166" s="13" t="n"/>
     </row>
     <row r="167" ht="23" customHeight="1">
       <c r="A167" s="6" t="n"/>
@@ -3618,14 +4290,18 @@
       <c r="F167" s="6" t="n"/>
       <c r="G167" s="8" t="n"/>
       <c r="H167" s="6" t="n"/>
-      <c r="I167" s="6" t="n"/>
+      <c r="I167" s="8" t="n"/>
       <c r="J167" s="8" t="n"/>
-      <c r="K167" s="6" t="n"/>
+      <c r="K167" s="9" t="n"/>
       <c r="L167" s="6" t="n"/>
-      <c r="M167" s="9" t="n"/>
-      <c r="N167" s="9" t="n"/>
-      <c r="O167" s="9" t="n"/>
-      <c r="P167" s="9" t="n"/>
+      <c r="M167" s="6" t="n"/>
+      <c r="N167" s="8" t="n"/>
+      <c r="O167" s="6" t="n"/>
+      <c r="P167" s="6" t="n"/>
+      <c r="Q167" s="9" t="n"/>
+      <c r="R167" s="9" t="n"/>
+      <c r="S167" s="9" t="n"/>
+      <c r="T167" s="9" t="n"/>
     </row>
     <row r="168" ht="23" customHeight="1">
       <c r="A168" s="10" t="n"/>
@@ -3636,14 +4312,18 @@
       <c r="F168" s="10" t="n"/>
       <c r="G168" s="12" t="n"/>
       <c r="H168" s="10" t="n"/>
-      <c r="I168" s="10" t="n"/>
+      <c r="I168" s="12" t="n"/>
       <c r="J168" s="12" t="n"/>
-      <c r="K168" s="10" t="n"/>
+      <c r="K168" s="13" t="n"/>
       <c r="L168" s="10" t="n"/>
-      <c r="M168" s="13" t="n"/>
-      <c r="N168" s="13" t="n"/>
-      <c r="O168" s="13" t="n"/>
-      <c r="P168" s="13" t="n"/>
+      <c r="M168" s="10" t="n"/>
+      <c r="N168" s="12" t="n"/>
+      <c r="O168" s="10" t="n"/>
+      <c r="P168" s="10" t="n"/>
+      <c r="Q168" s="13" t="n"/>
+      <c r="R168" s="13" t="n"/>
+      <c r="S168" s="13" t="n"/>
+      <c r="T168" s="13" t="n"/>
     </row>
     <row r="169" ht="23" customHeight="1">
       <c r="A169" s="6" t="n"/>
@@ -3654,14 +4334,18 @@
       <c r="F169" s="6" t="n"/>
       <c r="G169" s="8" t="n"/>
       <c r="H169" s="6" t="n"/>
-      <c r="I169" s="6" t="n"/>
+      <c r="I169" s="8" t="n"/>
       <c r="J169" s="8" t="n"/>
-      <c r="K169" s="6" t="n"/>
+      <c r="K169" s="9" t="n"/>
       <c r="L169" s="6" t="n"/>
-      <c r="M169" s="9" t="n"/>
-      <c r="N169" s="9" t="n"/>
-      <c r="O169" s="9" t="n"/>
-      <c r="P169" s="9" t="n"/>
+      <c r="M169" s="6" t="n"/>
+      <c r="N169" s="8" t="n"/>
+      <c r="O169" s="6" t="n"/>
+      <c r="P169" s="6" t="n"/>
+      <c r="Q169" s="9" t="n"/>
+      <c r="R169" s="9" t="n"/>
+      <c r="S169" s="9" t="n"/>
+      <c r="T169" s="9" t="n"/>
     </row>
     <row r="170" ht="23" customHeight="1">
       <c r="A170" s="10" t="n"/>
@@ -3672,14 +4356,18 @@
       <c r="F170" s="10" t="n"/>
       <c r="G170" s="12" t="n"/>
       <c r="H170" s="10" t="n"/>
-      <c r="I170" s="10" t="n"/>
+      <c r="I170" s="12" t="n"/>
       <c r="J170" s="12" t="n"/>
-      <c r="K170" s="10" t="n"/>
+      <c r="K170" s="13" t="n"/>
       <c r="L170" s="10" t="n"/>
-      <c r="M170" s="13" t="n"/>
-      <c r="N170" s="13" t="n"/>
-      <c r="O170" s="13" t="n"/>
-      <c r="P170" s="13" t="n"/>
+      <c r="M170" s="10" t="n"/>
+      <c r="N170" s="12" t="n"/>
+      <c r="O170" s="10" t="n"/>
+      <c r="P170" s="10" t="n"/>
+      <c r="Q170" s="13" t="n"/>
+      <c r="R170" s="13" t="n"/>
+      <c r="S170" s="13" t="n"/>
+      <c r="T170" s="13" t="n"/>
     </row>
     <row r="171" ht="23" customHeight="1">
       <c r="A171" s="6" t="n"/>
@@ -3690,14 +4378,18 @@
       <c r="F171" s="6" t="n"/>
       <c r="G171" s="8" t="n"/>
       <c r="H171" s="6" t="n"/>
-      <c r="I171" s="6" t="n"/>
+      <c r="I171" s="8" t="n"/>
       <c r="J171" s="8" t="n"/>
-      <c r="K171" s="6" t="n"/>
+      <c r="K171" s="9" t="n"/>
       <c r="L171" s="6" t="n"/>
-      <c r="M171" s="9" t="n"/>
-      <c r="N171" s="9" t="n"/>
-      <c r="O171" s="9" t="n"/>
-      <c r="P171" s="9" t="n"/>
+      <c r="M171" s="6" t="n"/>
+      <c r="N171" s="8" t="n"/>
+      <c r="O171" s="6" t="n"/>
+      <c r="P171" s="6" t="n"/>
+      <c r="Q171" s="9" t="n"/>
+      <c r="R171" s="9" t="n"/>
+      <c r="S171" s="9" t="n"/>
+      <c r="T171" s="9" t="n"/>
     </row>
     <row r="172" ht="23" customHeight="1">
       <c r="A172" s="10" t="n"/>
@@ -3708,14 +4400,18 @@
       <c r="F172" s="10" t="n"/>
       <c r="G172" s="12" t="n"/>
       <c r="H172" s="10" t="n"/>
-      <c r="I172" s="10" t="n"/>
+      <c r="I172" s="12" t="n"/>
       <c r="J172" s="12" t="n"/>
-      <c r="K172" s="10" t="n"/>
+      <c r="K172" s="13" t="n"/>
       <c r="L172" s="10" t="n"/>
-      <c r="M172" s="13" t="n"/>
-      <c r="N172" s="13" t="n"/>
-      <c r="O172" s="13" t="n"/>
-      <c r="P172" s="13" t="n"/>
+      <c r="M172" s="10" t="n"/>
+      <c r="N172" s="12" t="n"/>
+      <c r="O172" s="10" t="n"/>
+      <c r="P172" s="10" t="n"/>
+      <c r="Q172" s="13" t="n"/>
+      <c r="R172" s="13" t="n"/>
+      <c r="S172" s="13" t="n"/>
+      <c r="T172" s="13" t="n"/>
     </row>
     <row r="173" ht="23" customHeight="1">
       <c r="A173" s="6" t="n"/>
@@ -3726,14 +4422,18 @@
       <c r="F173" s="6" t="n"/>
       <c r="G173" s="8" t="n"/>
       <c r="H173" s="6" t="n"/>
-      <c r="I173" s="6" t="n"/>
+      <c r="I173" s="8" t="n"/>
       <c r="J173" s="8" t="n"/>
-      <c r="K173" s="6" t="n"/>
+      <c r="K173" s="9" t="n"/>
       <c r="L173" s="6" t="n"/>
-      <c r="M173" s="9" t="n"/>
-      <c r="N173" s="9" t="n"/>
-      <c r="O173" s="9" t="n"/>
-      <c r="P173" s="9" t="n"/>
+      <c r="M173" s="6" t="n"/>
+      <c r="N173" s="8" t="n"/>
+      <c r="O173" s="6" t="n"/>
+      <c r="P173" s="6" t="n"/>
+      <c r="Q173" s="9" t="n"/>
+      <c r="R173" s="9" t="n"/>
+      <c r="S173" s="9" t="n"/>
+      <c r="T173" s="9" t="n"/>
     </row>
     <row r="174" ht="23" customHeight="1">
       <c r="A174" s="10" t="n"/>
@@ -3744,14 +4444,18 @@
       <c r="F174" s="10" t="n"/>
       <c r="G174" s="12" t="n"/>
       <c r="H174" s="10" t="n"/>
-      <c r="I174" s="10" t="n"/>
+      <c r="I174" s="12" t="n"/>
       <c r="J174" s="12" t="n"/>
-      <c r="K174" s="10" t="n"/>
+      <c r="K174" s="13" t="n"/>
       <c r="L174" s="10" t="n"/>
-      <c r="M174" s="13" t="n"/>
-      <c r="N174" s="13" t="n"/>
-      <c r="O174" s="13" t="n"/>
-      <c r="P174" s="13" t="n"/>
+      <c r="M174" s="10" t="n"/>
+      <c r="N174" s="12" t="n"/>
+      <c r="O174" s="10" t="n"/>
+      <c r="P174" s="10" t="n"/>
+      <c r="Q174" s="13" t="n"/>
+      <c r="R174" s="13" t="n"/>
+      <c r="S174" s="13" t="n"/>
+      <c r="T174" s="13" t="n"/>
     </row>
     <row r="175" ht="23" customHeight="1">
       <c r="A175" s="6" t="n"/>
@@ -3762,14 +4466,18 @@
       <c r="F175" s="6" t="n"/>
       <c r="G175" s="8" t="n"/>
       <c r="H175" s="6" t="n"/>
-      <c r="I175" s="6" t="n"/>
+      <c r="I175" s="8" t="n"/>
       <c r="J175" s="8" t="n"/>
-      <c r="K175" s="6" t="n"/>
+      <c r="K175" s="9" t="n"/>
       <c r="L175" s="6" t="n"/>
-      <c r="M175" s="9" t="n"/>
-      <c r="N175" s="9" t="n"/>
-      <c r="O175" s="9" t="n"/>
-      <c r="P175" s="9" t="n"/>
+      <c r="M175" s="6" t="n"/>
+      <c r="N175" s="8" t="n"/>
+      <c r="O175" s="6" t="n"/>
+      <c r="P175" s="6" t="n"/>
+      <c r="Q175" s="9" t="n"/>
+      <c r="R175" s="9" t="n"/>
+      <c r="S175" s="9" t="n"/>
+      <c r="T175" s="9" t="n"/>
     </row>
     <row r="176" ht="23" customHeight="1">
       <c r="A176" s="10" t="n"/>
@@ -3780,14 +4488,18 @@
       <c r="F176" s="10" t="n"/>
       <c r="G176" s="12" t="n"/>
       <c r="H176" s="10" t="n"/>
-      <c r="I176" s="10" t="n"/>
+      <c r="I176" s="12" t="n"/>
       <c r="J176" s="12" t="n"/>
-      <c r="K176" s="10" t="n"/>
+      <c r="K176" s="13" t="n"/>
       <c r="L176" s="10" t="n"/>
-      <c r="M176" s="13" t="n"/>
-      <c r="N176" s="13" t="n"/>
-      <c r="O176" s="13" t="n"/>
-      <c r="P176" s="13" t="n"/>
+      <c r="M176" s="10" t="n"/>
+      <c r="N176" s="12" t="n"/>
+      <c r="O176" s="10" t="n"/>
+      <c r="P176" s="10" t="n"/>
+      <c r="Q176" s="13" t="n"/>
+      <c r="R176" s="13" t="n"/>
+      <c r="S176" s="13" t="n"/>
+      <c r="T176" s="13" t="n"/>
     </row>
     <row r="177" ht="23" customHeight="1">
       <c r="A177" s="6" t="n"/>
@@ -3798,14 +4510,18 @@
       <c r="F177" s="6" t="n"/>
       <c r="G177" s="8" t="n"/>
       <c r="H177" s="6" t="n"/>
-      <c r="I177" s="6" t="n"/>
+      <c r="I177" s="8" t="n"/>
       <c r="J177" s="8" t="n"/>
-      <c r="K177" s="6" t="n"/>
+      <c r="K177" s="9" t="n"/>
       <c r="L177" s="6" t="n"/>
-      <c r="M177" s="9" t="n"/>
-      <c r="N177" s="9" t="n"/>
-      <c r="O177" s="9" t="n"/>
-      <c r="P177" s="9" t="n"/>
+      <c r="M177" s="6" t="n"/>
+      <c r="N177" s="8" t="n"/>
+      <c r="O177" s="6" t="n"/>
+      <c r="P177" s="6" t="n"/>
+      <c r="Q177" s="9" t="n"/>
+      <c r="R177" s="9" t="n"/>
+      <c r="S177" s="9" t="n"/>
+      <c r="T177" s="9" t="n"/>
     </row>
     <row r="178" ht="23" customHeight="1">
       <c r="A178" s="10" t="n"/>
@@ -3816,14 +4532,18 @@
       <c r="F178" s="10" t="n"/>
       <c r="G178" s="12" t="n"/>
       <c r="H178" s="10" t="n"/>
-      <c r="I178" s="10" t="n"/>
+      <c r="I178" s="12" t="n"/>
       <c r="J178" s="12" t="n"/>
-      <c r="K178" s="10" t="n"/>
+      <c r="K178" s="13" t="n"/>
       <c r="L178" s="10" t="n"/>
-      <c r="M178" s="13" t="n"/>
-      <c r="N178" s="13" t="n"/>
-      <c r="O178" s="13" t="n"/>
-      <c r="P178" s="13" t="n"/>
+      <c r="M178" s="10" t="n"/>
+      <c r="N178" s="12" t="n"/>
+      <c r="O178" s="10" t="n"/>
+      <c r="P178" s="10" t="n"/>
+      <c r="Q178" s="13" t="n"/>
+      <c r="R178" s="13" t="n"/>
+      <c r="S178" s="13" t="n"/>
+      <c r="T178" s="13" t="n"/>
     </row>
     <row r="179" ht="23" customHeight="1">
       <c r="A179" s="6" t="n"/>
@@ -3834,14 +4554,18 @@
       <c r="F179" s="6" t="n"/>
       <c r="G179" s="8" t="n"/>
       <c r="H179" s="6" t="n"/>
-      <c r="I179" s="6" t="n"/>
+      <c r="I179" s="8" t="n"/>
       <c r="J179" s="8" t="n"/>
-      <c r="K179" s="6" t="n"/>
+      <c r="K179" s="9" t="n"/>
       <c r="L179" s="6" t="n"/>
-      <c r="M179" s="9" t="n"/>
-      <c r="N179" s="9" t="n"/>
-      <c r="O179" s="9" t="n"/>
-      <c r="P179" s="9" t="n"/>
+      <c r="M179" s="6" t="n"/>
+      <c r="N179" s="8" t="n"/>
+      <c r="O179" s="6" t="n"/>
+      <c r="P179" s="6" t="n"/>
+      <c r="Q179" s="9" t="n"/>
+      <c r="R179" s="9" t="n"/>
+      <c r="S179" s="9" t="n"/>
+      <c r="T179" s="9" t="n"/>
     </row>
     <row r="180" ht="23" customHeight="1">
       <c r="A180" s="10" t="n"/>
@@ -3852,14 +4576,18 @@
       <c r="F180" s="10" t="n"/>
       <c r="G180" s="12" t="n"/>
       <c r="H180" s="10" t="n"/>
-      <c r="I180" s="10" t="n"/>
+      <c r="I180" s="12" t="n"/>
       <c r="J180" s="12" t="n"/>
-      <c r="K180" s="10" t="n"/>
+      <c r="K180" s="13" t="n"/>
       <c r="L180" s="10" t="n"/>
-      <c r="M180" s="13" t="n"/>
-      <c r="N180" s="13" t="n"/>
-      <c r="O180" s="13" t="n"/>
-      <c r="P180" s="13" t="n"/>
+      <c r="M180" s="10" t="n"/>
+      <c r="N180" s="12" t="n"/>
+      <c r="O180" s="10" t="n"/>
+      <c r="P180" s="10" t="n"/>
+      <c r="Q180" s="13" t="n"/>
+      <c r="R180" s="13" t="n"/>
+      <c r="S180" s="13" t="n"/>
+      <c r="T180" s="13" t="n"/>
     </row>
     <row r="181" ht="23" customHeight="1">
       <c r="A181" s="6" t="n"/>
@@ -3870,14 +4598,18 @@
       <c r="F181" s="6" t="n"/>
       <c r="G181" s="8" t="n"/>
       <c r="H181" s="6" t="n"/>
-      <c r="I181" s="6" t="n"/>
+      <c r="I181" s="8" t="n"/>
       <c r="J181" s="8" t="n"/>
-      <c r="K181" s="6" t="n"/>
+      <c r="K181" s="9" t="n"/>
       <c r="L181" s="6" t="n"/>
-      <c r="M181" s="9" t="n"/>
-      <c r="N181" s="9" t="n"/>
-      <c r="O181" s="9" t="n"/>
-      <c r="P181" s="9" t="n"/>
+      <c r="M181" s="6" t="n"/>
+      <c r="N181" s="8" t="n"/>
+      <c r="O181" s="6" t="n"/>
+      <c r="P181" s="6" t="n"/>
+      <c r="Q181" s="9" t="n"/>
+      <c r="R181" s="9" t="n"/>
+      <c r="S181" s="9" t="n"/>
+      <c r="T181" s="9" t="n"/>
     </row>
     <row r="182" ht="23" customHeight="1">
       <c r="A182" s="10" t="n"/>
@@ -3888,14 +4620,18 @@
       <c r="F182" s="10" t="n"/>
       <c r="G182" s="12" t="n"/>
       <c r="H182" s="10" t="n"/>
-      <c r="I182" s="10" t="n"/>
+      <c r="I182" s="12" t="n"/>
       <c r="J182" s="12" t="n"/>
-      <c r="K182" s="10" t="n"/>
+      <c r="K182" s="13" t="n"/>
       <c r="L182" s="10" t="n"/>
-      <c r="M182" s="13" t="n"/>
-      <c r="N182" s="13" t="n"/>
-      <c r="O182" s="13" t="n"/>
-      <c r="P182" s="13" t="n"/>
+      <c r="M182" s="10" t="n"/>
+      <c r="N182" s="12" t="n"/>
+      <c r="O182" s="10" t="n"/>
+      <c r="P182" s="10" t="n"/>
+      <c r="Q182" s="13" t="n"/>
+      <c r="R182" s="13" t="n"/>
+      <c r="S182" s="13" t="n"/>
+      <c r="T182" s="13" t="n"/>
     </row>
     <row r="183" ht="23" customHeight="1">
       <c r="A183" s="6" t="n"/>
@@ -3906,14 +4642,18 @@
       <c r="F183" s="6" t="n"/>
       <c r="G183" s="8" t="n"/>
       <c r="H183" s="6" t="n"/>
-      <c r="I183" s="6" t="n"/>
+      <c r="I183" s="8" t="n"/>
       <c r="J183" s="8" t="n"/>
-      <c r="K183" s="6" t="n"/>
+      <c r="K183" s="9" t="n"/>
       <c r="L183" s="6" t="n"/>
-      <c r="M183" s="9" t="n"/>
-      <c r="N183" s="9" t="n"/>
-      <c r="O183" s="9" t="n"/>
-      <c r="P183" s="9" t="n"/>
+      <c r="M183" s="6" t="n"/>
+      <c r="N183" s="8" t="n"/>
+      <c r="O183" s="6" t="n"/>
+      <c r="P183" s="6" t="n"/>
+      <c r="Q183" s="9" t="n"/>
+      <c r="R183" s="9" t="n"/>
+      <c r="S183" s="9" t="n"/>
+      <c r="T183" s="9" t="n"/>
     </row>
     <row r="184" ht="23" customHeight="1">
       <c r="A184" s="10" t="n"/>
@@ -3924,14 +4664,18 @@
       <c r="F184" s="10" t="n"/>
       <c r="G184" s="12" t="n"/>
       <c r="H184" s="10" t="n"/>
-      <c r="I184" s="10" t="n"/>
+      <c r="I184" s="12" t="n"/>
       <c r="J184" s="12" t="n"/>
-      <c r="K184" s="10" t="n"/>
+      <c r="K184" s="13" t="n"/>
       <c r="L184" s="10" t="n"/>
-      <c r="M184" s="13" t="n"/>
-      <c r="N184" s="13" t="n"/>
-      <c r="O184" s="13" t="n"/>
-      <c r="P184" s="13" t="n"/>
+      <c r="M184" s="10" t="n"/>
+      <c r="N184" s="12" t="n"/>
+      <c r="O184" s="10" t="n"/>
+      <c r="P184" s="10" t="n"/>
+      <c r="Q184" s="13" t="n"/>
+      <c r="R184" s="13" t="n"/>
+      <c r="S184" s="13" t="n"/>
+      <c r="T184" s="13" t="n"/>
     </row>
     <row r="185" ht="23" customHeight="1">
       <c r="A185" s="6" t="n"/>
@@ -3942,14 +4686,18 @@
       <c r="F185" s="6" t="n"/>
       <c r="G185" s="8" t="n"/>
       <c r="H185" s="6" t="n"/>
-      <c r="I185" s="6" t="n"/>
+      <c r="I185" s="8" t="n"/>
       <c r="J185" s="8" t="n"/>
-      <c r="K185" s="6" t="n"/>
+      <c r="K185" s="9" t="n"/>
       <c r="L185" s="6" t="n"/>
-      <c r="M185" s="9" t="n"/>
-      <c r="N185" s="9" t="n"/>
-      <c r="O185" s="9" t="n"/>
-      <c r="P185" s="9" t="n"/>
+      <c r="M185" s="6" t="n"/>
+      <c r="N185" s="8" t="n"/>
+      <c r="O185" s="6" t="n"/>
+      <c r="P185" s="6" t="n"/>
+      <c r="Q185" s="9" t="n"/>
+      <c r="R185" s="9" t="n"/>
+      <c r="S185" s="9" t="n"/>
+      <c r="T185" s="9" t="n"/>
     </row>
     <row r="186" ht="23" customHeight="1">
       <c r="A186" s="10" t="n"/>
@@ -3960,14 +4708,18 @@
       <c r="F186" s="10" t="n"/>
       <c r="G186" s="12" t="n"/>
       <c r="H186" s="10" t="n"/>
-      <c r="I186" s="10" t="n"/>
+      <c r="I186" s="12" t="n"/>
       <c r="J186" s="12" t="n"/>
-      <c r="K186" s="10" t="n"/>
+      <c r="K186" s="13" t="n"/>
       <c r="L186" s="10" t="n"/>
-      <c r="M186" s="13" t="n"/>
-      <c r="N186" s="13" t="n"/>
-      <c r="O186" s="13" t="n"/>
-      <c r="P186" s="13" t="n"/>
+      <c r="M186" s="10" t="n"/>
+      <c r="N186" s="12" t="n"/>
+      <c r="O186" s="10" t="n"/>
+      <c r="P186" s="10" t="n"/>
+      <c r="Q186" s="13" t="n"/>
+      <c r="R186" s="13" t="n"/>
+      <c r="S186" s="13" t="n"/>
+      <c r="T186" s="13" t="n"/>
     </row>
     <row r="187" ht="23" customHeight="1">
       <c r="A187" s="6" t="n"/>
@@ -3978,14 +4730,18 @@
       <c r="F187" s="6" t="n"/>
       <c r="G187" s="8" t="n"/>
       <c r="H187" s="6" t="n"/>
-      <c r="I187" s="6" t="n"/>
+      <c r="I187" s="8" t="n"/>
       <c r="J187" s="8" t="n"/>
-      <c r="K187" s="6" t="n"/>
+      <c r="K187" s="9" t="n"/>
       <c r="L187" s="6" t="n"/>
-      <c r="M187" s="9" t="n"/>
-      <c r="N187" s="9" t="n"/>
-      <c r="O187" s="9" t="n"/>
-      <c r="P187" s="9" t="n"/>
+      <c r="M187" s="6" t="n"/>
+      <c r="N187" s="8" t="n"/>
+      <c r="O187" s="6" t="n"/>
+      <c r="P187" s="6" t="n"/>
+      <c r="Q187" s="9" t="n"/>
+      <c r="R187" s="9" t="n"/>
+      <c r="S187" s="9" t="n"/>
+      <c r="T187" s="9" t="n"/>
     </row>
     <row r="188" ht="23" customHeight="1">
       <c r="A188" s="10" t="n"/>
@@ -3996,14 +4752,18 @@
       <c r="F188" s="10" t="n"/>
       <c r="G188" s="12" t="n"/>
       <c r="H188" s="10" t="n"/>
-      <c r="I188" s="10" t="n"/>
+      <c r="I188" s="12" t="n"/>
       <c r="J188" s="12" t="n"/>
-      <c r="K188" s="10" t="n"/>
+      <c r="K188" s="13" t="n"/>
       <c r="L188" s="10" t="n"/>
-      <c r="M188" s="13" t="n"/>
-      <c r="N188" s="13" t="n"/>
-      <c r="O188" s="13" t="n"/>
-      <c r="P188" s="13" t="n"/>
+      <c r="M188" s="10" t="n"/>
+      <c r="N188" s="12" t="n"/>
+      <c r="O188" s="10" t="n"/>
+      <c r="P188" s="10" t="n"/>
+      <c r="Q188" s="13" t="n"/>
+      <c r="R188" s="13" t="n"/>
+      <c r="S188" s="13" t="n"/>
+      <c r="T188" s="13" t="n"/>
     </row>
     <row r="189" ht="23" customHeight="1">
       <c r="A189" s="6" t="n"/>
@@ -4014,14 +4774,18 @@
       <c r="F189" s="6" t="n"/>
       <c r="G189" s="8" t="n"/>
       <c r="H189" s="6" t="n"/>
-      <c r="I189" s="6" t="n"/>
+      <c r="I189" s="8" t="n"/>
       <c r="J189" s="8" t="n"/>
-      <c r="K189" s="6" t="n"/>
+      <c r="K189" s="9" t="n"/>
       <c r="L189" s="6" t="n"/>
-      <c r="M189" s="9" t="n"/>
-      <c r="N189" s="9" t="n"/>
-      <c r="O189" s="9" t="n"/>
-      <c r="P189" s="9" t="n"/>
+      <c r="M189" s="6" t="n"/>
+      <c r="N189" s="8" t="n"/>
+      <c r="O189" s="6" t="n"/>
+      <c r="P189" s="6" t="n"/>
+      <c r="Q189" s="9" t="n"/>
+      <c r="R189" s="9" t="n"/>
+      <c r="S189" s="9" t="n"/>
+      <c r="T189" s="9" t="n"/>
     </row>
     <row r="190" ht="23" customHeight="1">
       <c r="A190" s="10" t="n"/>
@@ -4032,14 +4796,18 @@
       <c r="F190" s="10" t="n"/>
       <c r="G190" s="12" t="n"/>
       <c r="H190" s="10" t="n"/>
-      <c r="I190" s="10" t="n"/>
+      <c r="I190" s="12" t="n"/>
       <c r="J190" s="12" t="n"/>
-      <c r="K190" s="10" t="n"/>
+      <c r="K190" s="13" t="n"/>
       <c r="L190" s="10" t="n"/>
-      <c r="M190" s="13" t="n"/>
-      <c r="N190" s="13" t="n"/>
-      <c r="O190" s="13" t="n"/>
-      <c r="P190" s="13" t="n"/>
+      <c r="M190" s="10" t="n"/>
+      <c r="N190" s="12" t="n"/>
+      <c r="O190" s="10" t="n"/>
+      <c r="P190" s="10" t="n"/>
+      <c r="Q190" s="13" t="n"/>
+      <c r="R190" s="13" t="n"/>
+      <c r="S190" s="13" t="n"/>
+      <c r="T190" s="13" t="n"/>
     </row>
     <row r="191" ht="23" customHeight="1">
       <c r="A191" s="6" t="n"/>
@@ -4050,14 +4818,18 @@
       <c r="F191" s="6" t="n"/>
       <c r="G191" s="8" t="n"/>
       <c r="H191" s="6" t="n"/>
-      <c r="I191" s="6" t="n"/>
+      <c r="I191" s="8" t="n"/>
       <c r="J191" s="8" t="n"/>
-      <c r="K191" s="6" t="n"/>
+      <c r="K191" s="9" t="n"/>
       <c r="L191" s="6" t="n"/>
-      <c r="M191" s="9" t="n"/>
-      <c r="N191" s="9" t="n"/>
-      <c r="O191" s="9" t="n"/>
-      <c r="P191" s="9" t="n"/>
+      <c r="M191" s="6" t="n"/>
+      <c r="N191" s="8" t="n"/>
+      <c r="O191" s="6" t="n"/>
+      <c r="P191" s="6" t="n"/>
+      <c r="Q191" s="9" t="n"/>
+      <c r="R191" s="9" t="n"/>
+      <c r="S191" s="9" t="n"/>
+      <c r="T191" s="9" t="n"/>
     </row>
     <row r="192" ht="23" customHeight="1">
       <c r="A192" s="10" t="n"/>
@@ -4068,14 +4840,18 @@
       <c r="F192" s="10" t="n"/>
       <c r="G192" s="12" t="n"/>
       <c r="H192" s="10" t="n"/>
-      <c r="I192" s="10" t="n"/>
+      <c r="I192" s="12" t="n"/>
       <c r="J192" s="12" t="n"/>
-      <c r="K192" s="10" t="n"/>
+      <c r="K192" s="13" t="n"/>
       <c r="L192" s="10" t="n"/>
-      <c r="M192" s="13" t="n"/>
-      <c r="N192" s="13" t="n"/>
-      <c r="O192" s="13" t="n"/>
-      <c r="P192" s="13" t="n"/>
+      <c r="M192" s="10" t="n"/>
+      <c r="N192" s="12" t="n"/>
+      <c r="O192" s="10" t="n"/>
+      <c r="P192" s="10" t="n"/>
+      <c r="Q192" s="13" t="n"/>
+      <c r="R192" s="13" t="n"/>
+      <c r="S192" s="13" t="n"/>
+      <c r="T192" s="13" t="n"/>
     </row>
     <row r="193" ht="23" customHeight="1">
       <c r="A193" s="6" t="n"/>
@@ -4086,14 +4862,18 @@
       <c r="F193" s="6" t="n"/>
       <c r="G193" s="8" t="n"/>
       <c r="H193" s="6" t="n"/>
-      <c r="I193" s="6" t="n"/>
+      <c r="I193" s="8" t="n"/>
       <c r="J193" s="8" t="n"/>
-      <c r="K193" s="6" t="n"/>
+      <c r="K193" s="9" t="n"/>
       <c r="L193" s="6" t="n"/>
-      <c r="M193" s="9" t="n"/>
-      <c r="N193" s="9" t="n"/>
-      <c r="O193" s="9" t="n"/>
-      <c r="P193" s="9" t="n"/>
+      <c r="M193" s="6" t="n"/>
+      <c r="N193" s="8" t="n"/>
+      <c r="O193" s="6" t="n"/>
+      <c r="P193" s="6" t="n"/>
+      <c r="Q193" s="9" t="n"/>
+      <c r="R193" s="9" t="n"/>
+      <c r="S193" s="9" t="n"/>
+      <c r="T193" s="9" t="n"/>
     </row>
     <row r="194" ht="23" customHeight="1">
       <c r="A194" s="10" t="n"/>
@@ -4104,14 +4884,18 @@
       <c r="F194" s="10" t="n"/>
       <c r="G194" s="12" t="n"/>
       <c r="H194" s="10" t="n"/>
-      <c r="I194" s="10" t="n"/>
+      <c r="I194" s="12" t="n"/>
       <c r="J194" s="12" t="n"/>
-      <c r="K194" s="10" t="n"/>
+      <c r="K194" s="13" t="n"/>
       <c r="L194" s="10" t="n"/>
-      <c r="M194" s="13" t="n"/>
-      <c r="N194" s="13" t="n"/>
-      <c r="O194" s="13" t="n"/>
-      <c r="P194" s="13" t="n"/>
+      <c r="M194" s="10" t="n"/>
+      <c r="N194" s="12" t="n"/>
+      <c r="O194" s="10" t="n"/>
+      <c r="P194" s="10" t="n"/>
+      <c r="Q194" s="13" t="n"/>
+      <c r="R194" s="13" t="n"/>
+      <c r="S194" s="13" t="n"/>
+      <c r="T194" s="13" t="n"/>
     </row>
     <row r="195" ht="23" customHeight="1">
       <c r="A195" s="6" t="n"/>
@@ -4122,14 +4906,18 @@
       <c r="F195" s="6" t="n"/>
       <c r="G195" s="8" t="n"/>
       <c r="H195" s="6" t="n"/>
-      <c r="I195" s="6" t="n"/>
+      <c r="I195" s="8" t="n"/>
       <c r="J195" s="8" t="n"/>
-      <c r="K195" s="6" t="n"/>
+      <c r="K195" s="9" t="n"/>
       <c r="L195" s="6" t="n"/>
-      <c r="M195" s="9" t="n"/>
-      <c r="N195" s="9" t="n"/>
-      <c r="O195" s="9" t="n"/>
-      <c r="P195" s="9" t="n"/>
+      <c r="M195" s="6" t="n"/>
+      <c r="N195" s="8" t="n"/>
+      <c r="O195" s="6" t="n"/>
+      <c r="P195" s="6" t="n"/>
+      <c r="Q195" s="9" t="n"/>
+      <c r="R195" s="9" t="n"/>
+      <c r="S195" s="9" t="n"/>
+      <c r="T195" s="9" t="n"/>
     </row>
     <row r="196" ht="23" customHeight="1">
       <c r="A196" s="10" t="n"/>
@@ -4140,14 +4928,18 @@
       <c r="F196" s="10" t="n"/>
       <c r="G196" s="12" t="n"/>
       <c r="H196" s="10" t="n"/>
-      <c r="I196" s="10" t="n"/>
+      <c r="I196" s="12" t="n"/>
       <c r="J196" s="12" t="n"/>
-      <c r="K196" s="10" t="n"/>
+      <c r="K196" s="13" t="n"/>
       <c r="L196" s="10" t="n"/>
-      <c r="M196" s="13" t="n"/>
-      <c r="N196" s="13" t="n"/>
-      <c r="O196" s="13" t="n"/>
-      <c r="P196" s="13" t="n"/>
+      <c r="M196" s="10" t="n"/>
+      <c r="N196" s="12" t="n"/>
+      <c r="O196" s="10" t="n"/>
+      <c r="P196" s="10" t="n"/>
+      <c r="Q196" s="13" t="n"/>
+      <c r="R196" s="13" t="n"/>
+      <c r="S196" s="13" t="n"/>
+      <c r="T196" s="13" t="n"/>
     </row>
     <row r="197" ht="23" customHeight="1">
       <c r="A197" s="6" t="n"/>
@@ -4158,14 +4950,18 @@
       <c r="F197" s="6" t="n"/>
       <c r="G197" s="8" t="n"/>
       <c r="H197" s="6" t="n"/>
-      <c r="I197" s="6" t="n"/>
+      <c r="I197" s="8" t="n"/>
       <c r="J197" s="8" t="n"/>
-      <c r="K197" s="6" t="n"/>
+      <c r="K197" s="9" t="n"/>
       <c r="L197" s="6" t="n"/>
-      <c r="M197" s="9" t="n"/>
-      <c r="N197" s="9" t="n"/>
-      <c r="O197" s="9" t="n"/>
-      <c r="P197" s="9" t="n"/>
+      <c r="M197" s="6" t="n"/>
+      <c r="N197" s="8" t="n"/>
+      <c r="O197" s="6" t="n"/>
+      <c r="P197" s="6" t="n"/>
+      <c r="Q197" s="9" t="n"/>
+      <c r="R197" s="9" t="n"/>
+      <c r="S197" s="9" t="n"/>
+      <c r="T197" s="9" t="n"/>
     </row>
     <row r="198" ht="23" customHeight="1">
       <c r="A198" s="10" t="n"/>
@@ -4176,14 +4972,18 @@
       <c r="F198" s="10" t="n"/>
       <c r="G198" s="12" t="n"/>
       <c r="H198" s="10" t="n"/>
-      <c r="I198" s="10" t="n"/>
+      <c r="I198" s="12" t="n"/>
       <c r="J198" s="12" t="n"/>
-      <c r="K198" s="10" t="n"/>
+      <c r="K198" s="13" t="n"/>
       <c r="L198" s="10" t="n"/>
-      <c r="M198" s="13" t="n"/>
-      <c r="N198" s="13" t="n"/>
-      <c r="O198" s="13" t="n"/>
-      <c r="P198" s="13" t="n"/>
+      <c r="M198" s="10" t="n"/>
+      <c r="N198" s="12" t="n"/>
+      <c r="O198" s="10" t="n"/>
+      <c r="P198" s="10" t="n"/>
+      <c r="Q198" s="13" t="n"/>
+      <c r="R198" s="13" t="n"/>
+      <c r="S198" s="13" t="n"/>
+      <c r="T198" s="13" t="n"/>
     </row>
     <row r="199" ht="23" customHeight="1">
       <c r="A199" s="6" t="n"/>
@@ -4194,14 +4994,18 @@
       <c r="F199" s="6" t="n"/>
       <c r="G199" s="8" t="n"/>
       <c r="H199" s="6" t="n"/>
-      <c r="I199" s="6" t="n"/>
+      <c r="I199" s="8" t="n"/>
       <c r="J199" s="8" t="n"/>
-      <c r="K199" s="6" t="n"/>
+      <c r="K199" s="9" t="n"/>
       <c r="L199" s="6" t="n"/>
-      <c r="M199" s="9" t="n"/>
-      <c r="N199" s="9" t="n"/>
-      <c r="O199" s="9" t="n"/>
-      <c r="P199" s="9" t="n"/>
+      <c r="M199" s="6" t="n"/>
+      <c r="N199" s="8" t="n"/>
+      <c r="O199" s="6" t="n"/>
+      <c r="P199" s="6" t="n"/>
+      <c r="Q199" s="9" t="n"/>
+      <c r="R199" s="9" t="n"/>
+      <c r="S199" s="9" t="n"/>
+      <c r="T199" s="9" t="n"/>
     </row>
     <row r="200" ht="23" customHeight="1">
       <c r="A200" s="10" t="n"/>
@@ -4212,14 +5016,18 @@
       <c r="F200" s="10" t="n"/>
       <c r="G200" s="12" t="n"/>
       <c r="H200" s="10" t="n"/>
-      <c r="I200" s="10" t="n"/>
+      <c r="I200" s="12" t="n"/>
       <c r="J200" s="12" t="n"/>
-      <c r="K200" s="10" t="n"/>
+      <c r="K200" s="13" t="n"/>
       <c r="L200" s="10" t="n"/>
-      <c r="M200" s="13" t="n"/>
-      <c r="N200" s="13" t="n"/>
-      <c r="O200" s="13" t="n"/>
-      <c r="P200" s="13" t="n"/>
+      <c r="M200" s="10" t="n"/>
+      <c r="N200" s="12" t="n"/>
+      <c r="O200" s="10" t="n"/>
+      <c r="P200" s="10" t="n"/>
+      <c r="Q200" s="13" t="n"/>
+      <c r="R200" s="13" t="n"/>
+      <c r="S200" s="13" t="n"/>
+      <c r="T200" s="13" t="n"/>
     </row>
     <row r="201" ht="23" customHeight="1">
       <c r="A201" s="6" t="n"/>
@@ -4230,14 +5038,18 @@
       <c r="F201" s="6" t="n"/>
       <c r="G201" s="8" t="n"/>
       <c r="H201" s="6" t="n"/>
-      <c r="I201" s="6" t="n"/>
+      <c r="I201" s="8" t="n"/>
       <c r="J201" s="8" t="n"/>
-      <c r="K201" s="6" t="n"/>
+      <c r="K201" s="9" t="n"/>
       <c r="L201" s="6" t="n"/>
-      <c r="M201" s="9" t="n"/>
-      <c r="N201" s="9" t="n"/>
-      <c r="O201" s="9" t="n"/>
-      <c r="P201" s="9" t="n"/>
+      <c r="M201" s="6" t="n"/>
+      <c r="N201" s="8" t="n"/>
+      <c r="O201" s="6" t="n"/>
+      <c r="P201" s="6" t="n"/>
+      <c r="Q201" s="9" t="n"/>
+      <c r="R201" s="9" t="n"/>
+      <c r="S201" s="9" t="n"/>
+      <c r="T201" s="9" t="n"/>
     </row>
     <row r="202" ht="23" customHeight="1">
       <c r="A202" s="10" t="n"/>
@@ -4248,14 +5060,18 @@
       <c r="F202" s="10" t="n"/>
       <c r="G202" s="12" t="n"/>
       <c r="H202" s="10" t="n"/>
-      <c r="I202" s="10" t="n"/>
+      <c r="I202" s="12" t="n"/>
       <c r="J202" s="12" t="n"/>
-      <c r="K202" s="10" t="n"/>
+      <c r="K202" s="13" t="n"/>
       <c r="L202" s="10" t="n"/>
-      <c r="M202" s="13" t="n"/>
-      <c r="N202" s="13" t="n"/>
-      <c r="O202" s="13" t="n"/>
-      <c r="P202" s="13" t="n"/>
+      <c r="M202" s="10" t="n"/>
+      <c r="N202" s="12" t="n"/>
+      <c r="O202" s="10" t="n"/>
+      <c r="P202" s="10" t="n"/>
+      <c r="Q202" s="13" t="n"/>
+      <c r="R202" s="13" t="n"/>
+      <c r="S202" s="13" t="n"/>
+      <c r="T202" s="13" t="n"/>
     </row>
     <row r="203" ht="23" customHeight="1">
       <c r="A203" s="6" t="n"/>
@@ -4266,14 +5082,18 @@
       <c r="F203" s="6" t="n"/>
       <c r="G203" s="8" t="n"/>
       <c r="H203" s="6" t="n"/>
-      <c r="I203" s="6" t="n"/>
+      <c r="I203" s="8" t="n"/>
       <c r="J203" s="8" t="n"/>
-      <c r="K203" s="6" t="n"/>
+      <c r="K203" s="9" t="n"/>
       <c r="L203" s="6" t="n"/>
-      <c r="M203" s="9" t="n"/>
-      <c r="N203" s="9" t="n"/>
-      <c r="O203" s="9" t="n"/>
-      <c r="P203" s="9" t="n"/>
+      <c r="M203" s="6" t="n"/>
+      <c r="N203" s="8" t="n"/>
+      <c r="O203" s="6" t="n"/>
+      <c r="P203" s="6" t="n"/>
+      <c r="Q203" s="9" t="n"/>
+      <c r="R203" s="9" t="n"/>
+      <c r="S203" s="9" t="n"/>
+      <c r="T203" s="9" t="n"/>
     </row>
     <row r="204" ht="23" customHeight="1">
       <c r="A204" s="10" t="n"/>
@@ -4284,37 +5104,44 @@
       <c r="F204" s="10" t="n"/>
       <c r="G204" s="12" t="n"/>
       <c r="H204" s="10" t="n"/>
-      <c r="I204" s="10" t="n"/>
+      <c r="I204" s="12" t="n"/>
       <c r="J204" s="12" t="n"/>
-      <c r="K204" s="10" t="n"/>
+      <c r="K204" s="13" t="n"/>
       <c r="L204" s="10" t="n"/>
-      <c r="M204" s="13" t="n"/>
-      <c r="N204" s="13" t="n"/>
-      <c r="O204" s="13" t="n"/>
-      <c r="P204" s="13" t="n"/>
+      <c r="M204" s="10" t="n"/>
+      <c r="N204" s="12" t="n"/>
+      <c r="O204" s="10" t="n"/>
+      <c r="P204" s="10" t="n"/>
+      <c r="Q204" s="13" t="n"/>
+      <c r="R204" s="13" t="n"/>
+      <c r="S204" s="13" t="n"/>
+      <c r="T204" s="13" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:P204"/>
+  <autoFilter ref="A4:T204"/>
   <mergeCells count="3">
-    <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A3:P3"/>
-    <mergeCell ref="A2:P2"/>
+    <mergeCell ref="A1:T1"/>
+    <mergeCell ref="A3:T3"/>
+    <mergeCell ref="A2:T2"/>
   </mergeCells>
-  <conditionalFormatting sqref="I5:I1004">
+  <conditionalFormatting sqref="M5:M1004">
     <cfRule type="expression" priority="1" dxfId="0">
-      <formula>$I5="已完成"</formula>
+      <formula>$M5="已完成"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H5:H1004">
+  <conditionalFormatting sqref="L5:L1004">
     <cfRule type="expression" priority="2" dxfId="1">
-      <formula>$H5="高"</formula>
+      <formula>$L5="高"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="5">
-    <dataValidation sqref="H5:H1004" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="选项无效" error="请从下拉选项中选择。" promptTitle="紧急程度" prompt="必填，请从下拉选项中选择。" type="list" errorStyle="stop">
+  <dataValidations count="6">
+    <dataValidation sqref="H5:H1004" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="选项无效" error="请从下拉选项中选择。" promptTitle="周期" prompt="留空按“不重复”导入。" type="list" errorStyle="stop">
+      <formula1>"不重复,每周,每月"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L5:L1004" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="选项无效" error="请从下拉选项中选择。" promptTitle="紧急程度" prompt="必填，请从下拉选项中选择。" type="list" errorStyle="stop">
       <formula1>"高,中,低"</formula1>
     </dataValidation>
-    <dataValidation sqref="I5:I1004" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="选项无效" error="请从下拉选项中选择。" promptTitle="完成状态" prompt="留空时按“未完成”导入。" type="list" errorStyle="stop">
+    <dataValidation sqref="M5:M1004" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" errorTitle="选项无效" error="请从下拉选项中选择。" promptTitle="完成状态" prompt="留空时按“未完成”导入。" type="list" errorStyle="stop">
       <formula1>"未完成,已完成"</formula1>
     </dataValidation>
     <dataValidation sqref="E5:E1004" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="步骤序号无效" error="Flow步骤必须是大于 0 的整数。" type="whole" operator="between">
@@ -4325,7 +5152,7 @@
       <formula1>DATE(2000,1,1)</formula1>
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
-    <dataValidation sqref="J5:J1004" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="完成日期无效" error="请输入 2000-01-01 至 2100-12-31 之间的日期。" type="date" operator="between">
+    <dataValidation sqref="I5:I1004 J5:J1004 N5:N1004" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="日期无效" error="请输入 2000-01-01 至 2100-12-31 之间的日期。" type="date" operator="between">
       <formula1>DATE(2000,1,1)</formula1>
       <formula2>DATE(2100,12,31)</formula2>
     </dataValidation>
@@ -4342,7 +5169,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -4368,7 +5195,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="16" t="inlineStr">
         <is>
-          <t>2. 分组与 Task name、DDL 为必填；Flow 可选。</t>
+          <t>2. 分组与 Task name、DDL 为必填；Flow 和周期可选，周期 Task 必须填写起止日期。</t>
         </is>
       </c>
     </row>
@@ -4565,139 +5392,139 @@
     <row r="14" ht="38" customHeight="1">
       <c r="A14" s="20" t="inlineStr">
         <is>
-          <t>紧急程度*</t>
+          <t>周期</t>
         </is>
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
         <is>
-          <t>高 / 中 / 低，必须从下拉选项中选择</t>
+          <t>不重复 / 每周 / 每月；留空按不重复</t>
         </is>
       </c>
       <c r="D14" s="20" t="inlineStr">
         <is>
-          <t>高</t>
+          <t>每周</t>
         </is>
       </c>
     </row>
     <row r="15" ht="38" customHeight="1">
       <c r="A15" s="18" t="inlineStr">
         <is>
-          <t>完成状态</t>
+          <t>周期开始</t>
         </is>
       </c>
       <c r="B15" s="19" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>周期时是</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>未完成 / 已完成；留空默认为未完成</t>
+          <t>周期 Task 的开始日期，须与周期结束同时填写</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>未完成</t>
+          <t>2026-08-01</t>
         </is>
       </c>
     </row>
     <row r="16" ht="38" customHeight="1">
       <c r="A16" s="20" t="inlineStr">
         <is>
-          <t>完成日期</t>
+          <t>周期结束</t>
         </is>
       </c>
       <c r="B16" s="21" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>周期时是</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
         <is>
-          <t>仅已完成 Task 使用；留空时按导入当天记录</t>
+          <t>周期 Task 的结束日期；DDL 必须位于起止范围内</t>
         </is>
       </c>
       <c r="D16" s="20" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-09-30</t>
         </is>
       </c>
     </row>
     <row r="17" ht="38" customHeight="1">
       <c r="A17" s="18" t="inlineStr">
         <is>
-          <t>汇报对象*</t>
+          <t>周期完成记录</t>
         </is>
       </c>
       <c r="B17" s="19" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>会与既有同名对象统一，便于筛选</t>
+          <t>格式：周期DDL|完成日期；多期用换行或中文分号分隔。新建时可留空，当前数据下载会自动填写</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>项目负责人</t>
+          <t>2026-08-07|2026-08-08</t>
         </is>
       </c>
     </row>
     <row r="18" ht="38" customHeight="1">
       <c r="A18" s="20" t="inlineStr">
         <is>
-          <t>管理对象</t>
+          <t>紧急程度*</t>
         </is>
       </c>
       <c r="B18" s="21" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
         <is>
-          <t>会与既有同名对象统一，便于筛选</t>
+          <t>高 / 中 / 低，必须从下拉选项中选择</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
         <is>
-          <t>发布小组</t>
+          <t>高</t>
         </is>
       </c>
     </row>
     <row r="19" ht="38" customHeight="1">
       <c r="A19" s="18" t="inlineStr">
         <is>
-          <t>交付物*</t>
+          <t>完成状态</t>
         </is>
       </c>
       <c r="B19" s="19" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="C19" s="18" t="inlineStr">
         <is>
-          <t>简要描述交付成果，最多 500 个字符</t>
+          <t>未完成 / 已完成；留空默认为未完成</t>
         </is>
       </c>
       <c r="D19" s="18" t="inlineStr">
         <is>
-          <t>发布确认单</t>
+          <t>未完成</t>
         </is>
       </c>
     </row>
     <row r="20" ht="38" customHeight="1">
       <c r="A20" s="20" t="inlineStr">
         <is>
-          <t>进度记录</t>
+          <t>完成日期</t>
         </is>
       </c>
       <c r="B20" s="21" t="inlineStr">
@@ -4707,61 +5534,149 @@
       </c>
       <c r="C20" s="20" t="inlineStr">
         <is>
-          <t>可填写当前进度或备注，最多 4000 个字符</t>
+          <t>仅已完成 Task 使用；留空时按导入当天记录</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
         <is>
-          <t>已完成联调</t>
+          <t>2026-08-06</t>
         </is>
       </c>
     </row>
     <row r="21" ht="38" customHeight="1">
       <c r="A21" s="18" t="inlineStr">
         <is>
-          <t>说明文档链接</t>
+          <t>汇报对象*</t>
         </is>
       </c>
       <c r="B21" s="19" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="C21" s="18" t="inlineStr">
         <is>
-          <t>格式：标题|https://...；多个链接用换行或中文分号分隔</t>
+          <t>填写人员姓名；会与既有同名人员统一，便于筛选</t>
         </is>
       </c>
       <c r="D21" s="18" t="inlineStr">
         <is>
-          <t>操作说明|https://example.com/guide</t>
+          <t>Wesley Yan</t>
         </is>
       </c>
     </row>
     <row r="22" ht="38" customHeight="1">
       <c r="A22" s="20" t="inlineStr">
         <is>
+          <t>管理对象</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C22" s="20" t="inlineStr">
+        <is>
+          <t>填写人员姓名；会与既有同名人员统一，便于筛选</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>Amy Chen</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="38" customHeight="1">
+      <c r="A23" s="18" t="inlineStr">
+        <is>
+          <t>交付物*</t>
+        </is>
+      </c>
+      <c r="B23" s="19" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>简要描述交付成果，最多 500 个字符</t>
+        </is>
+      </c>
+      <c r="D23" s="18" t="inlineStr">
+        <is>
+          <t>发布确认单</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="38" customHeight="1">
+      <c r="A24" s="20" t="inlineStr">
+        <is>
+          <t>进度记录</t>
+        </is>
+      </c>
+      <c r="B24" s="21" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C24" s="20" t="inlineStr">
+        <is>
+          <t>可填写当前进度或备注，最多 4000 个字符</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>已完成联调</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="38" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
+        <is>
+          <t>说明文档链接</t>
+        </is>
+      </c>
+      <c r="B25" s="19" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>格式：标题|https://...；多个链接用换行或中文分号分隔</t>
+        </is>
+      </c>
+      <c r="D25" s="18" t="inlineStr">
+        <is>
+          <t>操作说明|https://example.com/guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="38" customHeight="1">
+      <c r="A26" s="20" t="inlineStr">
+        <is>
           <t>交付物链接</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="C22" s="20" t="inlineStr">
+      <c r="C26" s="20" t="inlineStr">
         <is>
           <t>格式：标题|https://...；多个链接用换行或中文分号分隔</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
+      <c r="D26" s="20" t="inlineStr">
         <is>
           <t>交付文件|https://example.com/delivery</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:D22"/>
+  <autoFilter ref="A6:D26"/>
   <mergeCells count="5">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A5:D5"/>
